--- a/trips/astana-2026-10/spisok_uchenikov_astana.xlsx
+++ b/trips/astana-2026-10/spisok_uchenikov_astana.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Ученики!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Ученики!$A$4:$P$104</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Ученики!$A$4:$K$104</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
   <si>
     <t xml:space="preserve">Список учеников — поездка в Астану (университеты), 27–28 октября 2026</t>
   </si>
@@ -75,21 +75,6 @@
     <t xml:space="preserve">Классный руководитель</t>
   </si>
   <si>
-    <t xml:space="preserve">Дата рождения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Возраст на дату выезда</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИИН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласие родителей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мед. справка</t>
-  </si>
-  <si>
     <t xml:space="preserve">Оплачено, тг</t>
   </si>
   <si>
@@ -138,12 +123,6 @@
     <t xml:space="preserve">Учеников в списке</t>
   </si>
   <si>
-    <t xml:space="preserve">Согласие родителей получено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мед. справка сдана</t>
-  </si>
-  <si>
     <t xml:space="preserve">Оплатили полностью</t>
   </si>
   <si>
@@ -174,33 +153,21 @@
     <t xml:space="preserve">1. Лист «Ученики»: одна строка — один ученик. Заполняйте только жёлтые ячейки.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Серые ячейки (№, классный руководитель, возраст, остаток, статус оплаты, «Готов к поездке») считаются сами.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. ИИН вводится как 12 цифр (ячейка текстовая, ведущие нули сохраняются). Нужен для билетов и заселения.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. «Согласие родителей» и «Мед. справка» — выбор из списка Да / Нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Когда станет известна стоимость поездки, впишите её на листе «Сводка» в ячейку C4 — статусы оплаты пересчитаются.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. «Готов к поездке» = Да, только если есть ИИН из 12 цифр, согласие, справка и полная оплата.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Лист «Классы»: класс и его классный руководитель. Класс пишите так же, как в списке (например, 11 «А»).</t>
+    <t xml:space="preserve">2. Серые ячейки (№, классный руководитель, остаток, статус оплаты, «Готов к поездке») считаются сами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Когда станет известна стоимость поездки, впишите её на листе «Сводка» в ячейку C4 — статусы оплаты пересчитаются.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. «Готов к поездке» = Да, когда поездка оплачена полностью.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Лист «Классы»: класс и его классный руководитель. Класс пишите так же, как в списке (например, 11 «А»).</t>
   </si>
   <si>
     <t xml:space="preserve">Пример заполненной строки (вымышленный ученик, в список не переносить)</t>
   </si>
   <si>
-    <t xml:space="preserve">Согласие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Справка</t>
-  </si>
-  <si>
     <t xml:space="preserve">Иванов</t>
   </si>
   <si>
@@ -213,29 +180,22 @@
     <t xml:space="preserve">11 «А»</t>
   </si>
   <si>
-    <t xml:space="preserve">090314500123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Да</t>
-  </si>
-  <si>
     <t xml:space="preserve">Вегетарианец</t>
   </si>
   <si>
-    <t xml:space="preserve">Важно: файл с ИИН — персональные данные. Не выкладывайте заполненный список в общий доступ и в репозиторий.</t>
+    <t xml:space="preserve">Важно: список учеников — персональные данные. Не выкладывайте заполненный файл в общий доступ и в репозиторий.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
-    <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -398,7 +358,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -435,15 +395,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -455,7 +407,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -467,15 +419,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -488,10 +444,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -844,7 +796,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -853,15 +805,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -907,21 +854,6 @@
       </c>
       <c r="K4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -938,27 +870,19 @@
         <v/>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="4" t="str">
-        <f aca="false">IF(G5="","",DATEDIF(G5,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11" t="str">
-        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",Сводка!$C$4-L5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="4" t="str">
-        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",IF(L5&gt;=Сводка!$C$4,"Оплачено",IF(L5&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O5" s="4" t="str">
-        <f aca="false">IF(B5="","",IF(AND(LEN(I5)=12,J5="Да",K5="Да",N5="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P5" s="5"/>
+      <c r="H5" s="9" t="str">
+        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",Сводка!$C$4-G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
+        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",IF(G5&gt;=Сводка!$C$4,"Оплачено",IF(G5&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J5" s="4" t="str">
+        <f aca="false">IF(B5="","",IF(I5="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="str">
@@ -974,27 +898,19 @@
         <v/>
       </c>
       <c r="G6" s="8"/>
-      <c r="H6" s="4" t="str">
-        <f aca="false">IF(G6="","",DATEDIF(G6,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="11" t="str">
-        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",Сводка!$C$4-L6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="4" t="str">
-        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",IF(L6&gt;=Сводка!$C$4,"Оплачено",IF(L6&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O6" s="4" t="str">
-        <f aca="false">IF(B6="","",IF(AND(LEN(I6)=12,J6="Да",K6="Да",N6="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P6" s="5"/>
+      <c r="H6" s="9" t="str">
+        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",Сводка!$C$4-G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="str">
+        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",IF(G6&gt;=Сводка!$C$4,"Оплачено",IF(G6&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J6" s="4" t="str">
+        <f aca="false">IF(B6="","",IF(I6="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="str">
@@ -1010,27 +926,19 @@
         <v/>
       </c>
       <c r="G7" s="8"/>
-      <c r="H7" s="4" t="str">
-        <f aca="false">IF(G7="","",DATEDIF(G7,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="11" t="str">
-        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",Сводка!$C$4-L7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="4" t="str">
-        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",IF(L7&gt;=Сводка!$C$4,"Оплачено",IF(L7&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O7" s="4" t="str">
-        <f aca="false">IF(B7="","",IF(AND(LEN(I7)=12,J7="Да",K7="Да",N7="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P7" s="5"/>
+      <c r="H7" s="9" t="str">
+        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",Сводка!$C$4-G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="str">
+        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",IF(G7&gt;=Сводка!$C$4,"Оплачено",IF(G7&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="str">
+        <f aca="false">IF(B7="","",IF(I7="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="str">
@@ -1046,27 +954,19 @@
         <v/>
       </c>
       <c r="G8" s="8"/>
-      <c r="H8" s="4" t="str">
-        <f aca="false">IF(G8="","",DATEDIF(G8,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="11" t="str">
-        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",Сводка!$C$4-L8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="4" t="str">
-        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",IF(L8&gt;=Сводка!$C$4,"Оплачено",IF(L8&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O8" s="4" t="str">
-        <f aca="false">IF(B8="","",IF(AND(LEN(I8)=12,J8="Да",K8="Да",N8="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P8" s="5"/>
+      <c r="H8" s="9" t="str">
+        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",Сводка!$C$4-G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="str">
+        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",IF(G8&gt;=Сводка!$C$4,"Оплачено",IF(G8&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J8" s="4" t="str">
+        <f aca="false">IF(B8="","",IF(I8="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="str">
@@ -1082,27 +982,19 @@
         <v/>
       </c>
       <c r="G9" s="8"/>
-      <c r="H9" s="4" t="str">
-        <f aca="false">IF(G9="","",DATEDIF(G9,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11" t="str">
-        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",Сводка!$C$4-L9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="4" t="str">
-        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",IF(L9&gt;=Сводка!$C$4,"Оплачено",IF(L9&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O9" s="4" t="str">
-        <f aca="false">IF(B9="","",IF(AND(LEN(I9)=12,J9="Да",K9="Да",N9="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P9" s="5"/>
+      <c r="H9" s="9" t="str">
+        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",Сводка!$C$4-G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="str">
+        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",IF(G9&gt;=Сводка!$C$4,"Оплачено",IF(G9&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J9" s="4" t="str">
+        <f aca="false">IF(B9="","",IF(I9="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="str">
@@ -1118,27 +1010,19 @@
         <v/>
       </c>
       <c r="G10" s="8"/>
-      <c r="H10" s="4" t="str">
-        <f aca="false">IF(G10="","",DATEDIF(G10,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="11" t="str">
-        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",Сводка!$C$4-L10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="4" t="str">
-        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",IF(L10&gt;=Сводка!$C$4,"Оплачено",IF(L10&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O10" s="4" t="str">
-        <f aca="false">IF(B10="","",IF(AND(LEN(I10)=12,J10="Да",K10="Да",N10="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P10" s="5"/>
+      <c r="H10" s="9" t="str">
+        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",Сводка!$C$4-G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="str">
+        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",IF(G10&gt;=Сводка!$C$4,"Оплачено",IF(G10&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="str">
+        <f aca="false">IF(B10="","",IF(I10="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="str">
@@ -1154,27 +1038,19 @@
         <v/>
       </c>
       <c r="G11" s="8"/>
-      <c r="H11" s="4" t="str">
-        <f aca="false">IF(G11="","",DATEDIF(G11,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11" t="str">
-        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",Сводка!$C$4-L11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="4" t="str">
-        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",IF(L11&gt;=Сводка!$C$4,"Оплачено",IF(L11&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O11" s="4" t="str">
-        <f aca="false">IF(B11="","",IF(AND(LEN(I11)=12,J11="Да",K11="Да",N11="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P11" s="5"/>
+      <c r="H11" s="9" t="str">
+        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",Сводка!$C$4-G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="str">
+        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",IF(G11&gt;=Сводка!$C$4,"Оплачено",IF(G11&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J11" s="4" t="str">
+        <f aca="false">IF(B11="","",IF(I11="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="str">
@@ -1190,27 +1066,19 @@
         <v/>
       </c>
       <c r="G12" s="8"/>
-      <c r="H12" s="4" t="str">
-        <f aca="false">IF(G12="","",DATEDIF(G12,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="11" t="str">
-        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",Сводка!$C$4-L12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="4" t="str">
-        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",IF(L12&gt;=Сводка!$C$4,"Оплачено",IF(L12&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O12" s="4" t="str">
-        <f aca="false">IF(B12="","",IF(AND(LEN(I12)=12,J12="Да",K12="Да",N12="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P12" s="5"/>
+      <c r="H12" s="9" t="str">
+        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",Сводка!$C$4-G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="str">
+        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",IF(G12&gt;=Сводка!$C$4,"Оплачено",IF(G12&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J12" s="4" t="str">
+        <f aca="false">IF(B12="","",IF(I12="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="str">
@@ -1226,27 +1094,19 @@
         <v/>
       </c>
       <c r="G13" s="8"/>
-      <c r="H13" s="4" t="str">
-        <f aca="false">IF(G13="","",DATEDIF(G13,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="11" t="str">
-        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",Сводка!$C$4-L13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="4" t="str">
-        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",IF(L13&gt;=Сводка!$C$4,"Оплачено",IF(L13&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O13" s="4" t="str">
-        <f aca="false">IF(B13="","",IF(AND(LEN(I13)=12,J13="Да",K13="Да",N13="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P13" s="5"/>
+      <c r="H13" s="9" t="str">
+        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",Сводка!$C$4-G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="str">
+        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",IF(G13&gt;=Сводка!$C$4,"Оплачено",IF(G13&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J13" s="4" t="str">
+        <f aca="false">IF(B13="","",IF(I13="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="str">
@@ -1262,27 +1122,19 @@
         <v/>
       </c>
       <c r="G14" s="8"/>
-      <c r="H14" s="4" t="str">
-        <f aca="false">IF(G14="","",DATEDIF(G14,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="11" t="str">
-        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",Сводка!$C$4-L14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="4" t="str">
-        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",IF(L14&gt;=Сводка!$C$4,"Оплачено",IF(L14&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O14" s="4" t="str">
-        <f aca="false">IF(B14="","",IF(AND(LEN(I14)=12,J14="Да",K14="Да",N14="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P14" s="5"/>
+      <c r="H14" s="9" t="str">
+        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",Сводка!$C$4-G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="str">
+        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",IF(G14&gt;=Сводка!$C$4,"Оплачено",IF(G14&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="str">
+        <f aca="false">IF(B14="","",IF(I14="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="str">
@@ -1298,27 +1150,19 @@
         <v/>
       </c>
       <c r="G15" s="8"/>
-      <c r="H15" s="4" t="str">
-        <f aca="false">IF(G15="","",DATEDIF(G15,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="11" t="str">
-        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",Сводка!$C$4-L15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="4" t="str">
-        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",IF(L15&gt;=Сводка!$C$4,"Оплачено",IF(L15&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O15" s="4" t="str">
-        <f aca="false">IF(B15="","",IF(AND(LEN(I15)=12,J15="Да",K15="Да",N15="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P15" s="5"/>
+      <c r="H15" s="9" t="str">
+        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",Сводка!$C$4-G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="str">
+        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",IF(G15&gt;=Сводка!$C$4,"Оплачено",IF(G15&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J15" s="4" t="str">
+        <f aca="false">IF(B15="","",IF(I15="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="str">
@@ -1334,27 +1178,19 @@
         <v/>
       </c>
       <c r="G16" s="8"/>
-      <c r="H16" s="4" t="str">
-        <f aca="false">IF(G16="","",DATEDIF(G16,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="11" t="str">
-        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",Сводка!$C$4-L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="4" t="str">
-        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",IF(L16&gt;=Сводка!$C$4,"Оплачено",IF(L16&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O16" s="4" t="str">
-        <f aca="false">IF(B16="","",IF(AND(LEN(I16)=12,J16="Да",K16="Да",N16="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P16" s="5"/>
+      <c r="H16" s="9" t="str">
+        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",Сводка!$C$4-G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="str">
+        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",IF(G16&gt;=Сводка!$C$4,"Оплачено",IF(G16&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="str">
+        <f aca="false">IF(B16="","",IF(I16="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="str">
@@ -1370,27 +1206,19 @@
         <v/>
       </c>
       <c r="G17" s="8"/>
-      <c r="H17" s="4" t="str">
-        <f aca="false">IF(G17="","",DATEDIF(G17,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="11" t="str">
-        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",Сводка!$C$4-L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="4" t="str">
-        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",IF(L17&gt;=Сводка!$C$4,"Оплачено",IF(L17&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O17" s="4" t="str">
-        <f aca="false">IF(B17="","",IF(AND(LEN(I17)=12,J17="Да",K17="Да",N17="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P17" s="5"/>
+      <c r="H17" s="9" t="str">
+        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",Сводка!$C$4-G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="str">
+        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",IF(G17&gt;=Сводка!$C$4,"Оплачено",IF(G17&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J17" s="4" t="str">
+        <f aca="false">IF(B17="","",IF(I17="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="str">
@@ -1406,27 +1234,19 @@
         <v/>
       </c>
       <c r="G18" s="8"/>
-      <c r="H18" s="4" t="str">
-        <f aca="false">IF(G18="","",DATEDIF(G18,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="11" t="str">
-        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",Сводка!$C$4-L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="4" t="str">
-        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",IF(L18&gt;=Сводка!$C$4,"Оплачено",IF(L18&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O18" s="4" t="str">
-        <f aca="false">IF(B18="","",IF(AND(LEN(I18)=12,J18="Да",K18="Да",N18="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P18" s="5"/>
+      <c r="H18" s="9" t="str">
+        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",Сводка!$C$4-G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="str">
+        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",IF(G18&gt;=Сводка!$C$4,"Оплачено",IF(G18&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J18" s="4" t="str">
+        <f aca="false">IF(B18="","",IF(I18="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="str">
@@ -1442,27 +1262,19 @@
         <v/>
       </c>
       <c r="G19" s="8"/>
-      <c r="H19" s="4" t="str">
-        <f aca="false">IF(G19="","",DATEDIF(G19,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="11" t="str">
-        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",Сводка!$C$4-L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="4" t="str">
-        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",IF(L19&gt;=Сводка!$C$4,"Оплачено",IF(L19&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O19" s="4" t="str">
-        <f aca="false">IF(B19="","",IF(AND(LEN(I19)=12,J19="Да",K19="Да",N19="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P19" s="5"/>
+      <c r="H19" s="9" t="str">
+        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",Сводка!$C$4-G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="4" t="str">
+        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",IF(G19&gt;=Сводка!$C$4,"Оплачено",IF(G19&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J19" s="4" t="str">
+        <f aca="false">IF(B19="","",IF(I19="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="str">
@@ -1478,27 +1290,19 @@
         <v/>
       </c>
       <c r="G20" s="8"/>
-      <c r="H20" s="4" t="str">
-        <f aca="false">IF(G20="","",DATEDIF(G20,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="11" t="str">
-        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",Сводка!$C$4-L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="4" t="str">
-        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",IF(L20&gt;=Сводка!$C$4,"Оплачено",IF(L20&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O20" s="4" t="str">
-        <f aca="false">IF(B20="","",IF(AND(LEN(I20)=12,J20="Да",K20="Да",N20="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P20" s="5"/>
+      <c r="H20" s="9" t="str">
+        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",Сводка!$C$4-G20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="4" t="str">
+        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",IF(G20&gt;=Сводка!$C$4,"Оплачено",IF(G20&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J20" s="4" t="str">
+        <f aca="false">IF(B20="","",IF(I20="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="str">
@@ -1514,27 +1318,19 @@
         <v/>
       </c>
       <c r="G21" s="8"/>
-      <c r="H21" s="4" t="str">
-        <f aca="false">IF(G21="","",DATEDIF(G21,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="11" t="str">
-        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",Сводка!$C$4-L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="4" t="str">
-        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",IF(L21&gt;=Сводка!$C$4,"Оплачено",IF(L21&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O21" s="4" t="str">
-        <f aca="false">IF(B21="","",IF(AND(LEN(I21)=12,J21="Да",K21="Да",N21="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P21" s="5"/>
+      <c r="H21" s="9" t="str">
+        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",Сводка!$C$4-G21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="4" t="str">
+        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",IF(G21&gt;=Сводка!$C$4,"Оплачено",IF(G21&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J21" s="4" t="str">
+        <f aca="false">IF(B21="","",IF(I21="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="str">
@@ -1550,27 +1346,19 @@
         <v/>
       </c>
       <c r="G22" s="8"/>
-      <c r="H22" s="4" t="str">
-        <f aca="false">IF(G22="","",DATEDIF(G22,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="11" t="str">
-        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",Сводка!$C$4-L22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="4" t="str">
-        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",IF(L22&gt;=Сводка!$C$4,"Оплачено",IF(L22&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O22" s="4" t="str">
-        <f aca="false">IF(B22="","",IF(AND(LEN(I22)=12,J22="Да",K22="Да",N22="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P22" s="5"/>
+      <c r="H22" s="9" t="str">
+        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",Сводка!$C$4-G22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="4" t="str">
+        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",IF(G22&gt;=Сводка!$C$4,"Оплачено",IF(G22&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J22" s="4" t="str">
+        <f aca="false">IF(B22="","",IF(I22="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="str">
@@ -1586,27 +1374,19 @@
         <v/>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="4" t="str">
-        <f aca="false">IF(G23="","",DATEDIF(G23,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="11" t="str">
-        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",Сводка!$C$4-L23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="4" t="str">
-        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",IF(L23&gt;=Сводка!$C$4,"Оплачено",IF(L23&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O23" s="4" t="str">
-        <f aca="false">IF(B23="","",IF(AND(LEN(I23)=12,J23="Да",K23="Да",N23="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P23" s="5"/>
+      <c r="H23" s="9" t="str">
+        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",Сводка!$C$4-G23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="4" t="str">
+        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",IF(G23&gt;=Сводка!$C$4,"Оплачено",IF(G23&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J23" s="4" t="str">
+        <f aca="false">IF(B23="","",IF(I23="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="str">
@@ -1622,27 +1402,19 @@
         <v/>
       </c>
       <c r="G24" s="8"/>
-      <c r="H24" s="4" t="str">
-        <f aca="false">IF(G24="","",DATEDIF(G24,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="11" t="str">
-        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",Сводка!$C$4-L24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="4" t="str">
-        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",IF(L24&gt;=Сводка!$C$4,"Оплачено",IF(L24&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O24" s="4" t="str">
-        <f aca="false">IF(B24="","",IF(AND(LEN(I24)=12,J24="Да",K24="Да",N24="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P24" s="5"/>
+      <c r="H24" s="9" t="str">
+        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",Сводка!$C$4-G24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="4" t="str">
+        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",IF(G24&gt;=Сводка!$C$4,"Оплачено",IF(G24&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J24" s="4" t="str">
+        <f aca="false">IF(B24="","",IF(I24="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="str">
@@ -1658,27 +1430,19 @@
         <v/>
       </c>
       <c r="G25" s="8"/>
-      <c r="H25" s="4" t="str">
-        <f aca="false">IF(G25="","",DATEDIF(G25,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="11" t="str">
-        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",Сводка!$C$4-L25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="4" t="str">
-        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",IF(L25&gt;=Сводка!$C$4,"Оплачено",IF(L25&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O25" s="4" t="str">
-        <f aca="false">IF(B25="","",IF(AND(LEN(I25)=12,J25="Да",K25="Да",N25="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P25" s="5"/>
+      <c r="H25" s="9" t="str">
+        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",Сводка!$C$4-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="str">
+        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",IF(G25&gt;=Сводка!$C$4,"Оплачено",IF(G25&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J25" s="4" t="str">
+        <f aca="false">IF(B25="","",IF(I25="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="str">
@@ -1694,27 +1458,19 @@
         <v/>
       </c>
       <c r="G26" s="8"/>
-      <c r="H26" s="4" t="str">
-        <f aca="false">IF(G26="","",DATEDIF(G26,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="11" t="str">
-        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",Сводка!$C$4-L26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="4" t="str">
-        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",IF(L26&gt;=Сводка!$C$4,"Оплачено",IF(L26&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O26" s="4" t="str">
-        <f aca="false">IF(B26="","",IF(AND(LEN(I26)=12,J26="Да",K26="Да",N26="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P26" s="5"/>
+      <c r="H26" s="9" t="str">
+        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",Сводка!$C$4-G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="4" t="str">
+        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",IF(G26&gt;=Сводка!$C$4,"Оплачено",IF(G26&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J26" s="4" t="str">
+        <f aca="false">IF(B26="","",IF(I26="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="str">
@@ -1730,27 +1486,19 @@
         <v/>
       </c>
       <c r="G27" s="8"/>
-      <c r="H27" s="4" t="str">
-        <f aca="false">IF(G27="","",DATEDIF(G27,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="11" t="str">
-        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",Сводка!$C$4-L27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="4" t="str">
-        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",IF(L27&gt;=Сводка!$C$4,"Оплачено",IF(L27&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O27" s="4" t="str">
-        <f aca="false">IF(B27="","",IF(AND(LEN(I27)=12,J27="Да",K27="Да",N27="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P27" s="5"/>
+      <c r="H27" s="9" t="str">
+        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",Сводка!$C$4-G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="4" t="str">
+        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",IF(G27&gt;=Сводка!$C$4,"Оплачено",IF(G27&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J27" s="4" t="str">
+        <f aca="false">IF(B27="","",IF(I27="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="str">
@@ -1766,27 +1514,19 @@
         <v/>
       </c>
       <c r="G28" s="8"/>
-      <c r="H28" s="4" t="str">
-        <f aca="false">IF(G28="","",DATEDIF(G28,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="11" t="str">
-        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",Сводка!$C$4-L28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="4" t="str">
-        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",IF(L28&gt;=Сводка!$C$4,"Оплачено",IF(L28&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O28" s="4" t="str">
-        <f aca="false">IF(B28="","",IF(AND(LEN(I28)=12,J28="Да",K28="Да",N28="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P28" s="5"/>
+      <c r="H28" s="9" t="str">
+        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",Сводка!$C$4-G28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="str">
+        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",IF(G28&gt;=Сводка!$C$4,"Оплачено",IF(G28&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J28" s="4" t="str">
+        <f aca="false">IF(B28="","",IF(I28="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="str">
@@ -1802,27 +1542,19 @@
         <v/>
       </c>
       <c r="G29" s="8"/>
-      <c r="H29" s="4" t="str">
-        <f aca="false">IF(G29="","",DATEDIF(G29,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="11" t="str">
-        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",Сводка!$C$4-L29)</f>
-        <v/>
-      </c>
-      <c r="N29" s="4" t="str">
-        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",IF(L29&gt;=Сводка!$C$4,"Оплачено",IF(L29&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O29" s="4" t="str">
-        <f aca="false">IF(B29="","",IF(AND(LEN(I29)=12,J29="Да",K29="Да",N29="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P29" s="5"/>
+      <c r="H29" s="9" t="str">
+        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",Сводка!$C$4-G29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="4" t="str">
+        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",IF(G29&gt;=Сводка!$C$4,"Оплачено",IF(G29&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J29" s="4" t="str">
+        <f aca="false">IF(B29="","",IF(I29="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="str">
@@ -1838,27 +1570,19 @@
         <v/>
       </c>
       <c r="G30" s="8"/>
-      <c r="H30" s="4" t="str">
-        <f aca="false">IF(G30="","",DATEDIF(G30,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="11" t="str">
-        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",Сводка!$C$4-L30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="4" t="str">
-        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",IF(L30&gt;=Сводка!$C$4,"Оплачено",IF(L30&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O30" s="4" t="str">
-        <f aca="false">IF(B30="","",IF(AND(LEN(I30)=12,J30="Да",K30="Да",N30="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P30" s="5"/>
+      <c r="H30" s="9" t="str">
+        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",Сводка!$C$4-G30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="str">
+        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",IF(G30&gt;=Сводка!$C$4,"Оплачено",IF(G30&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J30" s="4" t="str">
+        <f aca="false">IF(B30="","",IF(I30="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="str">
@@ -1874,27 +1598,19 @@
         <v/>
       </c>
       <c r="G31" s="8"/>
-      <c r="H31" s="4" t="str">
-        <f aca="false">IF(G31="","",DATEDIF(G31,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="11" t="str">
-        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",Сводка!$C$4-L31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="4" t="str">
-        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",IF(L31&gt;=Сводка!$C$4,"Оплачено",IF(L31&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O31" s="4" t="str">
-        <f aca="false">IF(B31="","",IF(AND(LEN(I31)=12,J31="Да",K31="Да",N31="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P31" s="5"/>
+      <c r="H31" s="9" t="str">
+        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",Сводка!$C$4-G31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="str">
+        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",IF(G31&gt;=Сводка!$C$4,"Оплачено",IF(G31&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J31" s="4" t="str">
+        <f aca="false">IF(B31="","",IF(I31="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="str">
@@ -1910,27 +1626,19 @@
         <v/>
       </c>
       <c r="G32" s="8"/>
-      <c r="H32" s="4" t="str">
-        <f aca="false">IF(G32="","",DATEDIF(G32,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="11" t="str">
-        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",Сводка!$C$4-L32)</f>
-        <v/>
-      </c>
-      <c r="N32" s="4" t="str">
-        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",IF(L32&gt;=Сводка!$C$4,"Оплачено",IF(L32&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O32" s="4" t="str">
-        <f aca="false">IF(B32="","",IF(AND(LEN(I32)=12,J32="Да",K32="Да",N32="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P32" s="5"/>
+      <c r="H32" s="9" t="str">
+        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",Сводка!$C$4-G32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="str">
+        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",IF(G32&gt;=Сводка!$C$4,"Оплачено",IF(G32&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J32" s="4" t="str">
+        <f aca="false">IF(B32="","",IF(I32="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="str">
@@ -1946,27 +1654,19 @@
         <v/>
       </c>
       <c r="G33" s="8"/>
-      <c r="H33" s="4" t="str">
-        <f aca="false">IF(G33="","",DATEDIF(G33,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="11" t="str">
-        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",Сводка!$C$4-L33)</f>
-        <v/>
-      </c>
-      <c r="N33" s="4" t="str">
-        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",IF(L33&gt;=Сводка!$C$4,"Оплачено",IF(L33&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O33" s="4" t="str">
-        <f aca="false">IF(B33="","",IF(AND(LEN(I33)=12,J33="Да",K33="Да",N33="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P33" s="5"/>
+      <c r="H33" s="9" t="str">
+        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",Сводка!$C$4-G33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="4" t="str">
+        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",IF(G33&gt;=Сводка!$C$4,"Оплачено",IF(G33&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J33" s="4" t="str">
+        <f aca="false">IF(B33="","",IF(I33="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="str">
@@ -1982,27 +1682,19 @@
         <v/>
       </c>
       <c r="G34" s="8"/>
-      <c r="H34" s="4" t="str">
-        <f aca="false">IF(G34="","",DATEDIF(G34,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="11" t="str">
-        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",Сводка!$C$4-L34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="4" t="str">
-        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",IF(L34&gt;=Сводка!$C$4,"Оплачено",IF(L34&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O34" s="4" t="str">
-        <f aca="false">IF(B34="","",IF(AND(LEN(I34)=12,J34="Да",K34="Да",N34="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P34" s="5"/>
+      <c r="H34" s="9" t="str">
+        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",Сводка!$C$4-G34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="4" t="str">
+        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",IF(G34&gt;=Сводка!$C$4,"Оплачено",IF(G34&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J34" s="4" t="str">
+        <f aca="false">IF(B34="","",IF(I34="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="str">
@@ -2018,27 +1710,19 @@
         <v/>
       </c>
       <c r="G35" s="8"/>
-      <c r="H35" s="4" t="str">
-        <f aca="false">IF(G35="","",DATEDIF(G35,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="11" t="str">
-        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",Сводка!$C$4-L35)</f>
-        <v/>
-      </c>
-      <c r="N35" s="4" t="str">
-        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",IF(L35&gt;=Сводка!$C$4,"Оплачено",IF(L35&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O35" s="4" t="str">
-        <f aca="false">IF(B35="","",IF(AND(LEN(I35)=12,J35="Да",K35="Да",N35="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P35" s="5"/>
+      <c r="H35" s="9" t="str">
+        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",Сводка!$C$4-G35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="4" t="str">
+        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",IF(G35&gt;=Сводка!$C$4,"Оплачено",IF(G35&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J35" s="4" t="str">
+        <f aca="false">IF(B35="","",IF(I35="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="str">
@@ -2054,27 +1738,19 @@
         <v/>
       </c>
       <c r="G36" s="8"/>
-      <c r="H36" s="4" t="str">
-        <f aca="false">IF(G36="","",DATEDIF(G36,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="11" t="str">
-        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",Сводка!$C$4-L36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="4" t="str">
-        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",IF(L36&gt;=Сводка!$C$4,"Оплачено",IF(L36&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O36" s="4" t="str">
-        <f aca="false">IF(B36="","",IF(AND(LEN(I36)=12,J36="Да",K36="Да",N36="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P36" s="5"/>
+      <c r="H36" s="9" t="str">
+        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",Сводка!$C$4-G36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="str">
+        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",IF(G36&gt;=Сводка!$C$4,"Оплачено",IF(G36&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J36" s="4" t="str">
+        <f aca="false">IF(B36="","",IF(I36="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="str">
@@ -2090,27 +1766,19 @@
         <v/>
       </c>
       <c r="G37" s="8"/>
-      <c r="H37" s="4" t="str">
-        <f aca="false">IF(G37="","",DATEDIF(G37,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="11" t="str">
-        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",Сводка!$C$4-L37)</f>
-        <v/>
-      </c>
-      <c r="N37" s="4" t="str">
-        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",IF(L37&gt;=Сводка!$C$4,"Оплачено",IF(L37&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O37" s="4" t="str">
-        <f aca="false">IF(B37="","",IF(AND(LEN(I37)=12,J37="Да",K37="Да",N37="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P37" s="5"/>
+      <c r="H37" s="9" t="str">
+        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",Сводка!$C$4-G37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="4" t="str">
+        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",IF(G37&gt;=Сводка!$C$4,"Оплачено",IF(G37&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J37" s="4" t="str">
+        <f aca="false">IF(B37="","",IF(I37="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="str">
@@ -2126,27 +1794,19 @@
         <v/>
       </c>
       <c r="G38" s="8"/>
-      <c r="H38" s="4" t="str">
-        <f aca="false">IF(G38="","",DATEDIF(G38,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="11" t="str">
-        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",Сводка!$C$4-L38)</f>
-        <v/>
-      </c>
-      <c r="N38" s="4" t="str">
-        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",IF(L38&gt;=Сводка!$C$4,"Оплачено",IF(L38&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O38" s="4" t="str">
-        <f aca="false">IF(B38="","",IF(AND(LEN(I38)=12,J38="Да",K38="Да",N38="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P38" s="5"/>
+      <c r="H38" s="9" t="str">
+        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",Сводка!$C$4-G38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="4" t="str">
+        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",IF(G38&gt;=Сводка!$C$4,"Оплачено",IF(G38&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J38" s="4" t="str">
+        <f aca="false">IF(B38="","",IF(I38="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="str">
@@ -2162,27 +1822,19 @@
         <v/>
       </c>
       <c r="G39" s="8"/>
-      <c r="H39" s="4" t="str">
-        <f aca="false">IF(G39="","",DATEDIF(G39,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="11" t="str">
-        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",Сводка!$C$4-L39)</f>
-        <v/>
-      </c>
-      <c r="N39" s="4" t="str">
-        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",IF(L39&gt;=Сводка!$C$4,"Оплачено",IF(L39&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O39" s="4" t="str">
-        <f aca="false">IF(B39="","",IF(AND(LEN(I39)=12,J39="Да",K39="Да",N39="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P39" s="5"/>
+      <c r="H39" s="9" t="str">
+        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",Сводка!$C$4-G39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="4" t="str">
+        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",IF(G39&gt;=Сводка!$C$4,"Оплачено",IF(G39&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J39" s="4" t="str">
+        <f aca="false">IF(B39="","",IF(I39="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="str">
@@ -2198,27 +1850,19 @@
         <v/>
       </c>
       <c r="G40" s="8"/>
-      <c r="H40" s="4" t="str">
-        <f aca="false">IF(G40="","",DATEDIF(G40,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="11" t="str">
-        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",Сводка!$C$4-L40)</f>
-        <v/>
-      </c>
-      <c r="N40" s="4" t="str">
-        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",IF(L40&gt;=Сводка!$C$4,"Оплачено",IF(L40&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O40" s="4" t="str">
-        <f aca="false">IF(B40="","",IF(AND(LEN(I40)=12,J40="Да",K40="Да",N40="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P40" s="5"/>
+      <c r="H40" s="9" t="str">
+        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",Сводка!$C$4-G40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="4" t="str">
+        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",IF(G40&gt;=Сводка!$C$4,"Оплачено",IF(G40&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J40" s="4" t="str">
+        <f aca="false">IF(B40="","",IF(I40="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="str">
@@ -2234,27 +1878,19 @@
         <v/>
       </c>
       <c r="G41" s="8"/>
-      <c r="H41" s="4" t="str">
-        <f aca="false">IF(G41="","",DATEDIF(G41,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="11" t="str">
-        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",Сводка!$C$4-L41)</f>
-        <v/>
-      </c>
-      <c r="N41" s="4" t="str">
-        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",IF(L41&gt;=Сводка!$C$4,"Оплачено",IF(L41&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O41" s="4" t="str">
-        <f aca="false">IF(B41="","",IF(AND(LEN(I41)=12,J41="Да",K41="Да",N41="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P41" s="5"/>
+      <c r="H41" s="9" t="str">
+        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",Сводка!$C$4-G41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="4" t="str">
+        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",IF(G41&gt;=Сводка!$C$4,"Оплачено",IF(G41&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J41" s="4" t="str">
+        <f aca="false">IF(B41="","",IF(I41="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="str">
@@ -2270,27 +1906,19 @@
         <v/>
       </c>
       <c r="G42" s="8"/>
-      <c r="H42" s="4" t="str">
-        <f aca="false">IF(G42="","",DATEDIF(G42,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="11" t="str">
-        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",Сводка!$C$4-L42)</f>
-        <v/>
-      </c>
-      <c r="N42" s="4" t="str">
-        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",IF(L42&gt;=Сводка!$C$4,"Оплачено",IF(L42&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O42" s="4" t="str">
-        <f aca="false">IF(B42="","",IF(AND(LEN(I42)=12,J42="Да",K42="Да",N42="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P42" s="5"/>
+      <c r="H42" s="9" t="str">
+        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",Сводка!$C$4-G42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="4" t="str">
+        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",IF(G42&gt;=Сводка!$C$4,"Оплачено",IF(G42&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J42" s="4" t="str">
+        <f aca="false">IF(B42="","",IF(I42="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="str">
@@ -2306,27 +1934,19 @@
         <v/>
       </c>
       <c r="G43" s="8"/>
-      <c r="H43" s="4" t="str">
-        <f aca="false">IF(G43="","",DATEDIF(G43,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="11" t="str">
-        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",Сводка!$C$4-L43)</f>
-        <v/>
-      </c>
-      <c r="N43" s="4" t="str">
-        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",IF(L43&gt;=Сводка!$C$4,"Оплачено",IF(L43&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O43" s="4" t="str">
-        <f aca="false">IF(B43="","",IF(AND(LEN(I43)=12,J43="Да",K43="Да",N43="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P43" s="5"/>
+      <c r="H43" s="9" t="str">
+        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",Сводка!$C$4-G43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="4" t="str">
+        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",IF(G43&gt;=Сводка!$C$4,"Оплачено",IF(G43&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J43" s="4" t="str">
+        <f aca="false">IF(B43="","",IF(I43="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="str">
@@ -2342,27 +1962,19 @@
         <v/>
       </c>
       <c r="G44" s="8"/>
-      <c r="H44" s="4" t="str">
-        <f aca="false">IF(G44="","",DATEDIF(G44,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="11" t="str">
-        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",Сводка!$C$4-L44)</f>
-        <v/>
-      </c>
-      <c r="N44" s="4" t="str">
-        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",IF(L44&gt;=Сводка!$C$4,"Оплачено",IF(L44&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O44" s="4" t="str">
-        <f aca="false">IF(B44="","",IF(AND(LEN(I44)=12,J44="Да",K44="Да",N44="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P44" s="5"/>
+      <c r="H44" s="9" t="str">
+        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",Сводка!$C$4-G44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="4" t="str">
+        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",IF(G44&gt;=Сводка!$C$4,"Оплачено",IF(G44&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J44" s="4" t="str">
+        <f aca="false">IF(B44="","",IF(I44="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="str">
@@ -2378,27 +1990,19 @@
         <v/>
       </c>
       <c r="G45" s="8"/>
-      <c r="H45" s="4" t="str">
-        <f aca="false">IF(G45="","",DATEDIF(G45,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="11" t="str">
-        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",Сводка!$C$4-L45)</f>
-        <v/>
-      </c>
-      <c r="N45" s="4" t="str">
-        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",IF(L45&gt;=Сводка!$C$4,"Оплачено",IF(L45&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O45" s="4" t="str">
-        <f aca="false">IF(B45="","",IF(AND(LEN(I45)=12,J45="Да",K45="Да",N45="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P45" s="5"/>
+      <c r="H45" s="9" t="str">
+        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",Сводка!$C$4-G45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="4" t="str">
+        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",IF(G45&gt;=Сводка!$C$4,"Оплачено",IF(G45&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J45" s="4" t="str">
+        <f aca="false">IF(B45="","",IF(I45="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="str">
@@ -2414,27 +2018,19 @@
         <v/>
       </c>
       <c r="G46" s="8"/>
-      <c r="H46" s="4" t="str">
-        <f aca="false">IF(G46="","",DATEDIF(G46,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="11" t="str">
-        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",Сводка!$C$4-L46)</f>
-        <v/>
-      </c>
-      <c r="N46" s="4" t="str">
-        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",IF(L46&gt;=Сводка!$C$4,"Оплачено",IF(L46&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O46" s="4" t="str">
-        <f aca="false">IF(B46="","",IF(AND(LEN(I46)=12,J46="Да",K46="Да",N46="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P46" s="5"/>
+      <c r="H46" s="9" t="str">
+        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",Сводка!$C$4-G46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="4" t="str">
+        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",IF(G46&gt;=Сводка!$C$4,"Оплачено",IF(G46&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J46" s="4" t="str">
+        <f aca="false">IF(B46="","",IF(I46="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="str">
@@ -2450,27 +2046,19 @@
         <v/>
       </c>
       <c r="G47" s="8"/>
-      <c r="H47" s="4" t="str">
-        <f aca="false">IF(G47="","",DATEDIF(G47,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="11" t="str">
-        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",Сводка!$C$4-L47)</f>
-        <v/>
-      </c>
-      <c r="N47" s="4" t="str">
-        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",IF(L47&gt;=Сводка!$C$4,"Оплачено",IF(L47&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O47" s="4" t="str">
-        <f aca="false">IF(B47="","",IF(AND(LEN(I47)=12,J47="Да",K47="Да",N47="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P47" s="5"/>
+      <c r="H47" s="9" t="str">
+        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",Сводка!$C$4-G47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="4" t="str">
+        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",IF(G47&gt;=Сводка!$C$4,"Оплачено",IF(G47&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J47" s="4" t="str">
+        <f aca="false">IF(B47="","",IF(I47="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="str">
@@ -2486,27 +2074,19 @@
         <v/>
       </c>
       <c r="G48" s="8"/>
-      <c r="H48" s="4" t="str">
-        <f aca="false">IF(G48="","",DATEDIF(G48,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="11" t="str">
-        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",Сводка!$C$4-L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="4" t="str">
-        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",IF(L48&gt;=Сводка!$C$4,"Оплачено",IF(L48&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O48" s="4" t="str">
-        <f aca="false">IF(B48="","",IF(AND(LEN(I48)=12,J48="Да",K48="Да",N48="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P48" s="5"/>
+      <c r="H48" s="9" t="str">
+        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",Сводка!$C$4-G48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="4" t="str">
+        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",IF(G48&gt;=Сводка!$C$4,"Оплачено",IF(G48&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J48" s="4" t="str">
+        <f aca="false">IF(B48="","",IF(I48="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="str">
@@ -2522,27 +2102,19 @@
         <v/>
       </c>
       <c r="G49" s="8"/>
-      <c r="H49" s="4" t="str">
-        <f aca="false">IF(G49="","",DATEDIF(G49,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="11" t="str">
-        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",Сводка!$C$4-L49)</f>
-        <v/>
-      </c>
-      <c r="N49" s="4" t="str">
-        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",IF(L49&gt;=Сводка!$C$4,"Оплачено",IF(L49&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O49" s="4" t="str">
-        <f aca="false">IF(B49="","",IF(AND(LEN(I49)=12,J49="Да",K49="Да",N49="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P49" s="5"/>
+      <c r="H49" s="9" t="str">
+        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",Сводка!$C$4-G49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="4" t="str">
+        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",IF(G49&gt;=Сводка!$C$4,"Оплачено",IF(G49&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J49" s="4" t="str">
+        <f aca="false">IF(B49="","",IF(I49="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="str">
@@ -2558,27 +2130,19 @@
         <v/>
       </c>
       <c r="G50" s="8"/>
-      <c r="H50" s="4" t="str">
-        <f aca="false">IF(G50="","",DATEDIF(G50,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="11" t="str">
-        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",Сводка!$C$4-L50)</f>
-        <v/>
-      </c>
-      <c r="N50" s="4" t="str">
-        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",IF(L50&gt;=Сводка!$C$4,"Оплачено",IF(L50&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O50" s="4" t="str">
-        <f aca="false">IF(B50="","",IF(AND(LEN(I50)=12,J50="Да",K50="Да",N50="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P50" s="5"/>
+      <c r="H50" s="9" t="str">
+        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",Сводка!$C$4-G50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="4" t="str">
+        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",IF(G50&gt;=Сводка!$C$4,"Оплачено",IF(G50&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J50" s="4" t="str">
+        <f aca="false">IF(B50="","",IF(I50="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="str">
@@ -2594,27 +2158,19 @@
         <v/>
       </c>
       <c r="G51" s="8"/>
-      <c r="H51" s="4" t="str">
-        <f aca="false">IF(G51="","",DATEDIF(G51,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="11" t="str">
-        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",Сводка!$C$4-L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="4" t="str">
-        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",IF(L51&gt;=Сводка!$C$4,"Оплачено",IF(L51&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O51" s="4" t="str">
-        <f aca="false">IF(B51="","",IF(AND(LEN(I51)=12,J51="Да",K51="Да",N51="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P51" s="5"/>
+      <c r="H51" s="9" t="str">
+        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",Сводка!$C$4-G51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="4" t="str">
+        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",IF(G51&gt;=Сводка!$C$4,"Оплачено",IF(G51&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J51" s="4" t="str">
+        <f aca="false">IF(B51="","",IF(I51="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="str">
@@ -2630,27 +2186,19 @@
         <v/>
       </c>
       <c r="G52" s="8"/>
-      <c r="H52" s="4" t="str">
-        <f aca="false">IF(G52="","",DATEDIF(G52,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="11" t="str">
-        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",Сводка!$C$4-L52)</f>
-        <v/>
-      </c>
-      <c r="N52" s="4" t="str">
-        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",IF(L52&gt;=Сводка!$C$4,"Оплачено",IF(L52&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O52" s="4" t="str">
-        <f aca="false">IF(B52="","",IF(AND(LEN(I52)=12,J52="Да",K52="Да",N52="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P52" s="5"/>
+      <c r="H52" s="9" t="str">
+        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",Сводка!$C$4-G52)</f>
+        <v/>
+      </c>
+      <c r="I52" s="4" t="str">
+        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",IF(G52&gt;=Сводка!$C$4,"Оплачено",IF(G52&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J52" s="4" t="str">
+        <f aca="false">IF(B52="","",IF(I52="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="str">
@@ -2666,27 +2214,19 @@
         <v/>
       </c>
       <c r="G53" s="8"/>
-      <c r="H53" s="4" t="str">
-        <f aca="false">IF(G53="","",DATEDIF(G53,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="11" t="str">
-        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",Сводка!$C$4-L53)</f>
-        <v/>
-      </c>
-      <c r="N53" s="4" t="str">
-        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",IF(L53&gt;=Сводка!$C$4,"Оплачено",IF(L53&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O53" s="4" t="str">
-        <f aca="false">IF(B53="","",IF(AND(LEN(I53)=12,J53="Да",K53="Да",N53="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P53" s="5"/>
+      <c r="H53" s="9" t="str">
+        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",Сводка!$C$4-G53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="4" t="str">
+        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",IF(G53&gt;=Сводка!$C$4,"Оплачено",IF(G53&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J53" s="4" t="str">
+        <f aca="false">IF(B53="","",IF(I53="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="str">
@@ -2702,27 +2242,19 @@
         <v/>
       </c>
       <c r="G54" s="8"/>
-      <c r="H54" s="4" t="str">
-        <f aca="false">IF(G54="","",DATEDIF(G54,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="11" t="str">
-        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",Сводка!$C$4-L54)</f>
-        <v/>
-      </c>
-      <c r="N54" s="4" t="str">
-        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",IF(L54&gt;=Сводка!$C$4,"Оплачено",IF(L54&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O54" s="4" t="str">
-        <f aca="false">IF(B54="","",IF(AND(LEN(I54)=12,J54="Да",K54="Да",N54="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P54" s="5"/>
+      <c r="H54" s="9" t="str">
+        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",Сводка!$C$4-G54)</f>
+        <v/>
+      </c>
+      <c r="I54" s="4" t="str">
+        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",IF(G54&gt;=Сводка!$C$4,"Оплачено",IF(G54&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J54" s="4" t="str">
+        <f aca="false">IF(B54="","",IF(I54="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="str">
@@ -2738,27 +2270,19 @@
         <v/>
       </c>
       <c r="G55" s="8"/>
-      <c r="H55" s="4" t="str">
-        <f aca="false">IF(G55="","",DATEDIF(G55,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I55" s="9"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="11" t="str">
-        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",Сводка!$C$4-L55)</f>
-        <v/>
-      </c>
-      <c r="N55" s="4" t="str">
-        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",IF(L55&gt;=Сводка!$C$4,"Оплачено",IF(L55&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O55" s="4" t="str">
-        <f aca="false">IF(B55="","",IF(AND(LEN(I55)=12,J55="Да",K55="Да",N55="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P55" s="5"/>
+      <c r="H55" s="9" t="str">
+        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",Сводка!$C$4-G55)</f>
+        <v/>
+      </c>
+      <c r="I55" s="4" t="str">
+        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",IF(G55&gt;=Сводка!$C$4,"Оплачено",IF(G55&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J55" s="4" t="str">
+        <f aca="false">IF(B55="","",IF(I55="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="str">
@@ -2774,27 +2298,19 @@
         <v/>
       </c>
       <c r="G56" s="8"/>
-      <c r="H56" s="4" t="str">
-        <f aca="false">IF(G56="","",DATEDIF(G56,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="11" t="str">
-        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",Сводка!$C$4-L56)</f>
-        <v/>
-      </c>
-      <c r="N56" s="4" t="str">
-        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",IF(L56&gt;=Сводка!$C$4,"Оплачено",IF(L56&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O56" s="4" t="str">
-        <f aca="false">IF(B56="","",IF(AND(LEN(I56)=12,J56="Да",K56="Да",N56="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P56" s="5"/>
+      <c r="H56" s="9" t="str">
+        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",Сводка!$C$4-G56)</f>
+        <v/>
+      </c>
+      <c r="I56" s="4" t="str">
+        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",IF(G56&gt;=Сводка!$C$4,"Оплачено",IF(G56&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J56" s="4" t="str">
+        <f aca="false">IF(B56="","",IF(I56="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="str">
@@ -2810,27 +2326,19 @@
         <v/>
       </c>
       <c r="G57" s="8"/>
-      <c r="H57" s="4" t="str">
-        <f aca="false">IF(G57="","",DATEDIF(G57,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="11" t="str">
-        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",Сводка!$C$4-L57)</f>
-        <v/>
-      </c>
-      <c r="N57" s="4" t="str">
-        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",IF(L57&gt;=Сводка!$C$4,"Оплачено",IF(L57&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O57" s="4" t="str">
-        <f aca="false">IF(B57="","",IF(AND(LEN(I57)=12,J57="Да",K57="Да",N57="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P57" s="5"/>
+      <c r="H57" s="9" t="str">
+        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",Сводка!$C$4-G57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="4" t="str">
+        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",IF(G57&gt;=Сводка!$C$4,"Оплачено",IF(G57&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J57" s="4" t="str">
+        <f aca="false">IF(B57="","",IF(I57="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="str">
@@ -2846,27 +2354,19 @@
         <v/>
       </c>
       <c r="G58" s="8"/>
-      <c r="H58" s="4" t="str">
-        <f aca="false">IF(G58="","",DATEDIF(G58,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I58" s="9"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="11" t="str">
-        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",Сводка!$C$4-L58)</f>
-        <v/>
-      </c>
-      <c r="N58" s="4" t="str">
-        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",IF(L58&gt;=Сводка!$C$4,"Оплачено",IF(L58&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O58" s="4" t="str">
-        <f aca="false">IF(B58="","",IF(AND(LEN(I58)=12,J58="Да",K58="Да",N58="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P58" s="5"/>
+      <c r="H58" s="9" t="str">
+        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",Сводка!$C$4-G58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="4" t="str">
+        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",IF(G58&gt;=Сводка!$C$4,"Оплачено",IF(G58&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J58" s="4" t="str">
+        <f aca="false">IF(B58="","",IF(I58="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="str">
@@ -2882,27 +2382,19 @@
         <v/>
       </c>
       <c r="G59" s="8"/>
-      <c r="H59" s="4" t="str">
-        <f aca="false">IF(G59="","",DATEDIF(G59,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I59" s="9"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="11" t="str">
-        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",Сводка!$C$4-L59)</f>
-        <v/>
-      </c>
-      <c r="N59" s="4" t="str">
-        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",IF(L59&gt;=Сводка!$C$4,"Оплачено",IF(L59&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O59" s="4" t="str">
-        <f aca="false">IF(B59="","",IF(AND(LEN(I59)=12,J59="Да",K59="Да",N59="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P59" s="5"/>
+      <c r="H59" s="9" t="str">
+        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",Сводка!$C$4-G59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="4" t="str">
+        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",IF(G59&gt;=Сводка!$C$4,"Оплачено",IF(G59&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J59" s="4" t="str">
+        <f aca="false">IF(B59="","",IF(I59="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="str">
@@ -2918,27 +2410,19 @@
         <v/>
       </c>
       <c r="G60" s="8"/>
-      <c r="H60" s="4" t="str">
-        <f aca="false">IF(G60="","",DATEDIF(G60,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I60" s="9"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="11" t="str">
-        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",Сводка!$C$4-L60)</f>
-        <v/>
-      </c>
-      <c r="N60" s="4" t="str">
-        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",IF(L60&gt;=Сводка!$C$4,"Оплачено",IF(L60&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O60" s="4" t="str">
-        <f aca="false">IF(B60="","",IF(AND(LEN(I60)=12,J60="Да",K60="Да",N60="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P60" s="5"/>
+      <c r="H60" s="9" t="str">
+        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",Сводка!$C$4-G60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="4" t="str">
+        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",IF(G60&gt;=Сводка!$C$4,"Оплачено",IF(G60&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J60" s="4" t="str">
+        <f aca="false">IF(B60="","",IF(I60="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="str">
@@ -2954,27 +2438,19 @@
         <v/>
       </c>
       <c r="G61" s="8"/>
-      <c r="H61" s="4" t="str">
-        <f aca="false">IF(G61="","",DATEDIF(G61,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I61" s="9"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="11" t="str">
-        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",Сводка!$C$4-L61)</f>
-        <v/>
-      </c>
-      <c r="N61" s="4" t="str">
-        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",IF(L61&gt;=Сводка!$C$4,"Оплачено",IF(L61&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O61" s="4" t="str">
-        <f aca="false">IF(B61="","",IF(AND(LEN(I61)=12,J61="Да",K61="Да",N61="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P61" s="5"/>
+      <c r="H61" s="9" t="str">
+        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",Сводка!$C$4-G61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="4" t="str">
+        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",IF(G61&gt;=Сводка!$C$4,"Оплачено",IF(G61&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J61" s="4" t="str">
+        <f aca="false">IF(B61="","",IF(I61="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="str">
@@ -2990,27 +2466,19 @@
         <v/>
       </c>
       <c r="G62" s="8"/>
-      <c r="H62" s="4" t="str">
-        <f aca="false">IF(G62="","",DATEDIF(G62,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I62" s="9"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="11" t="str">
-        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",Сводка!$C$4-L62)</f>
-        <v/>
-      </c>
-      <c r="N62" s="4" t="str">
-        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",IF(L62&gt;=Сводка!$C$4,"Оплачено",IF(L62&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O62" s="4" t="str">
-        <f aca="false">IF(B62="","",IF(AND(LEN(I62)=12,J62="Да",K62="Да",N62="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P62" s="5"/>
+      <c r="H62" s="9" t="str">
+        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",Сводка!$C$4-G62)</f>
+        <v/>
+      </c>
+      <c r="I62" s="4" t="str">
+        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",IF(G62&gt;=Сводка!$C$4,"Оплачено",IF(G62&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J62" s="4" t="str">
+        <f aca="false">IF(B62="","",IF(I62="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="str">
@@ -3026,27 +2494,19 @@
         <v/>
       </c>
       <c r="G63" s="8"/>
-      <c r="H63" s="4" t="str">
-        <f aca="false">IF(G63="","",DATEDIF(G63,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="11" t="str">
-        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",Сводка!$C$4-L63)</f>
-        <v/>
-      </c>
-      <c r="N63" s="4" t="str">
-        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",IF(L63&gt;=Сводка!$C$4,"Оплачено",IF(L63&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O63" s="4" t="str">
-        <f aca="false">IF(B63="","",IF(AND(LEN(I63)=12,J63="Да",K63="Да",N63="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P63" s="5"/>
+      <c r="H63" s="9" t="str">
+        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",Сводка!$C$4-G63)</f>
+        <v/>
+      </c>
+      <c r="I63" s="4" t="str">
+        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",IF(G63&gt;=Сводка!$C$4,"Оплачено",IF(G63&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J63" s="4" t="str">
+        <f aca="false">IF(B63="","",IF(I63="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="str">
@@ -3062,27 +2522,19 @@
         <v/>
       </c>
       <c r="G64" s="8"/>
-      <c r="H64" s="4" t="str">
-        <f aca="false">IF(G64="","",DATEDIF(G64,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I64" s="9"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="11" t="str">
-        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",Сводка!$C$4-L64)</f>
-        <v/>
-      </c>
-      <c r="N64" s="4" t="str">
-        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",IF(L64&gt;=Сводка!$C$4,"Оплачено",IF(L64&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O64" s="4" t="str">
-        <f aca="false">IF(B64="","",IF(AND(LEN(I64)=12,J64="Да",K64="Да",N64="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P64" s="5"/>
+      <c r="H64" s="9" t="str">
+        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",Сводка!$C$4-G64)</f>
+        <v/>
+      </c>
+      <c r="I64" s="4" t="str">
+        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",IF(G64&gt;=Сводка!$C$4,"Оплачено",IF(G64&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J64" s="4" t="str">
+        <f aca="false">IF(B64="","",IF(I64="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="str">
@@ -3098,27 +2550,19 @@
         <v/>
       </c>
       <c r="G65" s="8"/>
-      <c r="H65" s="4" t="str">
-        <f aca="false">IF(G65="","",DATEDIF(G65,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I65" s="9"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="11" t="str">
-        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",Сводка!$C$4-L65)</f>
-        <v/>
-      </c>
-      <c r="N65" s="4" t="str">
-        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",IF(L65&gt;=Сводка!$C$4,"Оплачено",IF(L65&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O65" s="4" t="str">
-        <f aca="false">IF(B65="","",IF(AND(LEN(I65)=12,J65="Да",K65="Да",N65="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P65" s="5"/>
+      <c r="H65" s="9" t="str">
+        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",Сводка!$C$4-G65)</f>
+        <v/>
+      </c>
+      <c r="I65" s="4" t="str">
+        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",IF(G65&gt;=Сводка!$C$4,"Оплачено",IF(G65&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J65" s="4" t="str">
+        <f aca="false">IF(B65="","",IF(I65="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="str">
@@ -3134,27 +2578,19 @@
         <v/>
       </c>
       <c r="G66" s="8"/>
-      <c r="H66" s="4" t="str">
-        <f aca="false">IF(G66="","",DATEDIF(G66,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="11" t="str">
-        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",Сводка!$C$4-L66)</f>
-        <v/>
-      </c>
-      <c r="N66" s="4" t="str">
-        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",IF(L66&gt;=Сводка!$C$4,"Оплачено",IF(L66&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O66" s="4" t="str">
-        <f aca="false">IF(B66="","",IF(AND(LEN(I66)=12,J66="Да",K66="Да",N66="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P66" s="5"/>
+      <c r="H66" s="9" t="str">
+        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",Сводка!$C$4-G66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="4" t="str">
+        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",IF(G66&gt;=Сводка!$C$4,"Оплачено",IF(G66&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J66" s="4" t="str">
+        <f aca="false">IF(B66="","",IF(I66="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="str">
@@ -3170,27 +2606,19 @@
         <v/>
       </c>
       <c r="G67" s="8"/>
-      <c r="H67" s="4" t="str">
-        <f aca="false">IF(G67="","",DATEDIF(G67,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I67" s="9"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="11" t="str">
-        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",Сводка!$C$4-L67)</f>
-        <v/>
-      </c>
-      <c r="N67" s="4" t="str">
-        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",IF(L67&gt;=Сводка!$C$4,"Оплачено",IF(L67&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O67" s="4" t="str">
-        <f aca="false">IF(B67="","",IF(AND(LEN(I67)=12,J67="Да",K67="Да",N67="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P67" s="5"/>
+      <c r="H67" s="9" t="str">
+        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",Сводка!$C$4-G67)</f>
+        <v/>
+      </c>
+      <c r="I67" s="4" t="str">
+        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",IF(G67&gt;=Сводка!$C$4,"Оплачено",IF(G67&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J67" s="4" t="str">
+        <f aca="false">IF(B67="","",IF(I67="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="str">
@@ -3206,27 +2634,19 @@
         <v/>
       </c>
       <c r="G68" s="8"/>
-      <c r="H68" s="4" t="str">
-        <f aca="false">IF(G68="","",DATEDIF(G68,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I68" s="9"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="11" t="str">
-        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",Сводка!$C$4-L68)</f>
-        <v/>
-      </c>
-      <c r="N68" s="4" t="str">
-        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",IF(L68&gt;=Сводка!$C$4,"Оплачено",IF(L68&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O68" s="4" t="str">
-        <f aca="false">IF(B68="","",IF(AND(LEN(I68)=12,J68="Да",K68="Да",N68="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P68" s="5"/>
+      <c r="H68" s="9" t="str">
+        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",Сводка!$C$4-G68)</f>
+        <v/>
+      </c>
+      <c r="I68" s="4" t="str">
+        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",IF(G68&gt;=Сводка!$C$4,"Оплачено",IF(G68&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J68" s="4" t="str">
+        <f aca="false">IF(B68="","",IF(I68="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="str">
@@ -3242,27 +2662,19 @@
         <v/>
       </c>
       <c r="G69" s="8"/>
-      <c r="H69" s="4" t="str">
-        <f aca="false">IF(G69="","",DATEDIF(G69,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I69" s="9"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="11" t="str">
-        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",Сводка!$C$4-L69)</f>
-        <v/>
-      </c>
-      <c r="N69" s="4" t="str">
-        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",IF(L69&gt;=Сводка!$C$4,"Оплачено",IF(L69&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O69" s="4" t="str">
-        <f aca="false">IF(B69="","",IF(AND(LEN(I69)=12,J69="Да",K69="Да",N69="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P69" s="5"/>
+      <c r="H69" s="9" t="str">
+        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",Сводка!$C$4-G69)</f>
+        <v/>
+      </c>
+      <c r="I69" s="4" t="str">
+        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",IF(G69&gt;=Сводка!$C$4,"Оплачено",IF(G69&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J69" s="4" t="str">
+        <f aca="false">IF(B69="","",IF(I69="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="str">
@@ -3278,27 +2690,19 @@
         <v/>
       </c>
       <c r="G70" s="8"/>
-      <c r="H70" s="4" t="str">
-        <f aca="false">IF(G70="","",DATEDIF(G70,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I70" s="9"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="11" t="str">
-        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",Сводка!$C$4-L70)</f>
-        <v/>
-      </c>
-      <c r="N70" s="4" t="str">
-        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",IF(L70&gt;=Сводка!$C$4,"Оплачено",IF(L70&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O70" s="4" t="str">
-        <f aca="false">IF(B70="","",IF(AND(LEN(I70)=12,J70="Да",K70="Да",N70="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P70" s="5"/>
+      <c r="H70" s="9" t="str">
+        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",Сводка!$C$4-G70)</f>
+        <v/>
+      </c>
+      <c r="I70" s="4" t="str">
+        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",IF(G70&gt;=Сводка!$C$4,"Оплачено",IF(G70&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J70" s="4" t="str">
+        <f aca="false">IF(B70="","",IF(I70="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="str">
@@ -3314,27 +2718,19 @@
         <v/>
       </c>
       <c r="G71" s="8"/>
-      <c r="H71" s="4" t="str">
-        <f aca="false">IF(G71="","",DATEDIF(G71,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I71" s="9"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="11" t="str">
-        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",Сводка!$C$4-L71)</f>
-        <v/>
-      </c>
-      <c r="N71" s="4" t="str">
-        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",IF(L71&gt;=Сводка!$C$4,"Оплачено",IF(L71&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O71" s="4" t="str">
-        <f aca="false">IF(B71="","",IF(AND(LEN(I71)=12,J71="Да",K71="Да",N71="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P71" s="5"/>
+      <c r="H71" s="9" t="str">
+        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",Сводка!$C$4-G71)</f>
+        <v/>
+      </c>
+      <c r="I71" s="4" t="str">
+        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",IF(G71&gt;=Сводка!$C$4,"Оплачено",IF(G71&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J71" s="4" t="str">
+        <f aca="false">IF(B71="","",IF(I71="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="str">
@@ -3350,27 +2746,19 @@
         <v/>
       </c>
       <c r="G72" s="8"/>
-      <c r="H72" s="4" t="str">
-        <f aca="false">IF(G72="","",DATEDIF(G72,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="11" t="str">
-        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",Сводка!$C$4-L72)</f>
-        <v/>
-      </c>
-      <c r="N72" s="4" t="str">
-        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",IF(L72&gt;=Сводка!$C$4,"Оплачено",IF(L72&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O72" s="4" t="str">
-        <f aca="false">IF(B72="","",IF(AND(LEN(I72)=12,J72="Да",K72="Да",N72="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P72" s="5"/>
+      <c r="H72" s="9" t="str">
+        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",Сводка!$C$4-G72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="4" t="str">
+        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",IF(G72&gt;=Сводка!$C$4,"Оплачено",IF(G72&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J72" s="4" t="str">
+        <f aca="false">IF(B72="","",IF(I72="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="str">
@@ -3386,27 +2774,19 @@
         <v/>
       </c>
       <c r="G73" s="8"/>
-      <c r="H73" s="4" t="str">
-        <f aca="false">IF(G73="","",DATEDIF(G73,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="11" t="str">
-        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",Сводка!$C$4-L73)</f>
-        <v/>
-      </c>
-      <c r="N73" s="4" t="str">
-        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",IF(L73&gt;=Сводка!$C$4,"Оплачено",IF(L73&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O73" s="4" t="str">
-        <f aca="false">IF(B73="","",IF(AND(LEN(I73)=12,J73="Да",K73="Да",N73="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P73" s="5"/>
+      <c r="H73" s="9" t="str">
+        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",Сводка!$C$4-G73)</f>
+        <v/>
+      </c>
+      <c r="I73" s="4" t="str">
+        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",IF(G73&gt;=Сводка!$C$4,"Оплачено",IF(G73&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J73" s="4" t="str">
+        <f aca="false">IF(B73="","",IF(I73="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="str">
@@ -3422,27 +2802,19 @@
         <v/>
       </c>
       <c r="G74" s="8"/>
-      <c r="H74" s="4" t="str">
-        <f aca="false">IF(G74="","",DATEDIF(G74,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I74" s="9"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="11" t="str">
-        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",Сводка!$C$4-L74)</f>
-        <v/>
-      </c>
-      <c r="N74" s="4" t="str">
-        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",IF(L74&gt;=Сводка!$C$4,"Оплачено",IF(L74&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O74" s="4" t="str">
-        <f aca="false">IF(B74="","",IF(AND(LEN(I74)=12,J74="Да",K74="Да",N74="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P74" s="5"/>
+      <c r="H74" s="9" t="str">
+        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",Сводка!$C$4-G74)</f>
+        <v/>
+      </c>
+      <c r="I74" s="4" t="str">
+        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",IF(G74&gt;=Сводка!$C$4,"Оплачено",IF(G74&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J74" s="4" t="str">
+        <f aca="false">IF(B74="","",IF(I74="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="str">
@@ -3458,27 +2830,19 @@
         <v/>
       </c>
       <c r="G75" s="8"/>
-      <c r="H75" s="4" t="str">
-        <f aca="false">IF(G75="","",DATEDIF(G75,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I75" s="9"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="11" t="str">
-        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",Сводка!$C$4-L75)</f>
-        <v/>
-      </c>
-      <c r="N75" s="4" t="str">
-        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",IF(L75&gt;=Сводка!$C$4,"Оплачено",IF(L75&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O75" s="4" t="str">
-        <f aca="false">IF(B75="","",IF(AND(LEN(I75)=12,J75="Да",K75="Да",N75="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P75" s="5"/>
+      <c r="H75" s="9" t="str">
+        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",Сводка!$C$4-G75)</f>
+        <v/>
+      </c>
+      <c r="I75" s="4" t="str">
+        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",IF(G75&gt;=Сводка!$C$4,"Оплачено",IF(G75&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J75" s="4" t="str">
+        <f aca="false">IF(B75="","",IF(I75="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="str">
@@ -3494,27 +2858,19 @@
         <v/>
       </c>
       <c r="G76" s="8"/>
-      <c r="H76" s="4" t="str">
-        <f aca="false">IF(G76="","",DATEDIF(G76,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I76" s="9"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="11" t="str">
-        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",Сводка!$C$4-L76)</f>
-        <v/>
-      </c>
-      <c r="N76" s="4" t="str">
-        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",IF(L76&gt;=Сводка!$C$4,"Оплачено",IF(L76&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O76" s="4" t="str">
-        <f aca="false">IF(B76="","",IF(AND(LEN(I76)=12,J76="Да",K76="Да",N76="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P76" s="5"/>
+      <c r="H76" s="9" t="str">
+        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",Сводка!$C$4-G76)</f>
+        <v/>
+      </c>
+      <c r="I76" s="4" t="str">
+        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",IF(G76&gt;=Сводка!$C$4,"Оплачено",IF(G76&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J76" s="4" t="str">
+        <f aca="false">IF(B76="","",IF(I76="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="str">
@@ -3530,27 +2886,19 @@
         <v/>
       </c>
       <c r="G77" s="8"/>
-      <c r="H77" s="4" t="str">
-        <f aca="false">IF(G77="","",DATEDIF(G77,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I77" s="9"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="11" t="str">
-        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",Сводка!$C$4-L77)</f>
-        <v/>
-      </c>
-      <c r="N77" s="4" t="str">
-        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",IF(L77&gt;=Сводка!$C$4,"Оплачено",IF(L77&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O77" s="4" t="str">
-        <f aca="false">IF(B77="","",IF(AND(LEN(I77)=12,J77="Да",K77="Да",N77="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P77" s="5"/>
+      <c r="H77" s="9" t="str">
+        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",Сводка!$C$4-G77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="4" t="str">
+        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",IF(G77&gt;=Сводка!$C$4,"Оплачено",IF(G77&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J77" s="4" t="str">
+        <f aca="false">IF(B77="","",IF(I77="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="str">
@@ -3566,27 +2914,19 @@
         <v/>
       </c>
       <c r="G78" s="8"/>
-      <c r="H78" s="4" t="str">
-        <f aca="false">IF(G78="","",DATEDIF(G78,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="11" t="str">
-        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",Сводка!$C$4-L78)</f>
-        <v/>
-      </c>
-      <c r="N78" s="4" t="str">
-        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",IF(L78&gt;=Сводка!$C$4,"Оплачено",IF(L78&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O78" s="4" t="str">
-        <f aca="false">IF(B78="","",IF(AND(LEN(I78)=12,J78="Да",K78="Да",N78="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P78" s="5"/>
+      <c r="H78" s="9" t="str">
+        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",Сводка!$C$4-G78)</f>
+        <v/>
+      </c>
+      <c r="I78" s="4" t="str">
+        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",IF(G78&gt;=Сводка!$C$4,"Оплачено",IF(G78&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J78" s="4" t="str">
+        <f aca="false">IF(B78="","",IF(I78="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="str">
@@ -3602,27 +2942,19 @@
         <v/>
       </c>
       <c r="G79" s="8"/>
-      <c r="H79" s="4" t="str">
-        <f aca="false">IF(G79="","",DATEDIF(G79,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="11" t="str">
-        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",Сводка!$C$4-L79)</f>
-        <v/>
-      </c>
-      <c r="N79" s="4" t="str">
-        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",IF(L79&gt;=Сводка!$C$4,"Оплачено",IF(L79&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O79" s="4" t="str">
-        <f aca="false">IF(B79="","",IF(AND(LEN(I79)=12,J79="Да",K79="Да",N79="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P79" s="5"/>
+      <c r="H79" s="9" t="str">
+        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",Сводка!$C$4-G79)</f>
+        <v/>
+      </c>
+      <c r="I79" s="4" t="str">
+        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",IF(G79&gt;=Сводка!$C$4,"Оплачено",IF(G79&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="4" t="str">
+        <f aca="false">IF(B79="","",IF(I79="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="str">
@@ -3638,27 +2970,19 @@
         <v/>
       </c>
       <c r="G80" s="8"/>
-      <c r="H80" s="4" t="str">
-        <f aca="false">IF(G80="","",DATEDIF(G80,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I80" s="9"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="11" t="str">
-        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",Сводка!$C$4-L80)</f>
-        <v/>
-      </c>
-      <c r="N80" s="4" t="str">
-        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",IF(L80&gt;=Сводка!$C$4,"Оплачено",IF(L80&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O80" s="4" t="str">
-        <f aca="false">IF(B80="","",IF(AND(LEN(I80)=12,J80="Да",K80="Да",N80="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P80" s="5"/>
+      <c r="H80" s="9" t="str">
+        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",Сводка!$C$4-G80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="4" t="str">
+        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",IF(G80&gt;=Сводка!$C$4,"Оплачено",IF(G80&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J80" s="4" t="str">
+        <f aca="false">IF(B80="","",IF(I80="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K80" s="5"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="str">
@@ -3674,27 +2998,19 @@
         <v/>
       </c>
       <c r="G81" s="8"/>
-      <c r="H81" s="4" t="str">
-        <f aca="false">IF(G81="","",DATEDIF(G81,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I81" s="9"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="11" t="str">
-        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",Сводка!$C$4-L81)</f>
-        <v/>
-      </c>
-      <c r="N81" s="4" t="str">
-        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",IF(L81&gt;=Сводка!$C$4,"Оплачено",IF(L81&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O81" s="4" t="str">
-        <f aca="false">IF(B81="","",IF(AND(LEN(I81)=12,J81="Да",K81="Да",N81="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P81" s="5"/>
+      <c r="H81" s="9" t="str">
+        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",Сводка!$C$4-G81)</f>
+        <v/>
+      </c>
+      <c r="I81" s="4" t="str">
+        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",IF(G81&gt;=Сводка!$C$4,"Оплачено",IF(G81&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J81" s="4" t="str">
+        <f aca="false">IF(B81="","",IF(I81="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="str">
@@ -3710,27 +3026,19 @@
         <v/>
       </c>
       <c r="G82" s="8"/>
-      <c r="H82" s="4" t="str">
-        <f aca="false">IF(G82="","",DATEDIF(G82,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I82" s="9"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="11" t="str">
-        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",Сводка!$C$4-L82)</f>
-        <v/>
-      </c>
-      <c r="N82" s="4" t="str">
-        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",IF(L82&gt;=Сводка!$C$4,"Оплачено",IF(L82&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O82" s="4" t="str">
-        <f aca="false">IF(B82="","",IF(AND(LEN(I82)=12,J82="Да",K82="Да",N82="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P82" s="5"/>
+      <c r="H82" s="9" t="str">
+        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",Сводка!$C$4-G82)</f>
+        <v/>
+      </c>
+      <c r="I82" s="4" t="str">
+        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",IF(G82&gt;=Сводка!$C$4,"Оплачено",IF(G82&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="4" t="str">
+        <f aca="false">IF(B82="","",IF(I82="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="str">
@@ -3746,27 +3054,19 @@
         <v/>
       </c>
       <c r="G83" s="8"/>
-      <c r="H83" s="4" t="str">
-        <f aca="false">IF(G83="","",DATEDIF(G83,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I83" s="9"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="10"/>
-      <c r="M83" s="11" t="str">
-        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",Сводка!$C$4-L83)</f>
-        <v/>
-      </c>
-      <c r="N83" s="4" t="str">
-        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",IF(L83&gt;=Сводка!$C$4,"Оплачено",IF(L83&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O83" s="4" t="str">
-        <f aca="false">IF(B83="","",IF(AND(LEN(I83)=12,J83="Да",K83="Да",N83="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P83" s="5"/>
+      <c r="H83" s="9" t="str">
+        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",Сводка!$C$4-G83)</f>
+        <v/>
+      </c>
+      <c r="I83" s="4" t="str">
+        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",IF(G83&gt;=Сводка!$C$4,"Оплачено",IF(G83&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J83" s="4" t="str">
+        <f aca="false">IF(B83="","",IF(I83="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="str">
@@ -3782,27 +3082,19 @@
         <v/>
       </c>
       <c r="G84" s="8"/>
-      <c r="H84" s="4" t="str">
-        <f aca="false">IF(G84="","",DATEDIF(G84,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I84" s="9"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="10"/>
-      <c r="M84" s="11" t="str">
-        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",Сводка!$C$4-L84)</f>
-        <v/>
-      </c>
-      <c r="N84" s="4" t="str">
-        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",IF(L84&gt;=Сводка!$C$4,"Оплачено",IF(L84&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O84" s="4" t="str">
-        <f aca="false">IF(B84="","",IF(AND(LEN(I84)=12,J84="Да",K84="Да",N84="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P84" s="5"/>
+      <c r="H84" s="9" t="str">
+        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",Сводка!$C$4-G84)</f>
+        <v/>
+      </c>
+      <c r="I84" s="4" t="str">
+        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",IF(G84&gt;=Сводка!$C$4,"Оплачено",IF(G84&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J84" s="4" t="str">
+        <f aca="false">IF(B84="","",IF(I84="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="str">
@@ -3818,27 +3110,19 @@
         <v/>
       </c>
       <c r="G85" s="8"/>
-      <c r="H85" s="4" t="str">
-        <f aca="false">IF(G85="","",DATEDIF(G85,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I85" s="9"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="10"/>
-      <c r="M85" s="11" t="str">
-        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",Сводка!$C$4-L85)</f>
-        <v/>
-      </c>
-      <c r="N85" s="4" t="str">
-        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",IF(L85&gt;=Сводка!$C$4,"Оплачено",IF(L85&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O85" s="4" t="str">
-        <f aca="false">IF(B85="","",IF(AND(LEN(I85)=12,J85="Да",K85="Да",N85="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P85" s="5"/>
+      <c r="H85" s="9" t="str">
+        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",Сводка!$C$4-G85)</f>
+        <v/>
+      </c>
+      <c r="I85" s="4" t="str">
+        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",IF(G85&gt;=Сводка!$C$4,"Оплачено",IF(G85&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="4" t="str">
+        <f aca="false">IF(B85="","",IF(I85="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="str">
@@ -3854,27 +3138,19 @@
         <v/>
       </c>
       <c r="G86" s="8"/>
-      <c r="H86" s="4" t="str">
-        <f aca="false">IF(G86="","",DATEDIF(G86,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I86" s="9"/>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="10"/>
-      <c r="M86" s="11" t="str">
-        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",Сводка!$C$4-L86)</f>
-        <v/>
-      </c>
-      <c r="N86" s="4" t="str">
-        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",IF(L86&gt;=Сводка!$C$4,"Оплачено",IF(L86&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O86" s="4" t="str">
-        <f aca="false">IF(B86="","",IF(AND(LEN(I86)=12,J86="Да",K86="Да",N86="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P86" s="5"/>
+      <c r="H86" s="9" t="str">
+        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",Сводка!$C$4-G86)</f>
+        <v/>
+      </c>
+      <c r="I86" s="4" t="str">
+        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",IF(G86&gt;=Сводка!$C$4,"Оплачено",IF(G86&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="4" t="str">
+        <f aca="false">IF(B86="","",IF(I86="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="str">
@@ -3890,27 +3166,19 @@
         <v/>
       </c>
       <c r="G87" s="8"/>
-      <c r="H87" s="4" t="str">
-        <f aca="false">IF(G87="","",DATEDIF(G87,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I87" s="9"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="10"/>
-      <c r="M87" s="11" t="str">
-        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",Сводка!$C$4-L87)</f>
-        <v/>
-      </c>
-      <c r="N87" s="4" t="str">
-        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",IF(L87&gt;=Сводка!$C$4,"Оплачено",IF(L87&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O87" s="4" t="str">
-        <f aca="false">IF(B87="","",IF(AND(LEN(I87)=12,J87="Да",K87="Да",N87="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P87" s="5"/>
+      <c r="H87" s="9" t="str">
+        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",Сводка!$C$4-G87)</f>
+        <v/>
+      </c>
+      <c r="I87" s="4" t="str">
+        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",IF(G87&gt;=Сводка!$C$4,"Оплачено",IF(G87&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J87" s="4" t="str">
+        <f aca="false">IF(B87="","",IF(I87="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="str">
@@ -3926,27 +3194,19 @@
         <v/>
       </c>
       <c r="G88" s="8"/>
-      <c r="H88" s="4" t="str">
-        <f aca="false">IF(G88="","",DATEDIF(G88,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I88" s="9"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="11" t="str">
-        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",Сводка!$C$4-L88)</f>
-        <v/>
-      </c>
-      <c r="N88" s="4" t="str">
-        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",IF(L88&gt;=Сводка!$C$4,"Оплачено",IF(L88&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O88" s="4" t="str">
-        <f aca="false">IF(B88="","",IF(AND(LEN(I88)=12,J88="Да",K88="Да",N88="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P88" s="5"/>
+      <c r="H88" s="9" t="str">
+        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",Сводка!$C$4-G88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="4" t="str">
+        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",IF(G88&gt;=Сводка!$C$4,"Оплачено",IF(G88&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="4" t="str">
+        <f aca="false">IF(B88="","",IF(I88="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="str">
@@ -3962,27 +3222,19 @@
         <v/>
       </c>
       <c r="G89" s="8"/>
-      <c r="H89" s="4" t="str">
-        <f aca="false">IF(G89="","",DATEDIF(G89,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I89" s="9"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="10"/>
-      <c r="M89" s="11" t="str">
-        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",Сводка!$C$4-L89)</f>
-        <v/>
-      </c>
-      <c r="N89" s="4" t="str">
-        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",IF(L89&gt;=Сводка!$C$4,"Оплачено",IF(L89&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O89" s="4" t="str">
-        <f aca="false">IF(B89="","",IF(AND(LEN(I89)=12,J89="Да",K89="Да",N89="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P89" s="5"/>
+      <c r="H89" s="9" t="str">
+        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",Сводка!$C$4-G89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="4" t="str">
+        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",IF(G89&gt;=Сводка!$C$4,"Оплачено",IF(G89&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J89" s="4" t="str">
+        <f aca="false">IF(B89="","",IF(I89="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="str">
@@ -3998,27 +3250,19 @@
         <v/>
       </c>
       <c r="G90" s="8"/>
-      <c r="H90" s="4" t="str">
-        <f aca="false">IF(G90="","",DATEDIF(G90,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I90" s="9"/>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="10"/>
-      <c r="M90" s="11" t="str">
-        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",Сводка!$C$4-L90)</f>
-        <v/>
-      </c>
-      <c r="N90" s="4" t="str">
-        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",IF(L90&gt;=Сводка!$C$4,"Оплачено",IF(L90&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O90" s="4" t="str">
-        <f aca="false">IF(B90="","",IF(AND(LEN(I90)=12,J90="Да",K90="Да",N90="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P90" s="5"/>
+      <c r="H90" s="9" t="str">
+        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",Сводка!$C$4-G90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="4" t="str">
+        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",IF(G90&gt;=Сводка!$C$4,"Оплачено",IF(G90&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J90" s="4" t="str">
+        <f aca="false">IF(B90="","",IF(I90="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="str">
@@ -4034,27 +3278,19 @@
         <v/>
       </c>
       <c r="G91" s="8"/>
-      <c r="H91" s="4" t="str">
-        <f aca="false">IF(G91="","",DATEDIF(G91,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I91" s="9"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="11" t="str">
-        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",Сводка!$C$4-L91)</f>
-        <v/>
-      </c>
-      <c r="N91" s="4" t="str">
-        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",IF(L91&gt;=Сводка!$C$4,"Оплачено",IF(L91&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O91" s="4" t="str">
-        <f aca="false">IF(B91="","",IF(AND(LEN(I91)=12,J91="Да",K91="Да",N91="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P91" s="5"/>
+      <c r="H91" s="9" t="str">
+        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",Сводка!$C$4-G91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="4" t="str">
+        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",IF(G91&gt;=Сводка!$C$4,"Оплачено",IF(G91&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J91" s="4" t="str">
+        <f aca="false">IF(B91="","",IF(I91="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K91" s="5"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="str">
@@ -4070,27 +3306,19 @@
         <v/>
       </c>
       <c r="G92" s="8"/>
-      <c r="H92" s="4" t="str">
-        <f aca="false">IF(G92="","",DATEDIF(G92,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I92" s="9"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="11" t="str">
-        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",Сводка!$C$4-L92)</f>
-        <v/>
-      </c>
-      <c r="N92" s="4" t="str">
-        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",IF(L92&gt;=Сводка!$C$4,"Оплачено",IF(L92&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O92" s="4" t="str">
-        <f aca="false">IF(B92="","",IF(AND(LEN(I92)=12,J92="Да",K92="Да",N92="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P92" s="5"/>
+      <c r="H92" s="9" t="str">
+        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",Сводка!$C$4-G92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="4" t="str">
+        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",IF(G92&gt;=Сводка!$C$4,"Оплачено",IF(G92&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="4" t="str">
+        <f aca="false">IF(B92="","",IF(I92="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="str">
@@ -4106,27 +3334,19 @@
         <v/>
       </c>
       <c r="G93" s="8"/>
-      <c r="H93" s="4" t="str">
-        <f aca="false">IF(G93="","",DATEDIF(G93,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I93" s="9"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="11" t="str">
-        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",Сводка!$C$4-L93)</f>
-        <v/>
-      </c>
-      <c r="N93" s="4" t="str">
-        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",IF(L93&gt;=Сводка!$C$4,"Оплачено",IF(L93&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O93" s="4" t="str">
-        <f aca="false">IF(B93="","",IF(AND(LEN(I93)=12,J93="Да",K93="Да",N93="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P93" s="5"/>
+      <c r="H93" s="9" t="str">
+        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",Сводка!$C$4-G93)</f>
+        <v/>
+      </c>
+      <c r="I93" s="4" t="str">
+        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",IF(G93&gt;=Сводка!$C$4,"Оплачено",IF(G93&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J93" s="4" t="str">
+        <f aca="false">IF(B93="","",IF(I93="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K93" s="5"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="str">
@@ -4142,27 +3362,19 @@
         <v/>
       </c>
       <c r="G94" s="8"/>
-      <c r="H94" s="4" t="str">
-        <f aca="false">IF(G94="","",DATEDIF(G94,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I94" s="9"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="11" t="str">
-        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",Сводка!$C$4-L94)</f>
-        <v/>
-      </c>
-      <c r="N94" s="4" t="str">
-        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",IF(L94&gt;=Сводка!$C$4,"Оплачено",IF(L94&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O94" s="4" t="str">
-        <f aca="false">IF(B94="","",IF(AND(LEN(I94)=12,J94="Да",K94="Да",N94="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P94" s="5"/>
+      <c r="H94" s="9" t="str">
+        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",Сводка!$C$4-G94)</f>
+        <v/>
+      </c>
+      <c r="I94" s="4" t="str">
+        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",IF(G94&gt;=Сводка!$C$4,"Оплачено",IF(G94&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J94" s="4" t="str">
+        <f aca="false">IF(B94="","",IF(I94="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K94" s="5"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="str">
@@ -4178,27 +3390,19 @@
         <v/>
       </c>
       <c r="G95" s="8"/>
-      <c r="H95" s="4" t="str">
-        <f aca="false">IF(G95="","",DATEDIF(G95,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I95" s="9"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="10"/>
-      <c r="M95" s="11" t="str">
-        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",Сводка!$C$4-L95)</f>
-        <v/>
-      </c>
-      <c r="N95" s="4" t="str">
-        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",IF(L95&gt;=Сводка!$C$4,"Оплачено",IF(L95&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O95" s="4" t="str">
-        <f aca="false">IF(B95="","",IF(AND(LEN(I95)=12,J95="Да",K95="Да",N95="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P95" s="5"/>
+      <c r="H95" s="9" t="str">
+        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",Сводка!$C$4-G95)</f>
+        <v/>
+      </c>
+      <c r="I95" s="4" t="str">
+        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",IF(G95&gt;=Сводка!$C$4,"Оплачено",IF(G95&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J95" s="4" t="str">
+        <f aca="false">IF(B95="","",IF(I95="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="str">
@@ -4214,27 +3418,19 @@
         <v/>
       </c>
       <c r="G96" s="8"/>
-      <c r="H96" s="4" t="str">
-        <f aca="false">IF(G96="","",DATEDIF(G96,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I96" s="9"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="10"/>
-      <c r="M96" s="11" t="str">
-        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",Сводка!$C$4-L96)</f>
-        <v/>
-      </c>
-      <c r="N96" s="4" t="str">
-        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",IF(L96&gt;=Сводка!$C$4,"Оплачено",IF(L96&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O96" s="4" t="str">
-        <f aca="false">IF(B96="","",IF(AND(LEN(I96)=12,J96="Да",K96="Да",N96="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P96" s="5"/>
+      <c r="H96" s="9" t="str">
+        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",Сводка!$C$4-G96)</f>
+        <v/>
+      </c>
+      <c r="I96" s="4" t="str">
+        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",IF(G96&gt;=Сводка!$C$4,"Оплачено",IF(G96&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J96" s="4" t="str">
+        <f aca="false">IF(B96="","",IF(I96="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="str">
@@ -4250,27 +3446,19 @@
         <v/>
       </c>
       <c r="G97" s="8"/>
-      <c r="H97" s="4" t="str">
-        <f aca="false">IF(G97="","",DATEDIF(G97,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I97" s="9"/>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="10"/>
-      <c r="M97" s="11" t="str">
-        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",Сводка!$C$4-L97)</f>
-        <v/>
-      </c>
-      <c r="N97" s="4" t="str">
-        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",IF(L97&gt;=Сводка!$C$4,"Оплачено",IF(L97&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O97" s="4" t="str">
-        <f aca="false">IF(B97="","",IF(AND(LEN(I97)=12,J97="Да",K97="Да",N97="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P97" s="5"/>
+      <c r="H97" s="9" t="str">
+        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",Сводка!$C$4-G97)</f>
+        <v/>
+      </c>
+      <c r="I97" s="4" t="str">
+        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",IF(G97&gt;=Сводка!$C$4,"Оплачено",IF(G97&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J97" s="4" t="str">
+        <f aca="false">IF(B97="","",IF(I97="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K97" s="5"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="str">
@@ -4286,27 +3474,19 @@
         <v/>
       </c>
       <c r="G98" s="8"/>
-      <c r="H98" s="4" t="str">
-        <f aca="false">IF(G98="","",DATEDIF(G98,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I98" s="9"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="10"/>
-      <c r="M98" s="11" t="str">
-        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",Сводка!$C$4-L98)</f>
-        <v/>
-      </c>
-      <c r="N98" s="4" t="str">
-        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",IF(L98&gt;=Сводка!$C$4,"Оплачено",IF(L98&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O98" s="4" t="str">
-        <f aca="false">IF(B98="","",IF(AND(LEN(I98)=12,J98="Да",K98="Да",N98="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P98" s="5"/>
+      <c r="H98" s="9" t="str">
+        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",Сводка!$C$4-G98)</f>
+        <v/>
+      </c>
+      <c r="I98" s="4" t="str">
+        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",IF(G98&gt;=Сводка!$C$4,"Оплачено",IF(G98&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="4" t="str">
+        <f aca="false">IF(B98="","",IF(I98="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K98" s="5"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="str">
@@ -4322,27 +3502,19 @@
         <v/>
       </c>
       <c r="G99" s="8"/>
-      <c r="H99" s="4" t="str">
-        <f aca="false">IF(G99="","",DATEDIF(G99,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I99" s="9"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="10"/>
-      <c r="M99" s="11" t="str">
-        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",Сводка!$C$4-L99)</f>
-        <v/>
-      </c>
-      <c r="N99" s="4" t="str">
-        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",IF(L99&gt;=Сводка!$C$4,"Оплачено",IF(L99&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O99" s="4" t="str">
-        <f aca="false">IF(B99="","",IF(AND(LEN(I99)=12,J99="Да",K99="Да",N99="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P99" s="5"/>
+      <c r="H99" s="9" t="str">
+        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",Сводка!$C$4-G99)</f>
+        <v/>
+      </c>
+      <c r="I99" s="4" t="str">
+        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",IF(G99&gt;=Сводка!$C$4,"Оплачено",IF(G99&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J99" s="4" t="str">
+        <f aca="false">IF(B99="","",IF(I99="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="str">
@@ -4358,27 +3530,19 @@
         <v/>
       </c>
       <c r="G100" s="8"/>
-      <c r="H100" s="4" t="str">
-        <f aca="false">IF(G100="","",DATEDIF(G100,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I100" s="9"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="11" t="str">
-        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",Сводка!$C$4-L100)</f>
-        <v/>
-      </c>
-      <c r="N100" s="4" t="str">
-        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",IF(L100&gt;=Сводка!$C$4,"Оплачено",IF(L100&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O100" s="4" t="str">
-        <f aca="false">IF(B100="","",IF(AND(LEN(I100)=12,J100="Да",K100="Да",N100="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P100" s="5"/>
+      <c r="H100" s="9" t="str">
+        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",Сводка!$C$4-G100)</f>
+        <v/>
+      </c>
+      <c r="I100" s="4" t="str">
+        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",IF(G100&gt;=Сводка!$C$4,"Оплачено",IF(G100&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="4" t="str">
+        <f aca="false">IF(B100="","",IF(I100="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K100" s="5"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="str">
@@ -4394,27 +3558,19 @@
         <v/>
       </c>
       <c r="G101" s="8"/>
-      <c r="H101" s="4" t="str">
-        <f aca="false">IF(G101="","",DATEDIF(G101,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I101" s="9"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="11" t="str">
-        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",Сводка!$C$4-L101)</f>
-        <v/>
-      </c>
-      <c r="N101" s="4" t="str">
-        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",IF(L101&gt;=Сводка!$C$4,"Оплачено",IF(L101&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O101" s="4" t="str">
-        <f aca="false">IF(B101="","",IF(AND(LEN(I101)=12,J101="Да",K101="Да",N101="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P101" s="5"/>
+      <c r="H101" s="9" t="str">
+        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",Сводка!$C$4-G101)</f>
+        <v/>
+      </c>
+      <c r="I101" s="4" t="str">
+        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",IF(G101&gt;=Сводка!$C$4,"Оплачено",IF(G101&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J101" s="4" t="str">
+        <f aca="false">IF(B101="","",IF(I101="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K101" s="5"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="str">
@@ -4430,27 +3586,19 @@
         <v/>
       </c>
       <c r="G102" s="8"/>
-      <c r="H102" s="4" t="str">
-        <f aca="false">IF(G102="","",DATEDIF(G102,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I102" s="9"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="10"/>
-      <c r="M102" s="11" t="str">
-        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",Сводка!$C$4-L102)</f>
-        <v/>
-      </c>
-      <c r="N102" s="4" t="str">
-        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",IF(L102&gt;=Сводка!$C$4,"Оплачено",IF(L102&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O102" s="4" t="str">
-        <f aca="false">IF(B102="","",IF(AND(LEN(I102)=12,J102="Да",K102="Да",N102="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P102" s="5"/>
+      <c r="H102" s="9" t="str">
+        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",Сводка!$C$4-G102)</f>
+        <v/>
+      </c>
+      <c r="I102" s="4" t="str">
+        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",IF(G102&gt;=Сводка!$C$4,"Оплачено",IF(G102&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="4" t="str">
+        <f aca="false">IF(B102="","",IF(I102="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K102" s="5"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="str">
@@ -4466,27 +3614,19 @@
         <v/>
       </c>
       <c r="G103" s="8"/>
-      <c r="H103" s="4" t="str">
-        <f aca="false">IF(G103="","",DATEDIF(G103,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I103" s="9"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="10"/>
-      <c r="M103" s="11" t="str">
-        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",Сводка!$C$4-L103)</f>
-        <v/>
-      </c>
-      <c r="N103" s="4" t="str">
-        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",IF(L103&gt;=Сводка!$C$4,"Оплачено",IF(L103&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O103" s="4" t="str">
-        <f aca="false">IF(B103="","",IF(AND(LEN(I103)=12,J103="Да",K103="Да",N103="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P103" s="5"/>
+      <c r="H103" s="9" t="str">
+        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",Сводка!$C$4-G103)</f>
+        <v/>
+      </c>
+      <c r="I103" s="4" t="str">
+        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",IF(G103&gt;=Сводка!$C$4,"Оплачено",IF(G103&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J103" s="4" t="str">
+        <f aca="false">IF(B103="","",IF(I103="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K103" s="5"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="str">
@@ -4502,31 +3642,23 @@
         <v/>
       </c>
       <c r="G104" s="8"/>
-      <c r="H104" s="4" t="str">
-        <f aca="false">IF(G104="","",DATEDIF(G104,Сводка!$C$5,"Y"))</f>
-        <v/>
-      </c>
-      <c r="I104" s="9"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="11" t="str">
-        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",Сводка!$C$4-L104)</f>
-        <v/>
-      </c>
-      <c r="N104" s="4" t="str">
-        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",IF(L104&gt;=Сводка!$C$4,"Оплачено",IF(L104&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="O104" s="4" t="str">
-        <f aca="false">IF(B104="","",IF(AND(LEN(I104)=12,J104="Да",K104="Да",N104="Оплачено"),"Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="P104" s="5"/>
+      <c r="H104" s="9" t="str">
+        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",Сводка!$C$4-G104)</f>
+        <v/>
+      </c>
+      <c r="I104" s="4" t="str">
+        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",IF(G104&gt;=Сводка!$C$4,"Оплачено",IF(G104&gt;0,"Частично","Не оплачено")))</f>
+        <v/>
+      </c>
+      <c r="J104" s="4" t="str">
+        <f aca="false">IF(B104="","",IF(I104="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="K104" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P104"/>
-  <conditionalFormatting sqref="O5:O104">
+  <autoFilter ref="A4:K104"/>
+  <conditionalFormatting sqref="J5:J104">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Да"</formula>
     </cfRule>
@@ -4534,7 +3666,7 @@
       <formula>"Нет"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N104">
+  <conditionalFormatting sqref="I5:I104">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"Оплачено"</formula>
     </cfRule>
@@ -4545,20 +3677,8 @@
       <formula>"Не оплачено"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:K104" type="list">
-      <formula1>"Да,Нет"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="ИИН должен состоять из 12 цифр" errorStyle="stop" errorTitle="ИИН" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I5:I104" type="textLength">
-      <formula1>12</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Введите дату в формате ДД.ММ.ГГГГ" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G104" type="date">
-      <formula1>DATE(2005,1,1)</formula1>
-      <formula2>DATE(2016,12,31)</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L5:L104" type="decimal">
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G104" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4591,12 +3711,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4607,10 +3727,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4621,7 +3741,7 @@
         <v/>
       </c>
       <c r="E4" s="4" t="str">
-        <f aca="false">IF(B4="","",COUNTIFS(Ученики!$E$5:$E$104,B4,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B4="","",COUNTIFS(Ученики!$E$5:$E$104,B4,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4633,7 +3753,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <f aca="false">IF(B5="","",COUNTIFS(Ученики!$E$5:$E$104,B5,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B5="","",COUNTIFS(Ученики!$E$5:$E$104,B5,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4645,7 +3765,7 @@
         <v/>
       </c>
       <c r="E6" s="4" t="str">
-        <f aca="false">IF(B6="","",COUNTIFS(Ученики!$E$5:$E$104,B6,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B6="","",COUNTIFS(Ученики!$E$5:$E$104,B6,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4657,7 +3777,7 @@
         <v/>
       </c>
       <c r="E7" s="4" t="str">
-        <f aca="false">IF(B7="","",COUNTIFS(Ученики!$E$5:$E$104,B7,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B7="","",COUNTIFS(Ученики!$E$5:$E$104,B7,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4669,7 +3789,7 @@
         <v/>
       </c>
       <c r="E8" s="4" t="str">
-        <f aca="false">IF(B8="","",COUNTIFS(Ученики!$E$5:$E$104,B8,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B8="","",COUNTIFS(Ученики!$E$5:$E$104,B8,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4681,7 +3801,7 @@
         <v/>
       </c>
       <c r="E9" s="4" t="str">
-        <f aca="false">IF(B9="","",COUNTIFS(Ученики!$E$5:$E$104,B9,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B9="","",COUNTIFS(Ученики!$E$5:$E$104,B9,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4693,7 +3813,7 @@
         <v/>
       </c>
       <c r="E10" s="4" t="str">
-        <f aca="false">IF(B10="","",COUNTIFS(Ученики!$E$5:$E$104,B10,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B10="","",COUNTIFS(Ученики!$E$5:$E$104,B10,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4705,7 +3825,7 @@
         <v/>
       </c>
       <c r="E11" s="4" t="str">
-        <f aca="false">IF(B11="","",COUNTIFS(Ученики!$E$5:$E$104,B11,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B11="","",COUNTIFS(Ученики!$E$5:$E$104,B11,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4717,7 +3837,7 @@
         <v/>
       </c>
       <c r="E12" s="4" t="str">
-        <f aca="false">IF(B12="","",COUNTIFS(Ученики!$E$5:$E$104,B12,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B12="","",COUNTIFS(Ученики!$E$5:$E$104,B12,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4729,7 +3849,7 @@
         <v/>
       </c>
       <c r="E13" s="4" t="str">
-        <f aca="false">IF(B13="","",COUNTIFS(Ученики!$E$5:$E$104,B13,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B13="","",COUNTIFS(Ученики!$E$5:$E$104,B13,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4741,7 +3861,7 @@
         <v/>
       </c>
       <c r="E14" s="4" t="str">
-        <f aca="false">IF(B14="","",COUNTIFS(Ученики!$E$5:$E$104,B14,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B14="","",COUNTIFS(Ученики!$E$5:$E$104,B14,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4753,7 +3873,7 @@
         <v/>
       </c>
       <c r="E15" s="4" t="str">
-        <f aca="false">IF(B15="","",COUNTIFS(Ученики!$E$5:$E$104,B15,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B15="","",COUNTIFS(Ученики!$E$5:$E$104,B15,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4765,7 +3885,7 @@
         <v/>
       </c>
       <c r="E16" s="4" t="str">
-        <f aca="false">IF(B16="","",COUNTIFS(Ученики!$E$5:$E$104,B16,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B16="","",COUNTIFS(Ученики!$E$5:$E$104,B16,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4777,7 +3897,7 @@
         <v/>
       </c>
       <c r="E17" s="4" t="str">
-        <f aca="false">IF(B17="","",COUNTIFS(Ученики!$E$5:$E$104,B17,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B17="","",COUNTIFS(Ученики!$E$5:$E$104,B17,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4789,7 +3909,7 @@
         <v/>
       </c>
       <c r="E18" s="4" t="str">
-        <f aca="false">IF(B18="","",COUNTIFS(Ученики!$E$5:$E$104,B18,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B18="","",COUNTIFS(Ученики!$E$5:$E$104,B18,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4801,7 +3921,7 @@
         <v/>
       </c>
       <c r="E19" s="4" t="str">
-        <f aca="false">IF(B19="","",COUNTIFS(Ученики!$E$5:$E$104,B19,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B19="","",COUNTIFS(Ученики!$E$5:$E$104,B19,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4813,7 +3933,7 @@
         <v/>
       </c>
       <c r="E20" s="4" t="str">
-        <f aca="false">IF(B20="","",COUNTIFS(Ученики!$E$5:$E$104,B20,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B20="","",COUNTIFS(Ученики!$E$5:$E$104,B20,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4825,7 +3945,7 @@
         <v/>
       </c>
       <c r="E21" s="4" t="str">
-        <f aca="false">IF(B21="","",COUNTIFS(Ученики!$E$5:$E$104,B21,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B21="","",COUNTIFS(Ученики!$E$5:$E$104,B21,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4837,7 +3957,7 @@
         <v/>
       </c>
       <c r="E22" s="4" t="str">
-        <f aca="false">IF(B22="","",COUNTIFS(Ученики!$E$5:$E$104,B22,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B22="","",COUNTIFS(Ученики!$E$5:$E$104,B22,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4849,7 +3969,7 @@
         <v/>
       </c>
       <c r="E23" s="4" t="str">
-        <f aca="false">IF(B23="","",COUNTIFS(Ученики!$E$5:$E$104,B23,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B23="","",COUNTIFS(Ученики!$E$5:$E$104,B23,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4861,7 +3981,7 @@
         <v/>
       </c>
       <c r="E24" s="4" t="str">
-        <f aca="false">IF(B24="","",COUNTIFS(Ученики!$E$5:$E$104,B24,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B24="","",COUNTIFS(Ученики!$E$5:$E$104,B24,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4873,7 +3993,7 @@
         <v/>
       </c>
       <c r="E25" s="4" t="str">
-        <f aca="false">IF(B25="","",COUNTIFS(Ученики!$E$5:$E$104,B25,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B25="","",COUNTIFS(Ученики!$E$5:$E$104,B25,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4885,7 +4005,7 @@
         <v/>
       </c>
       <c r="E26" s="4" t="str">
-        <f aca="false">IF(B26="","",COUNTIFS(Ученики!$E$5:$E$104,B26,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B26="","",COUNTIFS(Ученики!$E$5:$E$104,B26,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4897,7 +4017,7 @@
         <v/>
       </c>
       <c r="E27" s="4" t="str">
-        <f aca="false">IF(B27="","",COUNTIFS(Ученики!$E$5:$E$104,B27,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B27="","",COUNTIFS(Ученики!$E$5:$E$104,B27,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4909,7 +4029,7 @@
         <v/>
       </c>
       <c r="E28" s="4" t="str">
-        <f aca="false">IF(B28="","",COUNTIFS(Ученики!$E$5:$E$104,B28,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B28="","",COUNTIFS(Ученики!$E$5:$E$104,B28,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4921,7 +4041,7 @@
         <v/>
       </c>
       <c r="E29" s="4" t="str">
-        <f aca="false">IF(B29="","",COUNTIFS(Ученики!$E$5:$E$104,B29,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B29="","",COUNTIFS(Ученики!$E$5:$E$104,B29,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4933,7 +4053,7 @@
         <v/>
       </c>
       <c r="E30" s="4" t="str">
-        <f aca="false">IF(B30="","",COUNTIFS(Ученики!$E$5:$E$104,B30,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B30="","",COUNTIFS(Ученики!$E$5:$E$104,B30,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4945,7 +4065,7 @@
         <v/>
       </c>
       <c r="E31" s="4" t="str">
-        <f aca="false">IF(B31="","",COUNTIFS(Ученики!$E$5:$E$104,B31,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B31="","",COUNTIFS(Ученики!$E$5:$E$104,B31,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4957,7 +4077,7 @@
         <v/>
       </c>
       <c r="E32" s="4" t="str">
-        <f aca="false">IF(B32="","",COUNTIFS(Ученики!$E$5:$E$104,B32,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B32="","",COUNTIFS(Ученики!$E$5:$E$104,B32,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4969,20 +4089,20 @@
         <v/>
       </c>
       <c r="E33" s="4" t="str">
-        <f aca="false">IF(B33="","",COUNTIFS(Ученики!$E$5:$E$104,B33,Ученики!$O$5:$O$104,"Да"))</f>
+        <f aca="false">IF(B33="","",COUNTIFS(Ученики!$E$5:$E$104,B33,Ученики!$J$5:$J$104,"Да"))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14" t="n">
+      <c r="B34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12" t="n">
         <f aca="false">SUM(D4:D33)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="12" t="n">
         <f aca="false">SUM(E4:E33)</f>
         <v>0</v>
       </c>
@@ -5003,7 +4123,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C19"/>
+  <dimension ref="B1:C17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -5013,126 +4133,108 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">COUNTA(Ученики!$B$5:$B$104)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Оплачено")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Частично")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Не оплачено")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <f aca="false">SUM(Ученики!$G$5:$G$104)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <f aca="false">C8*$C$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C14" s="18" t="n">
+        <f aca="false">C13-C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="17" t="n">
         <f aca="false">COUNTIF(Ученики!$J$5:$J$104,"Да")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="18" t="n">
-        <f aca="false">COUNTIF(Ученики!$K$5:$K$104,"Да")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="18" t="n">
-        <f aca="false">COUNTIF(Ученики!$N$5:$N$104,"Оплачено")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <f aca="false">COUNTIF(Ученики!$N$5:$N$104,"Частично")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="18" t="n">
-        <f aca="false">COUNTIF(Ученики!$N$5:$N$104,"Не оплачено")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <f aca="false">SUM(Ученики!$L$5:$L$104)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <f aca="false">C8*$C$4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <f aca="false">C15-C14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <f aca="false">COUNTIF(Ученики!$O$5:$O$104,"Да")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -5152,66 +4254,53 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>39</v>
+      <c r="A1" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>40</v>
+      <c r="A2" s="19" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="s">
-        <v>41</v>
+      <c r="A3" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>42</v>
+      <c r="A4" s="19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>43</v>
+      <c r="A5" s="19" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>44</v>
+      <c r="A6" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>45</v>
-      </c>
+      <c r="A7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>47</v>
+      <c r="A8" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,56 +4320,32 @@
         <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>39886</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="23" t="n">
+      <c r="A13" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="21" t="n">
         <v>45000</v>
       </c>
-      <c r="J13" s="21" t="s">
-        <v>56</v>
+      <c r="F13" s="20" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>57</v>
+      <c r="A15" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/trips/astana-2026-10/spisok_uchenikov_astana.xlsx
+++ b/trips/astana-2026-10/spisok_uchenikov_astana.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Ученики!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Ученики!$A$4:$K$104</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Ученики!$A$4:$M$104</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +32,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Впишите сумму, когда станет известна. От неё считаются остаток и статус оплаты.</t>
+          <t xml:space="preserve">Впишите цену каждого пакета. От неё считаются остаток и статус оплаты.</t>
         </r>
       </text>
     </comment>
@@ -49,12 +49,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t xml:space="preserve">Список учеников — поездка в Астану (университеты), 27–28 октября 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Жёлтые ячейки заполняются, серые считаются сами. Классные руководители — на листе «Классы», стоимость поездки — на листе «Сводка».</t>
+    <t xml:space="preserve">Жёлтые ячейки заполняются, серые считаются сами. Пакеты и их цены — на листе «Сводка», классные руководители — на листе «Классы».</t>
   </si>
   <si>
     <t xml:space="preserve">№</t>
@@ -75,6 +75,12 @@
     <t xml:space="preserve">Классный руководитель</t>
   </si>
   <si>
+    <t xml:space="preserve">Пакет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость пакета, тг</t>
+  </si>
+  <si>
     <t xml:space="preserve">Оплачено, тг</t>
   </si>
   <si>
@@ -108,21 +114,42 @@
     <t xml:space="preserve">Поездка в Астану: посещение университетов, 27–28 октября 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Настройки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стоимость поездки на одного ученика, тг</t>
-  </si>
-  <si>
     <t xml:space="preserve">Дата выезда</t>
   </si>
   <si>
+    <t xml:space="preserve">Пакеты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пакет (название можно изменить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стоимость, тг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выбрали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пакет 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пакет 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пакет 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Итоги</t>
   </si>
   <si>
     <t xml:space="preserve">Учеников в списке</t>
   </si>
   <si>
+    <t xml:space="preserve">Выбрали пакет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ещё не выбрали пакет</t>
+  </si>
+  <si>
     <t xml:space="preserve">Оплатили полностью</t>
   </si>
   <si>
@@ -135,7 +162,7 @@
     <t xml:space="preserve">Собрано, тг</t>
   </si>
   <si>
-    <t xml:space="preserve">Ожидается всего, тг</t>
+    <t xml:space="preserve">Ожидается по выбранным пакетам, тг</t>
   </si>
   <si>
     <t xml:space="preserve">Осталось собрать, тг</t>
@@ -153,16 +180,19 @@
     <t xml:space="preserve">1. Лист «Ученики»: одна строка — один ученик. Заполняйте только жёлтые ячейки.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Серые ячейки (№, классный руководитель, остаток, статус оплаты, «Готов к поездке») считаются сами.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Когда станет известна стоимость поездки, впишите её на листе «Сводка» в ячейку C4 — статусы оплаты пересчитаются.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. «Готов к поездке» = Да, когда поездка оплачена полностью.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Лист «Классы»: класс и его классный руководитель. Класс пишите так же, как в списке (например, 11 «А»).</t>
+    <t xml:space="preserve">2. Серые ячейки (№, классный руководитель, стоимость пакета, остаток, статус оплаты, «Готов к поездке») считаются сами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Пакет выбирается из списка в ячейке. Названия и цены пакетов задаются на листе «Сводка».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Если переименовать пакет на «Сводке», у учеников, которые уже выбрали его, нужно выбрать пакет заново.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. «Готов к поездке» = Да, когда выбранный пакет оплачен полностью.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Лист «Классы»: класс и его классный руководитель. Класс пишите так же, как в списке (например, 11 «А»).</t>
   </si>
   <si>
     <t xml:space="preserve">Пример заполненной строки (вымышленный ученик, в список не переносить)</t>
@@ -358,7 +388,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,11 +421,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -403,19 +433,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,7 +445,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -460,7 +482,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -547,6 +569,15 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <i val="1"/>
+        <color rgb="FF808080"/>
+      </font>
     </dxf>
   </dxfs>
   <colors>
@@ -796,7 +827,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -805,10 +836,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -854,6 +887,12 @@
       </c>
       <c r="K4" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -869,20 +908,25 @@
         <f aca="false">IF(E5="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E5,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9" t="str">
-        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",Сводка!$C$4-G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="str">
-        <f aca="false">IF(OR(B5="",Сводка!$C$4=""),"",IF(G5&gt;=Сводка!$C$4,"Оплачено",IF(G5&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J5" s="4" t="str">
-        <f aca="false">IF(B5="","",IF(I5="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="8" t="str">
+        <f aca="false">IF(OR(B5="",G5=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G5,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G5,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="8" t="str">
+        <f aca="false">IF(H5="","",H5-I5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="4" t="str">
+        <f aca="false">IF(B5="","",IF(G5="","Пакет не выбран",IF(H5="","",IF(I5&gt;=H5,"Оплачено",IF(I5&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L5" s="4" t="str">
+        <f aca="false">IF(B5="","",IF(K5="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="str">
@@ -897,20 +941,25 @@
         <f aca="false">IF(E6="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E6,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9" t="str">
-        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",Сводка!$C$4-G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="4" t="str">
-        <f aca="false">IF(OR(B6="",Сводка!$C$4=""),"",IF(G6&gt;=Сводка!$C$4,"Оплачено",IF(G6&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="str">
-        <f aca="false">IF(B6="","",IF(I6="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="8" t="str">
+        <f aca="false">IF(OR(B6="",G6=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G6,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G6,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="8" t="str">
+        <f aca="false">IF(H6="","",H6-I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="4" t="str">
+        <f aca="false">IF(B6="","",IF(G6="","Пакет не выбран",IF(H6="","",IF(I6&gt;=H6,"Оплачено",IF(I6&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L6" s="4" t="str">
+        <f aca="false">IF(B6="","",IF(K6="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="str">
@@ -925,20 +974,25 @@
         <f aca="false">IF(E7="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E7,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9" t="str">
-        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",Сводка!$C$4-G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="str">
-        <f aca="false">IF(OR(B7="",Сводка!$C$4=""),"",IF(G7&gt;=Сводка!$C$4,"Оплачено",IF(G7&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="str">
-        <f aca="false">IF(B7="","",IF(I7="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="8" t="str">
+        <f aca="false">IF(OR(B7="",G7=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G7,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G7,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="8" t="str">
+        <f aca="false">IF(H7="","",H7-I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="4" t="str">
+        <f aca="false">IF(B7="","",IF(G7="","Пакет не выбран",IF(H7="","",IF(I7&gt;=H7,"Оплачено",IF(I7&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L7" s="4" t="str">
+        <f aca="false">IF(B7="","",IF(K7="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="str">
@@ -953,20 +1007,25 @@
         <f aca="false">IF(E8="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E8,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9" t="str">
-        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",Сводка!$C$4-G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="4" t="str">
-        <f aca="false">IF(OR(B8="",Сводка!$C$4=""),"",IF(G8&gt;=Сводка!$C$4,"Оплачено",IF(G8&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="str">
-        <f aca="false">IF(B8="","",IF(I8="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="8" t="str">
+        <f aca="false">IF(OR(B8="",G8=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G8,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G8,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="8" t="str">
+        <f aca="false">IF(H8="","",H8-I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="4" t="str">
+        <f aca="false">IF(B8="","",IF(G8="","Пакет не выбран",IF(H8="","",IF(I8&gt;=H8,"Оплачено",IF(I8&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L8" s="4" t="str">
+        <f aca="false">IF(B8="","",IF(K8="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="str">
@@ -981,20 +1040,25 @@
         <f aca="false">IF(E9="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E9,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9" t="str">
-        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",Сводка!$C$4-G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="str">
-        <f aca="false">IF(OR(B9="",Сводка!$C$4=""),"",IF(G9&gt;=Сводка!$C$4,"Оплачено",IF(G9&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="str">
-        <f aca="false">IF(B9="","",IF(I9="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="8" t="str">
+        <f aca="false">IF(OR(B9="",G9=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G9,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G9,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="8" t="str">
+        <f aca="false">IF(H9="","",H9-I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="4" t="str">
+        <f aca="false">IF(B9="","",IF(G9="","Пакет не выбран",IF(H9="","",IF(I9&gt;=H9,"Оплачено",IF(I9&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L9" s="4" t="str">
+        <f aca="false">IF(B9="","",IF(K9="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="str">
@@ -1009,20 +1073,25 @@
         <f aca="false">IF(E10="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E10,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9" t="str">
-        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",Сводка!$C$4-G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="4" t="str">
-        <f aca="false">IF(OR(B10="",Сводка!$C$4=""),"",IF(G10&gt;=Сводка!$C$4,"Оплачено",IF(G10&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="str">
-        <f aca="false">IF(B10="","",IF(I10="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="8" t="str">
+        <f aca="false">IF(OR(B10="",G10=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G10,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G10,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="8" t="str">
+        <f aca="false">IF(H10="","",H10-I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="4" t="str">
+        <f aca="false">IF(B10="","",IF(G10="","Пакет не выбран",IF(H10="","",IF(I10&gt;=H10,"Оплачено",IF(I10&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L10" s="4" t="str">
+        <f aca="false">IF(B10="","",IF(K10="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="str">
@@ -1037,20 +1106,25 @@
         <f aca="false">IF(E11="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E11,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="9" t="str">
-        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",Сводка!$C$4-G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="str">
-        <f aca="false">IF(OR(B11="",Сводка!$C$4=""),"",IF(G11&gt;=Сводка!$C$4,"Оплачено",IF(G11&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="str">
-        <f aca="false">IF(B11="","",IF(I11="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="8" t="str">
+        <f aca="false">IF(OR(B11="",G11=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G11,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G11,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="8" t="str">
+        <f aca="false">IF(H11="","",H11-I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="4" t="str">
+        <f aca="false">IF(B11="","",IF(G11="","Пакет не выбран",IF(H11="","",IF(I11&gt;=H11,"Оплачено",IF(I11&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L11" s="4" t="str">
+        <f aca="false">IF(B11="","",IF(K11="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="str">
@@ -1065,20 +1139,25 @@
         <f aca="false">IF(E12="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E12,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="9" t="str">
-        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",Сводка!$C$4-G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="str">
-        <f aca="false">IF(OR(B12="",Сводка!$C$4=""),"",IF(G12&gt;=Сводка!$C$4,"Оплачено",IF(G12&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="str">
-        <f aca="false">IF(B12="","",IF(I12="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="8" t="str">
+        <f aca="false">IF(OR(B12="",G12=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G12,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G12,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="8" t="str">
+        <f aca="false">IF(H12="","",H12-I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="4" t="str">
+        <f aca="false">IF(B12="","",IF(G12="","Пакет не выбран",IF(H12="","",IF(I12&gt;=H12,"Оплачено",IF(I12&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L12" s="4" t="str">
+        <f aca="false">IF(B12="","",IF(K12="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="str">
@@ -1093,20 +1172,25 @@
         <f aca="false">IF(E13="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E13,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9" t="str">
-        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",Сводка!$C$4-G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="4" t="str">
-        <f aca="false">IF(OR(B13="",Сводка!$C$4=""),"",IF(G13&gt;=Сводка!$C$4,"Оплачено",IF(G13&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="str">
-        <f aca="false">IF(B13="","",IF(I13="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="8" t="str">
+        <f aca="false">IF(OR(B13="",G13=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G13,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G13,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="8" t="str">
+        <f aca="false">IF(H13="","",H13-I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="4" t="str">
+        <f aca="false">IF(B13="","",IF(G13="","Пакет не выбран",IF(H13="","",IF(I13&gt;=H13,"Оплачено",IF(I13&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L13" s="4" t="str">
+        <f aca="false">IF(B13="","",IF(K13="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="str">
@@ -1121,20 +1205,25 @@
         <f aca="false">IF(E14="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E14,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9" t="str">
-        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",Сводка!$C$4-G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="str">
-        <f aca="false">IF(OR(B14="",Сводка!$C$4=""),"",IF(G14&gt;=Сводка!$C$4,"Оплачено",IF(G14&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="str">
-        <f aca="false">IF(B14="","",IF(I14="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K14" s="5"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="8" t="str">
+        <f aca="false">IF(OR(B14="",G14=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G14,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G14,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="8" t="str">
+        <f aca="false">IF(H14="","",H14-I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="4" t="str">
+        <f aca="false">IF(B14="","",IF(G14="","Пакет не выбран",IF(H14="","",IF(I14&gt;=H14,"Оплачено",IF(I14&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L14" s="4" t="str">
+        <f aca="false">IF(B14="","",IF(K14="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="str">
@@ -1149,20 +1238,25 @@
         <f aca="false">IF(E15="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E15,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9" t="str">
-        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",Сводка!$C$4-G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="4" t="str">
-        <f aca="false">IF(OR(B15="",Сводка!$C$4=""),"",IF(G15&gt;=Сводка!$C$4,"Оплачено",IF(G15&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="str">
-        <f aca="false">IF(B15="","",IF(I15="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="8" t="str">
+        <f aca="false">IF(OR(B15="",G15=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G15,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G15,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="8" t="str">
+        <f aca="false">IF(H15="","",H15-I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="4" t="str">
+        <f aca="false">IF(B15="","",IF(G15="","Пакет не выбран",IF(H15="","",IF(I15&gt;=H15,"Оплачено",IF(I15&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L15" s="4" t="str">
+        <f aca="false">IF(B15="","",IF(K15="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="str">
@@ -1177,20 +1271,25 @@
         <f aca="false">IF(E16="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E16,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9" t="str">
-        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",Сводка!$C$4-G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="str">
-        <f aca="false">IF(OR(B16="",Сводка!$C$4=""),"",IF(G16&gt;=Сводка!$C$4,"Оплачено",IF(G16&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J16" s="4" t="str">
-        <f aca="false">IF(B16="","",IF(I16="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="8" t="str">
+        <f aca="false">IF(OR(B16="",G16=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G16,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G16,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="8" t="str">
+        <f aca="false">IF(H16="","",H16-I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="4" t="str">
+        <f aca="false">IF(B16="","",IF(G16="","Пакет не выбран",IF(H16="","",IF(I16&gt;=H16,"Оплачено",IF(I16&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L16" s="4" t="str">
+        <f aca="false">IF(B16="","",IF(K16="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="str">
@@ -1205,20 +1304,25 @@
         <f aca="false">IF(E17="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E17,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="9" t="str">
-        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",Сводка!$C$4-G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="4" t="str">
-        <f aca="false">IF(OR(B17="",Сводка!$C$4=""),"",IF(G17&gt;=Сводка!$C$4,"Оплачено",IF(G17&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J17" s="4" t="str">
-        <f aca="false">IF(B17="","",IF(I17="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="8" t="str">
+        <f aca="false">IF(OR(B17="",G17=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G17,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G17,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="8" t="str">
+        <f aca="false">IF(H17="","",H17-I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4" t="str">
+        <f aca="false">IF(B17="","",IF(G17="","Пакет не выбран",IF(H17="","",IF(I17&gt;=H17,"Оплачено",IF(I17&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L17" s="4" t="str">
+        <f aca="false">IF(B17="","",IF(K17="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="str">
@@ -1233,20 +1337,25 @@
         <f aca="false">IF(E18="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E18,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="9" t="str">
-        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",Сводка!$C$4-G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="4" t="str">
-        <f aca="false">IF(OR(B18="",Сводка!$C$4=""),"",IF(G18&gt;=Сводка!$C$4,"Оплачено",IF(G18&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J18" s="4" t="str">
-        <f aca="false">IF(B18="","",IF(I18="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="8" t="str">
+        <f aca="false">IF(OR(B18="",G18=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G18,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G18,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="8" t="str">
+        <f aca="false">IF(H18="","",H18-I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="4" t="str">
+        <f aca="false">IF(B18="","",IF(G18="","Пакет не выбран",IF(H18="","",IF(I18&gt;=H18,"Оплачено",IF(I18&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L18" s="4" t="str">
+        <f aca="false">IF(B18="","",IF(K18="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="str">
@@ -1261,20 +1370,25 @@
         <f aca="false">IF(E19="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E19,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9" t="str">
-        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",Сводка!$C$4-G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="4" t="str">
-        <f aca="false">IF(OR(B19="",Сводка!$C$4=""),"",IF(G19&gt;=Сводка!$C$4,"Оплачено",IF(G19&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J19" s="4" t="str">
-        <f aca="false">IF(B19="","",IF(I19="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="8" t="str">
+        <f aca="false">IF(OR(B19="",G19=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G19,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G19,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="8" t="str">
+        <f aca="false">IF(H19="","",H19-I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="4" t="str">
+        <f aca="false">IF(B19="","",IF(G19="","Пакет не выбран",IF(H19="","",IF(I19&gt;=H19,"Оплачено",IF(I19&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L19" s="4" t="str">
+        <f aca="false">IF(B19="","",IF(K19="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="str">
@@ -1289,20 +1403,25 @@
         <f aca="false">IF(E20="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E20,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9" t="str">
-        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",Сводка!$C$4-G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="4" t="str">
-        <f aca="false">IF(OR(B20="",Сводка!$C$4=""),"",IF(G20&gt;=Сводка!$C$4,"Оплачено",IF(G20&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J20" s="4" t="str">
-        <f aca="false">IF(B20="","",IF(I20="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K20" s="5"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="8" t="str">
+        <f aca="false">IF(OR(B20="",G20=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G20,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G20,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="8" t="str">
+        <f aca="false">IF(H20="","",H20-I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="4" t="str">
+        <f aca="false">IF(B20="","",IF(G20="","Пакет не выбран",IF(H20="","",IF(I20&gt;=H20,"Оплачено",IF(I20&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L20" s="4" t="str">
+        <f aca="false">IF(B20="","",IF(K20="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="str">
@@ -1317,20 +1436,25 @@
         <f aca="false">IF(E21="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E21,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9" t="str">
-        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",Сводка!$C$4-G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="4" t="str">
-        <f aca="false">IF(OR(B21="",Сводка!$C$4=""),"",IF(G21&gt;=Сводка!$C$4,"Оплачено",IF(G21&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J21" s="4" t="str">
-        <f aca="false">IF(B21="","",IF(I21="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K21" s="5"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8" t="str">
+        <f aca="false">IF(OR(B21="",G21=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G21,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G21,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="8" t="str">
+        <f aca="false">IF(H21="","",H21-I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="4" t="str">
+        <f aca="false">IF(B21="","",IF(G21="","Пакет не выбран",IF(H21="","",IF(I21&gt;=H21,"Оплачено",IF(I21&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L21" s="4" t="str">
+        <f aca="false">IF(B21="","",IF(K21="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="str">
@@ -1345,20 +1469,25 @@
         <f aca="false">IF(E22="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E22,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="9" t="str">
-        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",Сводка!$C$4-G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="4" t="str">
-        <f aca="false">IF(OR(B22="",Сводка!$C$4=""),"",IF(G22&gt;=Сводка!$C$4,"Оплачено",IF(G22&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J22" s="4" t="str">
-        <f aca="false">IF(B22="","",IF(I22="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K22" s="5"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="8" t="str">
+        <f aca="false">IF(OR(B22="",G22=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G22,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G22,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8" t="str">
+        <f aca="false">IF(H22="","",H22-I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="4" t="str">
+        <f aca="false">IF(B22="","",IF(G22="","Пакет не выбран",IF(H22="","",IF(I22&gt;=H22,"Оплачено",IF(I22&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L22" s="4" t="str">
+        <f aca="false">IF(B22="","",IF(K22="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="str">
@@ -1373,20 +1502,25 @@
         <f aca="false">IF(E23="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E23,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9" t="str">
-        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",Сводка!$C$4-G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="4" t="str">
-        <f aca="false">IF(OR(B23="",Сводка!$C$4=""),"",IF(G23&gt;=Сводка!$C$4,"Оплачено",IF(G23&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J23" s="4" t="str">
-        <f aca="false">IF(B23="","",IF(I23="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K23" s="5"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="8" t="str">
+        <f aca="false">IF(OR(B23="",G23=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G23,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G23,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8" t="str">
+        <f aca="false">IF(H23="","",H23-I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="4" t="str">
+        <f aca="false">IF(B23="","",IF(G23="","Пакет не выбран",IF(H23="","",IF(I23&gt;=H23,"Оплачено",IF(I23&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L23" s="4" t="str">
+        <f aca="false">IF(B23="","",IF(K23="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="str">
@@ -1401,20 +1535,25 @@
         <f aca="false">IF(E24="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E24,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9" t="str">
-        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",Сводка!$C$4-G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="4" t="str">
-        <f aca="false">IF(OR(B24="",Сводка!$C$4=""),"",IF(G24&gt;=Сводка!$C$4,"Оплачено",IF(G24&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J24" s="4" t="str">
-        <f aca="false">IF(B24="","",IF(I24="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K24" s="5"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="8" t="str">
+        <f aca="false">IF(OR(B24="",G24=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G24,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G24,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="8" t="str">
+        <f aca="false">IF(H24="","",H24-I24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="4" t="str">
+        <f aca="false">IF(B24="","",IF(G24="","Пакет не выбран",IF(H24="","",IF(I24&gt;=H24,"Оплачено",IF(I24&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L24" s="4" t="str">
+        <f aca="false">IF(B24="","",IF(K24="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="str">
@@ -1429,20 +1568,25 @@
         <f aca="false">IF(E25="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E25,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="str">
-        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",Сводка!$C$4-G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="4" t="str">
-        <f aca="false">IF(OR(B25="",Сводка!$C$4=""),"",IF(G25&gt;=Сводка!$C$4,"Оплачено",IF(G25&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J25" s="4" t="str">
-        <f aca="false">IF(B25="","",IF(I25="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K25" s="5"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="8" t="str">
+        <f aca="false">IF(OR(B25="",G25=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G25,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G25,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="8" t="str">
+        <f aca="false">IF(H25="","",H25-I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="4" t="str">
+        <f aca="false">IF(B25="","",IF(G25="","Пакет не выбран",IF(H25="","",IF(I25&gt;=H25,"Оплачено",IF(I25&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L25" s="4" t="str">
+        <f aca="false">IF(B25="","",IF(K25="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="str">
@@ -1457,20 +1601,25 @@
         <f aca="false">IF(E26="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E26,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9" t="str">
-        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",Сводка!$C$4-G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="4" t="str">
-        <f aca="false">IF(OR(B26="",Сводка!$C$4=""),"",IF(G26&gt;=Сводка!$C$4,"Оплачено",IF(G26&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J26" s="4" t="str">
-        <f aca="false">IF(B26="","",IF(I26="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="8" t="str">
+        <f aca="false">IF(OR(B26="",G26=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G26,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G26,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="8" t="str">
+        <f aca="false">IF(H26="","",H26-I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="4" t="str">
+        <f aca="false">IF(B26="","",IF(G26="","Пакет не выбран",IF(H26="","",IF(I26&gt;=H26,"Оплачено",IF(I26&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L26" s="4" t="str">
+        <f aca="false">IF(B26="","",IF(K26="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="str">
@@ -1485,20 +1634,25 @@
         <f aca="false">IF(E27="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E27,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9" t="str">
-        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",Сводка!$C$4-G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="4" t="str">
-        <f aca="false">IF(OR(B27="",Сводка!$C$4=""),"",IF(G27&gt;=Сводка!$C$4,"Оплачено",IF(G27&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J27" s="4" t="str">
-        <f aca="false">IF(B27="","",IF(I27="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K27" s="5"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="8" t="str">
+        <f aca="false">IF(OR(B27="",G27=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G27,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G27,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="8" t="str">
+        <f aca="false">IF(H27="","",H27-I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="4" t="str">
+        <f aca="false">IF(B27="","",IF(G27="","Пакет не выбран",IF(H27="","",IF(I27&gt;=H27,"Оплачено",IF(I27&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L27" s="4" t="str">
+        <f aca="false">IF(B27="","",IF(K27="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="str">
@@ -1513,20 +1667,25 @@
         <f aca="false">IF(E28="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E28,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9" t="str">
-        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",Сводка!$C$4-G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="4" t="str">
-        <f aca="false">IF(OR(B28="",Сводка!$C$4=""),"",IF(G28&gt;=Сводка!$C$4,"Оплачено",IF(G28&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J28" s="4" t="str">
-        <f aca="false">IF(B28="","",IF(I28="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K28" s="5"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="8" t="str">
+        <f aca="false">IF(OR(B28="",G28=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G28,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G28,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="8" t="str">
+        <f aca="false">IF(H28="","",H28-I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="4" t="str">
+        <f aca="false">IF(B28="","",IF(G28="","Пакет не выбран",IF(H28="","",IF(I28&gt;=H28,"Оплачено",IF(I28&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L28" s="4" t="str">
+        <f aca="false">IF(B28="","",IF(K28="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="str">
@@ -1541,20 +1700,25 @@
         <f aca="false">IF(E29="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E29,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9" t="str">
-        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",Сводка!$C$4-G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="4" t="str">
-        <f aca="false">IF(OR(B29="",Сводка!$C$4=""),"",IF(G29&gt;=Сводка!$C$4,"Оплачено",IF(G29&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J29" s="4" t="str">
-        <f aca="false">IF(B29="","",IF(I29="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K29" s="5"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="8" t="str">
+        <f aca="false">IF(OR(B29="",G29=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G29,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G29,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="8" t="str">
+        <f aca="false">IF(H29="","",H29-I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="4" t="str">
+        <f aca="false">IF(B29="","",IF(G29="","Пакет не выбран",IF(H29="","",IF(I29&gt;=H29,"Оплачено",IF(I29&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L29" s="4" t="str">
+        <f aca="false">IF(B29="","",IF(K29="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="str">
@@ -1569,20 +1733,25 @@
         <f aca="false">IF(E30="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E30,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9" t="str">
-        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",Сводка!$C$4-G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="4" t="str">
-        <f aca="false">IF(OR(B30="",Сводка!$C$4=""),"",IF(G30&gt;=Сводка!$C$4,"Оплачено",IF(G30&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J30" s="4" t="str">
-        <f aca="false">IF(B30="","",IF(I30="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="8" t="str">
+        <f aca="false">IF(OR(B30="",G30=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G30,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G30,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="8" t="str">
+        <f aca="false">IF(H30="","",H30-I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="4" t="str">
+        <f aca="false">IF(B30="","",IF(G30="","Пакет не выбран",IF(H30="","",IF(I30&gt;=H30,"Оплачено",IF(I30&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L30" s="4" t="str">
+        <f aca="false">IF(B30="","",IF(K30="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="str">
@@ -1597,20 +1766,25 @@
         <f aca="false">IF(E31="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E31,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="str">
-        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",Сводка!$C$4-G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="4" t="str">
-        <f aca="false">IF(OR(B31="",Сводка!$C$4=""),"",IF(G31&gt;=Сводка!$C$4,"Оплачено",IF(G31&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J31" s="4" t="str">
-        <f aca="false">IF(B31="","",IF(I31="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K31" s="5"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="8" t="str">
+        <f aca="false">IF(OR(B31="",G31=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G31,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G31,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="8" t="str">
+        <f aca="false">IF(H31="","",H31-I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="4" t="str">
+        <f aca="false">IF(B31="","",IF(G31="","Пакет не выбран",IF(H31="","",IF(I31&gt;=H31,"Оплачено",IF(I31&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L31" s="4" t="str">
+        <f aca="false">IF(B31="","",IF(K31="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="str">
@@ -1625,20 +1799,25 @@
         <f aca="false">IF(E32="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E32,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9" t="str">
-        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",Сводка!$C$4-G32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="4" t="str">
-        <f aca="false">IF(OR(B32="",Сводка!$C$4=""),"",IF(G32&gt;=Сводка!$C$4,"Оплачено",IF(G32&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="str">
-        <f aca="false">IF(B32="","",IF(I32="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="8" t="str">
+        <f aca="false">IF(OR(B32="",G32=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G32,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G32,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="8" t="str">
+        <f aca="false">IF(H32="","",H32-I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="4" t="str">
+        <f aca="false">IF(B32="","",IF(G32="","Пакет не выбран",IF(H32="","",IF(I32&gt;=H32,"Оплачено",IF(I32&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L32" s="4" t="str">
+        <f aca="false">IF(B32="","",IF(K32="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="str">
@@ -1653,20 +1832,25 @@
         <f aca="false">IF(E33="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E33,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9" t="str">
-        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",Сводка!$C$4-G33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="4" t="str">
-        <f aca="false">IF(OR(B33="",Сводка!$C$4=""),"",IF(G33&gt;=Сводка!$C$4,"Оплачено",IF(G33&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="str">
-        <f aca="false">IF(B33="","",IF(I33="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="8" t="str">
+        <f aca="false">IF(OR(B33="",G33=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G33,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G33,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="8" t="str">
+        <f aca="false">IF(H33="","",H33-I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="4" t="str">
+        <f aca="false">IF(B33="","",IF(G33="","Пакет не выбран",IF(H33="","",IF(I33&gt;=H33,"Оплачено",IF(I33&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L33" s="4" t="str">
+        <f aca="false">IF(B33="","",IF(K33="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="str">
@@ -1681,20 +1865,25 @@
         <f aca="false">IF(E34="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E34,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9" t="str">
-        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",Сводка!$C$4-G34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="4" t="str">
-        <f aca="false">IF(OR(B34="",Сводка!$C$4=""),"",IF(G34&gt;=Сводка!$C$4,"Оплачено",IF(G34&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="str">
-        <f aca="false">IF(B34="","",IF(I34="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K34" s="5"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="8" t="str">
+        <f aca="false">IF(OR(B34="",G34=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G34,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G34,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="8" t="str">
+        <f aca="false">IF(H34="","",H34-I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="4" t="str">
+        <f aca="false">IF(B34="","",IF(G34="","Пакет не выбран",IF(H34="","",IF(I34&gt;=H34,"Оплачено",IF(I34&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L34" s="4" t="str">
+        <f aca="false">IF(B34="","",IF(K34="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="str">
@@ -1709,20 +1898,25 @@
         <f aca="false">IF(E35="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E35,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="9" t="str">
-        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",Сводка!$C$4-G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="4" t="str">
-        <f aca="false">IF(OR(B35="",Сводка!$C$4=""),"",IF(G35&gt;=Сводка!$C$4,"Оплачено",IF(G35&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="str">
-        <f aca="false">IF(B35="","",IF(I35="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K35" s="5"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="8" t="str">
+        <f aca="false">IF(OR(B35="",G35=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G35,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G35,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="8" t="str">
+        <f aca="false">IF(H35="","",H35-I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="4" t="str">
+        <f aca="false">IF(B35="","",IF(G35="","Пакет не выбран",IF(H35="","",IF(I35&gt;=H35,"Оплачено",IF(I35&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L35" s="4" t="str">
+        <f aca="false">IF(B35="","",IF(K35="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="str">
@@ -1737,20 +1931,25 @@
         <f aca="false">IF(E36="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E36,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9" t="str">
-        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",Сводка!$C$4-G36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="4" t="str">
-        <f aca="false">IF(OR(B36="",Сводка!$C$4=""),"",IF(G36&gt;=Сводка!$C$4,"Оплачено",IF(G36&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="str">
-        <f aca="false">IF(B36="","",IF(I36="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K36" s="5"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="8" t="str">
+        <f aca="false">IF(OR(B36="",G36=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G36,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G36,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="8" t="str">
+        <f aca="false">IF(H36="","",H36-I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="4" t="str">
+        <f aca="false">IF(B36="","",IF(G36="","Пакет не выбран",IF(H36="","",IF(I36&gt;=H36,"Оплачено",IF(I36&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L36" s="4" t="str">
+        <f aca="false">IF(B36="","",IF(K36="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="str">
@@ -1765,20 +1964,25 @@
         <f aca="false">IF(E37="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E37,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9" t="str">
-        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",Сводка!$C$4-G37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="4" t="str">
-        <f aca="false">IF(OR(B37="",Сводка!$C$4=""),"",IF(G37&gt;=Сводка!$C$4,"Оплачено",IF(G37&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="str">
-        <f aca="false">IF(B37="","",IF(I37="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="8" t="str">
+        <f aca="false">IF(OR(B37="",G37=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G37,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G37,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I37" s="9"/>
+      <c r="J37" s="8" t="str">
+        <f aca="false">IF(H37="","",H37-I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="4" t="str">
+        <f aca="false">IF(B37="","",IF(G37="","Пакет не выбран",IF(H37="","",IF(I37&gt;=H37,"Оплачено",IF(I37&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L37" s="4" t="str">
+        <f aca="false">IF(B37="","",IF(K37="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="str">
@@ -1793,20 +1997,25 @@
         <f aca="false">IF(E38="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E38,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9" t="str">
-        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",Сводка!$C$4-G38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="4" t="str">
-        <f aca="false">IF(OR(B38="",Сводка!$C$4=""),"",IF(G38&gt;=Сводка!$C$4,"Оплачено",IF(G38&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="str">
-        <f aca="false">IF(B38="","",IF(I38="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K38" s="5"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="8" t="str">
+        <f aca="false">IF(OR(B38="",G38=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G38,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G38,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I38" s="9"/>
+      <c r="J38" s="8" t="str">
+        <f aca="false">IF(H38="","",H38-I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="4" t="str">
+        <f aca="false">IF(B38="","",IF(G38="","Пакет не выбран",IF(H38="","",IF(I38&gt;=H38,"Оплачено",IF(I38&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L38" s="4" t="str">
+        <f aca="false">IF(B38="","",IF(K38="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="str">
@@ -1821,20 +2030,25 @@
         <f aca="false">IF(E39="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E39,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9" t="str">
-        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",Сводка!$C$4-G39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="4" t="str">
-        <f aca="false">IF(OR(B39="",Сводка!$C$4=""),"",IF(G39&gt;=Сводка!$C$4,"Оплачено",IF(G39&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="str">
-        <f aca="false">IF(B39="","",IF(I39="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K39" s="5"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="8" t="str">
+        <f aca="false">IF(OR(B39="",G39=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G39,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G39,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="8" t="str">
+        <f aca="false">IF(H39="","",H39-I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="4" t="str">
+        <f aca="false">IF(B39="","",IF(G39="","Пакет не выбран",IF(H39="","",IF(I39&gt;=H39,"Оплачено",IF(I39&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L39" s="4" t="str">
+        <f aca="false">IF(B39="","",IF(K39="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="str">
@@ -1849,20 +2063,25 @@
         <f aca="false">IF(E40="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E40,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="9" t="str">
-        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",Сводка!$C$4-G40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="4" t="str">
-        <f aca="false">IF(OR(B40="",Сводка!$C$4=""),"",IF(G40&gt;=Сводка!$C$4,"Оплачено",IF(G40&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="str">
-        <f aca="false">IF(B40="","",IF(I40="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K40" s="5"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="8" t="str">
+        <f aca="false">IF(OR(B40="",G40=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G40,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G40,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I40" s="9"/>
+      <c r="J40" s="8" t="str">
+        <f aca="false">IF(H40="","",H40-I40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="4" t="str">
+        <f aca="false">IF(B40="","",IF(G40="","Пакет не выбран",IF(H40="","",IF(I40&gt;=H40,"Оплачено",IF(I40&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L40" s="4" t="str">
+        <f aca="false">IF(B40="","",IF(K40="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="str">
@@ -1877,20 +2096,25 @@
         <f aca="false">IF(E41="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E41,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G41" s="8"/>
-      <c r="H41" s="9" t="str">
-        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",Сводка!$C$4-G41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="4" t="str">
-        <f aca="false">IF(OR(B41="",Сводка!$C$4=""),"",IF(G41&gt;=Сводка!$C$4,"Оплачено",IF(G41&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="str">
-        <f aca="false">IF(B41="","",IF(I41="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K41" s="5"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="8" t="str">
+        <f aca="false">IF(OR(B41="",G41=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G41,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G41,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I41" s="9"/>
+      <c r="J41" s="8" t="str">
+        <f aca="false">IF(H41="","",H41-I41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="4" t="str">
+        <f aca="false">IF(B41="","",IF(G41="","Пакет не выбран",IF(H41="","",IF(I41&gt;=H41,"Оплачено",IF(I41&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L41" s="4" t="str">
+        <f aca="false">IF(B41="","",IF(K41="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="str">
@@ -1905,20 +2129,25 @@
         <f aca="false">IF(E42="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E42,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="9" t="str">
-        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",Сводка!$C$4-G42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="4" t="str">
-        <f aca="false">IF(OR(B42="",Сводка!$C$4=""),"",IF(G42&gt;=Сводка!$C$4,"Оплачено",IF(G42&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J42" s="4" t="str">
-        <f aca="false">IF(B42="","",IF(I42="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K42" s="5"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="8" t="str">
+        <f aca="false">IF(OR(B42="",G42=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G42,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G42,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I42" s="9"/>
+      <c r="J42" s="8" t="str">
+        <f aca="false">IF(H42="","",H42-I42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="4" t="str">
+        <f aca="false">IF(B42="","",IF(G42="","Пакет не выбран",IF(H42="","",IF(I42&gt;=H42,"Оплачено",IF(I42&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L42" s="4" t="str">
+        <f aca="false">IF(B42="","",IF(K42="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="str">
@@ -1933,20 +2162,25 @@
         <f aca="false">IF(E43="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E43,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G43" s="8"/>
-      <c r="H43" s="9" t="str">
-        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",Сводка!$C$4-G43)</f>
-        <v/>
-      </c>
-      <c r="I43" s="4" t="str">
-        <f aca="false">IF(OR(B43="",Сводка!$C$4=""),"",IF(G43&gt;=Сводка!$C$4,"Оплачено",IF(G43&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J43" s="4" t="str">
-        <f aca="false">IF(B43="","",IF(I43="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K43" s="5"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="8" t="str">
+        <f aca="false">IF(OR(B43="",G43=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G43,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G43,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I43" s="9"/>
+      <c r="J43" s="8" t="str">
+        <f aca="false">IF(H43="","",H43-I43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="4" t="str">
+        <f aca="false">IF(B43="","",IF(G43="","Пакет не выбран",IF(H43="","",IF(I43&gt;=H43,"Оплачено",IF(I43&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L43" s="4" t="str">
+        <f aca="false">IF(B43="","",IF(K43="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="str">
@@ -1961,20 +2195,25 @@
         <f aca="false">IF(E44="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E44,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G44" s="8"/>
-      <c r="H44" s="9" t="str">
-        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",Сводка!$C$4-G44)</f>
-        <v/>
-      </c>
-      <c r="I44" s="4" t="str">
-        <f aca="false">IF(OR(B44="",Сводка!$C$4=""),"",IF(G44&gt;=Сводка!$C$4,"Оплачено",IF(G44&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J44" s="4" t="str">
-        <f aca="false">IF(B44="","",IF(I44="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K44" s="5"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="8" t="str">
+        <f aca="false">IF(OR(B44="",G44=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G44,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G44,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I44" s="9"/>
+      <c r="J44" s="8" t="str">
+        <f aca="false">IF(H44="","",H44-I44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="4" t="str">
+        <f aca="false">IF(B44="","",IF(G44="","Пакет не выбран",IF(H44="","",IF(I44&gt;=H44,"Оплачено",IF(I44&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L44" s="4" t="str">
+        <f aca="false">IF(B44="","",IF(K44="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="str">
@@ -1989,20 +2228,25 @@
         <f aca="false">IF(E45="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E45,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="9" t="str">
-        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",Сводка!$C$4-G45)</f>
-        <v/>
-      </c>
-      <c r="I45" s="4" t="str">
-        <f aca="false">IF(OR(B45="",Сводка!$C$4=""),"",IF(G45&gt;=Сводка!$C$4,"Оплачено",IF(G45&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J45" s="4" t="str">
-        <f aca="false">IF(B45="","",IF(I45="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K45" s="5"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="8" t="str">
+        <f aca="false">IF(OR(B45="",G45=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G45,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G45,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I45" s="9"/>
+      <c r="J45" s="8" t="str">
+        <f aca="false">IF(H45="","",H45-I45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="4" t="str">
+        <f aca="false">IF(B45="","",IF(G45="","Пакет не выбран",IF(H45="","",IF(I45&gt;=H45,"Оплачено",IF(I45&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L45" s="4" t="str">
+        <f aca="false">IF(B45="","",IF(K45="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="str">
@@ -2017,20 +2261,25 @@
         <f aca="false">IF(E46="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E46,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G46" s="8"/>
-      <c r="H46" s="9" t="str">
-        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",Сводка!$C$4-G46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="4" t="str">
-        <f aca="false">IF(OR(B46="",Сводка!$C$4=""),"",IF(G46&gt;=Сводка!$C$4,"Оплачено",IF(G46&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J46" s="4" t="str">
-        <f aca="false">IF(B46="","",IF(I46="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K46" s="5"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="8" t="str">
+        <f aca="false">IF(OR(B46="",G46=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G46,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G46,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I46" s="9"/>
+      <c r="J46" s="8" t="str">
+        <f aca="false">IF(H46="","",H46-I46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="4" t="str">
+        <f aca="false">IF(B46="","",IF(G46="","Пакет не выбран",IF(H46="","",IF(I46&gt;=H46,"Оплачено",IF(I46&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L46" s="4" t="str">
+        <f aca="false">IF(B46="","",IF(K46="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="str">
@@ -2045,20 +2294,25 @@
         <f aca="false">IF(E47="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E47,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G47" s="8"/>
-      <c r="H47" s="9" t="str">
-        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",Сводка!$C$4-G47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="4" t="str">
-        <f aca="false">IF(OR(B47="",Сводка!$C$4=""),"",IF(G47&gt;=Сводка!$C$4,"Оплачено",IF(G47&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J47" s="4" t="str">
-        <f aca="false">IF(B47="","",IF(I47="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K47" s="5"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="8" t="str">
+        <f aca="false">IF(OR(B47="",G47=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G47,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G47,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="8" t="str">
+        <f aca="false">IF(H47="","",H47-I47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="4" t="str">
+        <f aca="false">IF(B47="","",IF(G47="","Пакет не выбран",IF(H47="","",IF(I47&gt;=H47,"Оплачено",IF(I47&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L47" s="4" t="str">
+        <f aca="false">IF(B47="","",IF(K47="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="str">
@@ -2073,20 +2327,25 @@
         <f aca="false">IF(E48="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E48,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="9" t="str">
-        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",Сводка!$C$4-G48)</f>
-        <v/>
-      </c>
-      <c r="I48" s="4" t="str">
-        <f aca="false">IF(OR(B48="",Сводка!$C$4=""),"",IF(G48&gt;=Сводка!$C$4,"Оплачено",IF(G48&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J48" s="4" t="str">
-        <f aca="false">IF(B48="","",IF(I48="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K48" s="5"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="8" t="str">
+        <f aca="false">IF(OR(B48="",G48=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G48,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G48,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="8" t="str">
+        <f aca="false">IF(H48="","",H48-I48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="4" t="str">
+        <f aca="false">IF(B48="","",IF(G48="","Пакет не выбран",IF(H48="","",IF(I48&gt;=H48,"Оплачено",IF(I48&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L48" s="4" t="str">
+        <f aca="false">IF(B48="","",IF(K48="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="str">
@@ -2101,20 +2360,25 @@
         <f aca="false">IF(E49="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E49,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="9" t="str">
-        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",Сводка!$C$4-G49)</f>
-        <v/>
-      </c>
-      <c r="I49" s="4" t="str">
-        <f aca="false">IF(OR(B49="",Сводка!$C$4=""),"",IF(G49&gt;=Сводка!$C$4,"Оплачено",IF(G49&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J49" s="4" t="str">
-        <f aca="false">IF(B49="","",IF(I49="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K49" s="5"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="8" t="str">
+        <f aca="false">IF(OR(B49="",G49=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G49,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G49,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="8" t="str">
+        <f aca="false">IF(H49="","",H49-I49)</f>
+        <v/>
+      </c>
+      <c r="K49" s="4" t="str">
+        <f aca="false">IF(B49="","",IF(G49="","Пакет не выбран",IF(H49="","",IF(I49&gt;=H49,"Оплачено",IF(I49&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L49" s="4" t="str">
+        <f aca="false">IF(B49="","",IF(K49="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="str">
@@ -2129,20 +2393,25 @@
         <f aca="false">IF(E50="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E50,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="9" t="str">
-        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",Сводка!$C$4-G50)</f>
-        <v/>
-      </c>
-      <c r="I50" s="4" t="str">
-        <f aca="false">IF(OR(B50="",Сводка!$C$4=""),"",IF(G50&gt;=Сводка!$C$4,"Оплачено",IF(G50&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J50" s="4" t="str">
-        <f aca="false">IF(B50="","",IF(I50="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K50" s="5"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="8" t="str">
+        <f aca="false">IF(OR(B50="",G50=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G50,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G50,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I50" s="9"/>
+      <c r="J50" s="8" t="str">
+        <f aca="false">IF(H50="","",H50-I50)</f>
+        <v/>
+      </c>
+      <c r="K50" s="4" t="str">
+        <f aca="false">IF(B50="","",IF(G50="","Пакет не выбран",IF(H50="","",IF(I50&gt;=H50,"Оплачено",IF(I50&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L50" s="4" t="str">
+        <f aca="false">IF(B50="","",IF(K50="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="str">
@@ -2157,20 +2426,25 @@
         <f aca="false">IF(E51="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E51,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="9" t="str">
-        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",Сводка!$C$4-G51)</f>
-        <v/>
-      </c>
-      <c r="I51" s="4" t="str">
-        <f aca="false">IF(OR(B51="",Сводка!$C$4=""),"",IF(G51&gt;=Сводка!$C$4,"Оплачено",IF(G51&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J51" s="4" t="str">
-        <f aca="false">IF(B51="","",IF(I51="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K51" s="5"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="8" t="str">
+        <f aca="false">IF(OR(B51="",G51=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G51,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G51,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I51" s="9"/>
+      <c r="J51" s="8" t="str">
+        <f aca="false">IF(H51="","",H51-I51)</f>
+        <v/>
+      </c>
+      <c r="K51" s="4" t="str">
+        <f aca="false">IF(B51="","",IF(G51="","Пакет не выбран",IF(H51="","",IF(I51&gt;=H51,"Оплачено",IF(I51&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L51" s="4" t="str">
+        <f aca="false">IF(B51="","",IF(K51="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="str">
@@ -2185,20 +2459,25 @@
         <f aca="false">IF(E52="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E52,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9" t="str">
-        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",Сводка!$C$4-G52)</f>
-        <v/>
-      </c>
-      <c r="I52" s="4" t="str">
-        <f aca="false">IF(OR(B52="",Сводка!$C$4=""),"",IF(G52&gt;=Сводка!$C$4,"Оплачено",IF(G52&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J52" s="4" t="str">
-        <f aca="false">IF(B52="","",IF(I52="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K52" s="5"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="8" t="str">
+        <f aca="false">IF(OR(B52="",G52=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G52,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G52,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I52" s="9"/>
+      <c r="J52" s="8" t="str">
+        <f aca="false">IF(H52="","",H52-I52)</f>
+        <v/>
+      </c>
+      <c r="K52" s="4" t="str">
+        <f aca="false">IF(B52="","",IF(G52="","Пакет не выбран",IF(H52="","",IF(I52&gt;=H52,"Оплачено",IF(I52&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L52" s="4" t="str">
+        <f aca="false">IF(B52="","",IF(K52="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="str">
@@ -2213,20 +2492,25 @@
         <f aca="false">IF(E53="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E53,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G53" s="8"/>
-      <c r="H53" s="9" t="str">
-        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",Сводка!$C$4-G53)</f>
-        <v/>
-      </c>
-      <c r="I53" s="4" t="str">
-        <f aca="false">IF(OR(B53="",Сводка!$C$4=""),"",IF(G53&gt;=Сводка!$C$4,"Оплачено",IF(G53&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J53" s="4" t="str">
-        <f aca="false">IF(B53="","",IF(I53="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K53" s="5"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="8" t="str">
+        <f aca="false">IF(OR(B53="",G53=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G53,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G53,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I53" s="9"/>
+      <c r="J53" s="8" t="str">
+        <f aca="false">IF(H53="","",H53-I53)</f>
+        <v/>
+      </c>
+      <c r="K53" s="4" t="str">
+        <f aca="false">IF(B53="","",IF(G53="","Пакет не выбран",IF(H53="","",IF(I53&gt;=H53,"Оплачено",IF(I53&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L53" s="4" t="str">
+        <f aca="false">IF(B53="","",IF(K53="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="str">
@@ -2241,20 +2525,25 @@
         <f aca="false">IF(E54="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E54,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G54" s="8"/>
-      <c r="H54" s="9" t="str">
-        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",Сводка!$C$4-G54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="4" t="str">
-        <f aca="false">IF(OR(B54="",Сводка!$C$4=""),"",IF(G54&gt;=Сводка!$C$4,"Оплачено",IF(G54&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J54" s="4" t="str">
-        <f aca="false">IF(B54="","",IF(I54="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K54" s="5"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="8" t="str">
+        <f aca="false">IF(OR(B54="",G54=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G54,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G54,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I54" s="9"/>
+      <c r="J54" s="8" t="str">
+        <f aca="false">IF(H54="","",H54-I54)</f>
+        <v/>
+      </c>
+      <c r="K54" s="4" t="str">
+        <f aca="false">IF(B54="","",IF(G54="","Пакет не выбран",IF(H54="","",IF(I54&gt;=H54,"Оплачено",IF(I54&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L54" s="4" t="str">
+        <f aca="false">IF(B54="","",IF(K54="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="str">
@@ -2269,20 +2558,25 @@
         <f aca="false">IF(E55="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E55,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G55" s="8"/>
-      <c r="H55" s="9" t="str">
-        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",Сводка!$C$4-G55)</f>
-        <v/>
-      </c>
-      <c r="I55" s="4" t="str">
-        <f aca="false">IF(OR(B55="",Сводка!$C$4=""),"",IF(G55&gt;=Сводка!$C$4,"Оплачено",IF(G55&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J55" s="4" t="str">
-        <f aca="false">IF(B55="","",IF(I55="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K55" s="5"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="8" t="str">
+        <f aca="false">IF(OR(B55="",G55=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G55,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G55,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="8" t="str">
+        <f aca="false">IF(H55="","",H55-I55)</f>
+        <v/>
+      </c>
+      <c r="K55" s="4" t="str">
+        <f aca="false">IF(B55="","",IF(G55="","Пакет не выбран",IF(H55="","",IF(I55&gt;=H55,"Оплачено",IF(I55&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L55" s="4" t="str">
+        <f aca="false">IF(B55="","",IF(K55="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="str">
@@ -2297,20 +2591,25 @@
         <f aca="false">IF(E56="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E56,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G56" s="8"/>
-      <c r="H56" s="9" t="str">
-        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",Сводка!$C$4-G56)</f>
-        <v/>
-      </c>
-      <c r="I56" s="4" t="str">
-        <f aca="false">IF(OR(B56="",Сводка!$C$4=""),"",IF(G56&gt;=Сводка!$C$4,"Оплачено",IF(G56&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J56" s="4" t="str">
-        <f aca="false">IF(B56="","",IF(I56="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K56" s="5"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="8" t="str">
+        <f aca="false">IF(OR(B56="",G56=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G56,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G56,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="8" t="str">
+        <f aca="false">IF(H56="","",H56-I56)</f>
+        <v/>
+      </c>
+      <c r="K56" s="4" t="str">
+        <f aca="false">IF(B56="","",IF(G56="","Пакет не выбран",IF(H56="","",IF(I56&gt;=H56,"Оплачено",IF(I56&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L56" s="4" t="str">
+        <f aca="false">IF(B56="","",IF(K56="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="str">
@@ -2325,20 +2624,25 @@
         <f aca="false">IF(E57="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E57,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="9" t="str">
-        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",Сводка!$C$4-G57)</f>
-        <v/>
-      </c>
-      <c r="I57" s="4" t="str">
-        <f aca="false">IF(OR(B57="",Сводка!$C$4=""),"",IF(G57&gt;=Сводка!$C$4,"Оплачено",IF(G57&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J57" s="4" t="str">
-        <f aca="false">IF(B57="","",IF(I57="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K57" s="5"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="8" t="str">
+        <f aca="false">IF(OR(B57="",G57=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G57,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G57,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I57" s="9"/>
+      <c r="J57" s="8" t="str">
+        <f aca="false">IF(H57="","",H57-I57)</f>
+        <v/>
+      </c>
+      <c r="K57" s="4" t="str">
+        <f aca="false">IF(B57="","",IF(G57="","Пакет не выбран",IF(H57="","",IF(I57&gt;=H57,"Оплачено",IF(I57&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L57" s="4" t="str">
+        <f aca="false">IF(B57="","",IF(K57="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="str">
@@ -2353,20 +2657,25 @@
         <f aca="false">IF(E58="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E58,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G58" s="8"/>
-      <c r="H58" s="9" t="str">
-        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",Сводка!$C$4-G58)</f>
-        <v/>
-      </c>
-      <c r="I58" s="4" t="str">
-        <f aca="false">IF(OR(B58="",Сводка!$C$4=""),"",IF(G58&gt;=Сводка!$C$4,"Оплачено",IF(G58&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J58" s="4" t="str">
-        <f aca="false">IF(B58="","",IF(I58="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="8" t="str">
+        <f aca="false">IF(OR(B58="",G58=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G58,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G58,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="8" t="str">
+        <f aca="false">IF(H58="","",H58-I58)</f>
+        <v/>
+      </c>
+      <c r="K58" s="4" t="str">
+        <f aca="false">IF(B58="","",IF(G58="","Пакет не выбран",IF(H58="","",IF(I58&gt;=H58,"Оплачено",IF(I58&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L58" s="4" t="str">
+        <f aca="false">IF(B58="","",IF(K58="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="str">
@@ -2381,20 +2690,25 @@
         <f aca="false">IF(E59="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E59,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9" t="str">
-        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",Сводка!$C$4-G59)</f>
-        <v/>
-      </c>
-      <c r="I59" s="4" t="str">
-        <f aca="false">IF(OR(B59="",Сводка!$C$4=""),"",IF(G59&gt;=Сводка!$C$4,"Оплачено",IF(G59&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J59" s="4" t="str">
-        <f aca="false">IF(B59="","",IF(I59="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K59" s="5"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="8" t="str">
+        <f aca="false">IF(OR(B59="",G59=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G59,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G59,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="8" t="str">
+        <f aca="false">IF(H59="","",H59-I59)</f>
+        <v/>
+      </c>
+      <c r="K59" s="4" t="str">
+        <f aca="false">IF(B59="","",IF(G59="","Пакет не выбран",IF(H59="","",IF(I59&gt;=H59,"Оплачено",IF(I59&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L59" s="4" t="str">
+        <f aca="false">IF(B59="","",IF(K59="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="str">
@@ -2409,20 +2723,25 @@
         <f aca="false">IF(E60="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E60,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9" t="str">
-        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",Сводка!$C$4-G60)</f>
-        <v/>
-      </c>
-      <c r="I60" s="4" t="str">
-        <f aca="false">IF(OR(B60="",Сводка!$C$4=""),"",IF(G60&gt;=Сводка!$C$4,"Оплачено",IF(G60&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J60" s="4" t="str">
-        <f aca="false">IF(B60="","",IF(I60="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K60" s="5"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="8" t="str">
+        <f aca="false">IF(OR(B60="",G60=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G60,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G60,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I60" s="9"/>
+      <c r="J60" s="8" t="str">
+        <f aca="false">IF(H60="","",H60-I60)</f>
+        <v/>
+      </c>
+      <c r="K60" s="4" t="str">
+        <f aca="false">IF(B60="","",IF(G60="","Пакет не выбран",IF(H60="","",IF(I60&gt;=H60,"Оплачено",IF(I60&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L60" s="4" t="str">
+        <f aca="false">IF(B60="","",IF(K60="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="str">
@@ -2437,20 +2756,25 @@
         <f aca="false">IF(E61="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E61,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="9" t="str">
-        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",Сводка!$C$4-G61)</f>
-        <v/>
-      </c>
-      <c r="I61" s="4" t="str">
-        <f aca="false">IF(OR(B61="",Сводка!$C$4=""),"",IF(G61&gt;=Сводка!$C$4,"Оплачено",IF(G61&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J61" s="4" t="str">
-        <f aca="false">IF(B61="","",IF(I61="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K61" s="5"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="8" t="str">
+        <f aca="false">IF(OR(B61="",G61=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G61,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G61,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I61" s="9"/>
+      <c r="J61" s="8" t="str">
+        <f aca="false">IF(H61="","",H61-I61)</f>
+        <v/>
+      </c>
+      <c r="K61" s="4" t="str">
+        <f aca="false">IF(B61="","",IF(G61="","Пакет не выбран",IF(H61="","",IF(I61&gt;=H61,"Оплачено",IF(I61&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L61" s="4" t="str">
+        <f aca="false">IF(B61="","",IF(K61="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="str">
@@ -2465,20 +2789,25 @@
         <f aca="false">IF(E62="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E62,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G62" s="8"/>
-      <c r="H62" s="9" t="str">
-        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",Сводка!$C$4-G62)</f>
-        <v/>
-      </c>
-      <c r="I62" s="4" t="str">
-        <f aca="false">IF(OR(B62="",Сводка!$C$4=""),"",IF(G62&gt;=Сводка!$C$4,"Оплачено",IF(G62&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J62" s="4" t="str">
-        <f aca="false">IF(B62="","",IF(I62="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K62" s="5"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="8" t="str">
+        <f aca="false">IF(OR(B62="",G62=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G62,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G62,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I62" s="9"/>
+      <c r="J62" s="8" t="str">
+        <f aca="false">IF(H62="","",H62-I62)</f>
+        <v/>
+      </c>
+      <c r="K62" s="4" t="str">
+        <f aca="false">IF(B62="","",IF(G62="","Пакет не выбран",IF(H62="","",IF(I62&gt;=H62,"Оплачено",IF(I62&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L62" s="4" t="str">
+        <f aca="false">IF(B62="","",IF(K62="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="str">
@@ -2493,20 +2822,25 @@
         <f aca="false">IF(E63="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E63,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G63" s="8"/>
-      <c r="H63" s="9" t="str">
-        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",Сводка!$C$4-G63)</f>
-        <v/>
-      </c>
-      <c r="I63" s="4" t="str">
-        <f aca="false">IF(OR(B63="",Сводка!$C$4=""),"",IF(G63&gt;=Сводка!$C$4,"Оплачено",IF(G63&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J63" s="4" t="str">
-        <f aca="false">IF(B63="","",IF(I63="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K63" s="5"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="8" t="str">
+        <f aca="false">IF(OR(B63="",G63=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G63,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G63,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I63" s="9"/>
+      <c r="J63" s="8" t="str">
+        <f aca="false">IF(H63="","",H63-I63)</f>
+        <v/>
+      </c>
+      <c r="K63" s="4" t="str">
+        <f aca="false">IF(B63="","",IF(G63="","Пакет не выбран",IF(H63="","",IF(I63&gt;=H63,"Оплачено",IF(I63&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L63" s="4" t="str">
+        <f aca="false">IF(B63="","",IF(K63="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="str">
@@ -2521,20 +2855,25 @@
         <f aca="false">IF(E64="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E64,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G64" s="8"/>
-      <c r="H64" s="9" t="str">
-        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",Сводка!$C$4-G64)</f>
-        <v/>
-      </c>
-      <c r="I64" s="4" t="str">
-        <f aca="false">IF(OR(B64="",Сводка!$C$4=""),"",IF(G64&gt;=Сводка!$C$4,"Оплачено",IF(G64&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J64" s="4" t="str">
-        <f aca="false">IF(B64="","",IF(I64="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K64" s="5"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="8" t="str">
+        <f aca="false">IF(OR(B64="",G64=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G64,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G64,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I64" s="9"/>
+      <c r="J64" s="8" t="str">
+        <f aca="false">IF(H64="","",H64-I64)</f>
+        <v/>
+      </c>
+      <c r="K64" s="4" t="str">
+        <f aca="false">IF(B64="","",IF(G64="","Пакет не выбран",IF(H64="","",IF(I64&gt;=H64,"Оплачено",IF(I64&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L64" s="4" t="str">
+        <f aca="false">IF(B64="","",IF(K64="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="str">
@@ -2549,20 +2888,25 @@
         <f aca="false">IF(E65="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E65,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G65" s="8"/>
-      <c r="H65" s="9" t="str">
-        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",Сводка!$C$4-G65)</f>
-        <v/>
-      </c>
-      <c r="I65" s="4" t="str">
-        <f aca="false">IF(OR(B65="",Сводка!$C$4=""),"",IF(G65&gt;=Сводка!$C$4,"Оплачено",IF(G65&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J65" s="4" t="str">
-        <f aca="false">IF(B65="","",IF(I65="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K65" s="5"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="8" t="str">
+        <f aca="false">IF(OR(B65="",G65=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G65,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G65,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I65" s="9"/>
+      <c r="J65" s="8" t="str">
+        <f aca="false">IF(H65="","",H65-I65)</f>
+        <v/>
+      </c>
+      <c r="K65" s="4" t="str">
+        <f aca="false">IF(B65="","",IF(G65="","Пакет не выбран",IF(H65="","",IF(I65&gt;=H65,"Оплачено",IF(I65&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L65" s="4" t="str">
+        <f aca="false">IF(B65="","",IF(K65="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="str">
@@ -2577,20 +2921,25 @@
         <f aca="false">IF(E66="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E66,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G66" s="8"/>
-      <c r="H66" s="9" t="str">
-        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",Сводка!$C$4-G66)</f>
-        <v/>
-      </c>
-      <c r="I66" s="4" t="str">
-        <f aca="false">IF(OR(B66="",Сводка!$C$4=""),"",IF(G66&gt;=Сводка!$C$4,"Оплачено",IF(G66&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J66" s="4" t="str">
-        <f aca="false">IF(B66="","",IF(I66="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K66" s="5"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="8" t="str">
+        <f aca="false">IF(OR(B66="",G66=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G66,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G66,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I66" s="9"/>
+      <c r="J66" s="8" t="str">
+        <f aca="false">IF(H66="","",H66-I66)</f>
+        <v/>
+      </c>
+      <c r="K66" s="4" t="str">
+        <f aca="false">IF(B66="","",IF(G66="","Пакет не выбран",IF(H66="","",IF(I66&gt;=H66,"Оплачено",IF(I66&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L66" s="4" t="str">
+        <f aca="false">IF(B66="","",IF(K66="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="str">
@@ -2605,20 +2954,25 @@
         <f aca="false">IF(E67="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E67,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G67" s="8"/>
-      <c r="H67" s="9" t="str">
-        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",Сводка!$C$4-G67)</f>
-        <v/>
-      </c>
-      <c r="I67" s="4" t="str">
-        <f aca="false">IF(OR(B67="",Сводка!$C$4=""),"",IF(G67&gt;=Сводка!$C$4,"Оплачено",IF(G67&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J67" s="4" t="str">
-        <f aca="false">IF(B67="","",IF(I67="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K67" s="5"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="8" t="str">
+        <f aca="false">IF(OR(B67="",G67=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G67,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G67,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I67" s="9"/>
+      <c r="J67" s="8" t="str">
+        <f aca="false">IF(H67="","",H67-I67)</f>
+        <v/>
+      </c>
+      <c r="K67" s="4" t="str">
+        <f aca="false">IF(B67="","",IF(G67="","Пакет не выбран",IF(H67="","",IF(I67&gt;=H67,"Оплачено",IF(I67&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L67" s="4" t="str">
+        <f aca="false">IF(B67="","",IF(K67="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="str">
@@ -2633,20 +2987,25 @@
         <f aca="false">IF(E68="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E68,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G68" s="8"/>
-      <c r="H68" s="9" t="str">
-        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",Сводка!$C$4-G68)</f>
-        <v/>
-      </c>
-      <c r="I68" s="4" t="str">
-        <f aca="false">IF(OR(B68="",Сводка!$C$4=""),"",IF(G68&gt;=Сводка!$C$4,"Оплачено",IF(G68&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J68" s="4" t="str">
-        <f aca="false">IF(B68="","",IF(I68="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K68" s="5"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="8" t="str">
+        <f aca="false">IF(OR(B68="",G68=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G68,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G68,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I68" s="9"/>
+      <c r="J68" s="8" t="str">
+        <f aca="false">IF(H68="","",H68-I68)</f>
+        <v/>
+      </c>
+      <c r="K68" s="4" t="str">
+        <f aca="false">IF(B68="","",IF(G68="","Пакет не выбран",IF(H68="","",IF(I68&gt;=H68,"Оплачено",IF(I68&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L68" s="4" t="str">
+        <f aca="false">IF(B68="","",IF(K68="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="str">
@@ -2661,20 +3020,25 @@
         <f aca="false">IF(E69="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E69,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G69" s="8"/>
-      <c r="H69" s="9" t="str">
-        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",Сводка!$C$4-G69)</f>
-        <v/>
-      </c>
-      <c r="I69" s="4" t="str">
-        <f aca="false">IF(OR(B69="",Сводка!$C$4=""),"",IF(G69&gt;=Сводка!$C$4,"Оплачено",IF(G69&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J69" s="4" t="str">
-        <f aca="false">IF(B69="","",IF(I69="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K69" s="5"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="8" t="str">
+        <f aca="false">IF(OR(B69="",G69=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G69,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G69,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I69" s="9"/>
+      <c r="J69" s="8" t="str">
+        <f aca="false">IF(H69="","",H69-I69)</f>
+        <v/>
+      </c>
+      <c r="K69" s="4" t="str">
+        <f aca="false">IF(B69="","",IF(G69="","Пакет не выбран",IF(H69="","",IF(I69&gt;=H69,"Оплачено",IF(I69&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L69" s="4" t="str">
+        <f aca="false">IF(B69="","",IF(K69="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="str">
@@ -2689,20 +3053,25 @@
         <f aca="false">IF(E70="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E70,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G70" s="8"/>
-      <c r="H70" s="9" t="str">
-        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",Сводка!$C$4-G70)</f>
-        <v/>
-      </c>
-      <c r="I70" s="4" t="str">
-        <f aca="false">IF(OR(B70="",Сводка!$C$4=""),"",IF(G70&gt;=Сводка!$C$4,"Оплачено",IF(G70&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J70" s="4" t="str">
-        <f aca="false">IF(B70="","",IF(I70="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K70" s="5"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="8" t="str">
+        <f aca="false">IF(OR(B70="",G70=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G70,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G70,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I70" s="9"/>
+      <c r="J70" s="8" t="str">
+        <f aca="false">IF(H70="","",H70-I70)</f>
+        <v/>
+      </c>
+      <c r="K70" s="4" t="str">
+        <f aca="false">IF(B70="","",IF(G70="","Пакет не выбран",IF(H70="","",IF(I70&gt;=H70,"Оплачено",IF(I70&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L70" s="4" t="str">
+        <f aca="false">IF(B70="","",IF(K70="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="str">
@@ -2717,20 +3086,25 @@
         <f aca="false">IF(E71="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E71,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G71" s="8"/>
-      <c r="H71" s="9" t="str">
-        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",Сводка!$C$4-G71)</f>
-        <v/>
-      </c>
-      <c r="I71" s="4" t="str">
-        <f aca="false">IF(OR(B71="",Сводка!$C$4=""),"",IF(G71&gt;=Сводка!$C$4,"Оплачено",IF(G71&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J71" s="4" t="str">
-        <f aca="false">IF(B71="","",IF(I71="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K71" s="5"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="8" t="str">
+        <f aca="false">IF(OR(B71="",G71=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G71,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G71,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I71" s="9"/>
+      <c r="J71" s="8" t="str">
+        <f aca="false">IF(H71="","",H71-I71)</f>
+        <v/>
+      </c>
+      <c r="K71" s="4" t="str">
+        <f aca="false">IF(B71="","",IF(G71="","Пакет не выбран",IF(H71="","",IF(I71&gt;=H71,"Оплачено",IF(I71&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L71" s="4" t="str">
+        <f aca="false">IF(B71="","",IF(K71="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="str">
@@ -2745,20 +3119,25 @@
         <f aca="false">IF(E72="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E72,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="9" t="str">
-        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",Сводка!$C$4-G72)</f>
-        <v/>
-      </c>
-      <c r="I72" s="4" t="str">
-        <f aca="false">IF(OR(B72="",Сводка!$C$4=""),"",IF(G72&gt;=Сводка!$C$4,"Оплачено",IF(G72&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J72" s="4" t="str">
-        <f aca="false">IF(B72="","",IF(I72="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K72" s="5"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="8" t="str">
+        <f aca="false">IF(OR(B72="",G72=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G72,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G72,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I72" s="9"/>
+      <c r="J72" s="8" t="str">
+        <f aca="false">IF(H72="","",H72-I72)</f>
+        <v/>
+      </c>
+      <c r="K72" s="4" t="str">
+        <f aca="false">IF(B72="","",IF(G72="","Пакет не выбран",IF(H72="","",IF(I72&gt;=H72,"Оплачено",IF(I72&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L72" s="4" t="str">
+        <f aca="false">IF(B72="","",IF(K72="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="str">
@@ -2773,20 +3152,25 @@
         <f aca="false">IF(E73="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E73,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G73" s="8"/>
-      <c r="H73" s="9" t="str">
-        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",Сводка!$C$4-G73)</f>
-        <v/>
-      </c>
-      <c r="I73" s="4" t="str">
-        <f aca="false">IF(OR(B73="",Сводка!$C$4=""),"",IF(G73&gt;=Сводка!$C$4,"Оплачено",IF(G73&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J73" s="4" t="str">
-        <f aca="false">IF(B73="","",IF(I73="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K73" s="5"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="8" t="str">
+        <f aca="false">IF(OR(B73="",G73=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G73,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G73,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I73" s="9"/>
+      <c r="J73" s="8" t="str">
+        <f aca="false">IF(H73="","",H73-I73)</f>
+        <v/>
+      </c>
+      <c r="K73" s="4" t="str">
+        <f aca="false">IF(B73="","",IF(G73="","Пакет не выбран",IF(H73="","",IF(I73&gt;=H73,"Оплачено",IF(I73&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L73" s="4" t="str">
+        <f aca="false">IF(B73="","",IF(K73="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="str">
@@ -2801,20 +3185,25 @@
         <f aca="false">IF(E74="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E74,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G74" s="8"/>
-      <c r="H74" s="9" t="str">
-        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",Сводка!$C$4-G74)</f>
-        <v/>
-      </c>
-      <c r="I74" s="4" t="str">
-        <f aca="false">IF(OR(B74="",Сводка!$C$4=""),"",IF(G74&gt;=Сводка!$C$4,"Оплачено",IF(G74&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J74" s="4" t="str">
-        <f aca="false">IF(B74="","",IF(I74="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K74" s="5"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="8" t="str">
+        <f aca="false">IF(OR(B74="",G74=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G74,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G74,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I74" s="9"/>
+      <c r="J74" s="8" t="str">
+        <f aca="false">IF(H74="","",H74-I74)</f>
+        <v/>
+      </c>
+      <c r="K74" s="4" t="str">
+        <f aca="false">IF(B74="","",IF(G74="","Пакет не выбран",IF(H74="","",IF(I74&gt;=H74,"Оплачено",IF(I74&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L74" s="4" t="str">
+        <f aca="false">IF(B74="","",IF(K74="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="str">
@@ -2829,20 +3218,25 @@
         <f aca="false">IF(E75="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E75,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G75" s="8"/>
-      <c r="H75" s="9" t="str">
-        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",Сводка!$C$4-G75)</f>
-        <v/>
-      </c>
-      <c r="I75" s="4" t="str">
-        <f aca="false">IF(OR(B75="",Сводка!$C$4=""),"",IF(G75&gt;=Сводка!$C$4,"Оплачено",IF(G75&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J75" s="4" t="str">
-        <f aca="false">IF(B75="","",IF(I75="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K75" s="5"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="8" t="str">
+        <f aca="false">IF(OR(B75="",G75=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G75,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G75,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I75" s="9"/>
+      <c r="J75" s="8" t="str">
+        <f aca="false">IF(H75="","",H75-I75)</f>
+        <v/>
+      </c>
+      <c r="K75" s="4" t="str">
+        <f aca="false">IF(B75="","",IF(G75="","Пакет не выбран",IF(H75="","",IF(I75&gt;=H75,"Оплачено",IF(I75&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L75" s="4" t="str">
+        <f aca="false">IF(B75="","",IF(K75="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="str">
@@ -2857,20 +3251,25 @@
         <f aca="false">IF(E76="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E76,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G76" s="8"/>
-      <c r="H76" s="9" t="str">
-        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",Сводка!$C$4-G76)</f>
-        <v/>
-      </c>
-      <c r="I76" s="4" t="str">
-        <f aca="false">IF(OR(B76="",Сводка!$C$4=""),"",IF(G76&gt;=Сводка!$C$4,"Оплачено",IF(G76&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J76" s="4" t="str">
-        <f aca="false">IF(B76="","",IF(I76="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K76" s="5"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="8" t="str">
+        <f aca="false">IF(OR(B76="",G76=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G76,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G76,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I76" s="9"/>
+      <c r="J76" s="8" t="str">
+        <f aca="false">IF(H76="","",H76-I76)</f>
+        <v/>
+      </c>
+      <c r="K76" s="4" t="str">
+        <f aca="false">IF(B76="","",IF(G76="","Пакет не выбран",IF(H76="","",IF(I76&gt;=H76,"Оплачено",IF(I76&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L76" s="4" t="str">
+        <f aca="false">IF(B76="","",IF(K76="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="str">
@@ -2885,20 +3284,25 @@
         <f aca="false">IF(E77="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E77,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G77" s="8"/>
-      <c r="H77" s="9" t="str">
-        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",Сводка!$C$4-G77)</f>
-        <v/>
-      </c>
-      <c r="I77" s="4" t="str">
-        <f aca="false">IF(OR(B77="",Сводка!$C$4=""),"",IF(G77&gt;=Сводка!$C$4,"Оплачено",IF(G77&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J77" s="4" t="str">
-        <f aca="false">IF(B77="","",IF(I77="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K77" s="5"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="8" t="str">
+        <f aca="false">IF(OR(B77="",G77=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G77,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G77,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I77" s="9"/>
+      <c r="J77" s="8" t="str">
+        <f aca="false">IF(H77="","",H77-I77)</f>
+        <v/>
+      </c>
+      <c r="K77" s="4" t="str">
+        <f aca="false">IF(B77="","",IF(G77="","Пакет не выбран",IF(H77="","",IF(I77&gt;=H77,"Оплачено",IF(I77&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L77" s="4" t="str">
+        <f aca="false">IF(B77="","",IF(K77="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M77" s="5"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="str">
@@ -2913,20 +3317,25 @@
         <f aca="false">IF(E78="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E78,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G78" s="8"/>
-      <c r="H78" s="9" t="str">
-        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",Сводка!$C$4-G78)</f>
-        <v/>
-      </c>
-      <c r="I78" s="4" t="str">
-        <f aca="false">IF(OR(B78="",Сводка!$C$4=""),"",IF(G78&gt;=Сводка!$C$4,"Оплачено",IF(G78&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J78" s="4" t="str">
-        <f aca="false">IF(B78="","",IF(I78="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K78" s="5"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="8" t="str">
+        <f aca="false">IF(OR(B78="",G78=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G78,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G78,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="8" t="str">
+        <f aca="false">IF(H78="","",H78-I78)</f>
+        <v/>
+      </c>
+      <c r="K78" s="4" t="str">
+        <f aca="false">IF(B78="","",IF(G78="","Пакет не выбран",IF(H78="","",IF(I78&gt;=H78,"Оплачено",IF(I78&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L78" s="4" t="str">
+        <f aca="false">IF(B78="","",IF(K78="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M78" s="5"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="str">
@@ -2941,20 +3350,25 @@
         <f aca="false">IF(E79="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E79,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G79" s="8"/>
-      <c r="H79" s="9" t="str">
-        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",Сводка!$C$4-G79)</f>
-        <v/>
-      </c>
-      <c r="I79" s="4" t="str">
-        <f aca="false">IF(OR(B79="",Сводка!$C$4=""),"",IF(G79&gt;=Сводка!$C$4,"Оплачено",IF(G79&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J79" s="4" t="str">
-        <f aca="false">IF(B79="","",IF(I79="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K79" s="5"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="8" t="str">
+        <f aca="false">IF(OR(B79="",G79=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G79,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G79,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I79" s="9"/>
+      <c r="J79" s="8" t="str">
+        <f aca="false">IF(H79="","",H79-I79)</f>
+        <v/>
+      </c>
+      <c r="K79" s="4" t="str">
+        <f aca="false">IF(B79="","",IF(G79="","Пакет не выбран",IF(H79="","",IF(I79&gt;=H79,"Оплачено",IF(I79&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L79" s="4" t="str">
+        <f aca="false">IF(B79="","",IF(K79="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M79" s="5"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="str">
@@ -2969,20 +3383,25 @@
         <f aca="false">IF(E80="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E80,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G80" s="8"/>
-      <c r="H80" s="9" t="str">
-        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",Сводка!$C$4-G80)</f>
-        <v/>
-      </c>
-      <c r="I80" s="4" t="str">
-        <f aca="false">IF(OR(B80="",Сводка!$C$4=""),"",IF(G80&gt;=Сводка!$C$4,"Оплачено",IF(G80&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J80" s="4" t="str">
-        <f aca="false">IF(B80="","",IF(I80="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K80" s="5"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="8" t="str">
+        <f aca="false">IF(OR(B80="",G80=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G80,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G80,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I80" s="9"/>
+      <c r="J80" s="8" t="str">
+        <f aca="false">IF(H80="","",H80-I80)</f>
+        <v/>
+      </c>
+      <c r="K80" s="4" t="str">
+        <f aca="false">IF(B80="","",IF(G80="","Пакет не выбран",IF(H80="","",IF(I80&gt;=H80,"Оплачено",IF(I80&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L80" s="4" t="str">
+        <f aca="false">IF(B80="","",IF(K80="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M80" s="5"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="str">
@@ -2997,20 +3416,25 @@
         <f aca="false">IF(E81="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E81,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G81" s="8"/>
-      <c r="H81" s="9" t="str">
-        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",Сводка!$C$4-G81)</f>
-        <v/>
-      </c>
-      <c r="I81" s="4" t="str">
-        <f aca="false">IF(OR(B81="",Сводка!$C$4=""),"",IF(G81&gt;=Сводка!$C$4,"Оплачено",IF(G81&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J81" s="4" t="str">
-        <f aca="false">IF(B81="","",IF(I81="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K81" s="5"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="8" t="str">
+        <f aca="false">IF(OR(B81="",G81=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G81,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G81,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I81" s="9"/>
+      <c r="J81" s="8" t="str">
+        <f aca="false">IF(H81="","",H81-I81)</f>
+        <v/>
+      </c>
+      <c r="K81" s="4" t="str">
+        <f aca="false">IF(B81="","",IF(G81="","Пакет не выбран",IF(H81="","",IF(I81&gt;=H81,"Оплачено",IF(I81&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L81" s="4" t="str">
+        <f aca="false">IF(B81="","",IF(K81="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M81" s="5"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="str">
@@ -3025,20 +3449,25 @@
         <f aca="false">IF(E82="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E82,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G82" s="8"/>
-      <c r="H82" s="9" t="str">
-        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",Сводка!$C$4-G82)</f>
-        <v/>
-      </c>
-      <c r="I82" s="4" t="str">
-        <f aca="false">IF(OR(B82="",Сводка!$C$4=""),"",IF(G82&gt;=Сводка!$C$4,"Оплачено",IF(G82&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J82" s="4" t="str">
-        <f aca="false">IF(B82="","",IF(I82="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K82" s="5"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="8" t="str">
+        <f aca="false">IF(OR(B82="",G82=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G82,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G82,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I82" s="9"/>
+      <c r="J82" s="8" t="str">
+        <f aca="false">IF(H82="","",H82-I82)</f>
+        <v/>
+      </c>
+      <c r="K82" s="4" t="str">
+        <f aca="false">IF(B82="","",IF(G82="","Пакет не выбран",IF(H82="","",IF(I82&gt;=H82,"Оплачено",IF(I82&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L82" s="4" t="str">
+        <f aca="false">IF(B82="","",IF(K82="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M82" s="5"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="str">
@@ -3053,20 +3482,25 @@
         <f aca="false">IF(E83="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E83,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G83" s="8"/>
-      <c r="H83" s="9" t="str">
-        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",Сводка!$C$4-G83)</f>
-        <v/>
-      </c>
-      <c r="I83" s="4" t="str">
-        <f aca="false">IF(OR(B83="",Сводка!$C$4=""),"",IF(G83&gt;=Сводка!$C$4,"Оплачено",IF(G83&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J83" s="4" t="str">
-        <f aca="false">IF(B83="","",IF(I83="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K83" s="5"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="8" t="str">
+        <f aca="false">IF(OR(B83="",G83=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G83,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G83,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I83" s="9"/>
+      <c r="J83" s="8" t="str">
+        <f aca="false">IF(H83="","",H83-I83)</f>
+        <v/>
+      </c>
+      <c r="K83" s="4" t="str">
+        <f aca="false">IF(B83="","",IF(G83="","Пакет не выбран",IF(H83="","",IF(I83&gt;=H83,"Оплачено",IF(I83&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L83" s="4" t="str">
+        <f aca="false">IF(B83="","",IF(K83="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M83" s="5"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="str">
@@ -3081,20 +3515,25 @@
         <f aca="false">IF(E84="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E84,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9" t="str">
-        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",Сводка!$C$4-G84)</f>
-        <v/>
-      </c>
-      <c r="I84" s="4" t="str">
-        <f aca="false">IF(OR(B84="",Сводка!$C$4=""),"",IF(G84&gt;=Сводка!$C$4,"Оплачено",IF(G84&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J84" s="4" t="str">
-        <f aca="false">IF(B84="","",IF(I84="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K84" s="5"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="8" t="str">
+        <f aca="false">IF(OR(B84="",G84=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G84,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G84,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I84" s="9"/>
+      <c r="J84" s="8" t="str">
+        <f aca="false">IF(H84="","",H84-I84)</f>
+        <v/>
+      </c>
+      <c r="K84" s="4" t="str">
+        <f aca="false">IF(B84="","",IF(G84="","Пакет не выбран",IF(H84="","",IF(I84&gt;=H84,"Оплачено",IF(I84&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L84" s="4" t="str">
+        <f aca="false">IF(B84="","",IF(K84="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M84" s="5"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="str">
@@ -3109,20 +3548,25 @@
         <f aca="false">IF(E85="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E85,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G85" s="8"/>
-      <c r="H85" s="9" t="str">
-        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",Сводка!$C$4-G85)</f>
-        <v/>
-      </c>
-      <c r="I85" s="4" t="str">
-        <f aca="false">IF(OR(B85="",Сводка!$C$4=""),"",IF(G85&gt;=Сводка!$C$4,"Оплачено",IF(G85&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J85" s="4" t="str">
-        <f aca="false">IF(B85="","",IF(I85="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K85" s="5"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="8" t="str">
+        <f aca="false">IF(OR(B85="",G85=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G85,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G85,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I85" s="9"/>
+      <c r="J85" s="8" t="str">
+        <f aca="false">IF(H85="","",H85-I85)</f>
+        <v/>
+      </c>
+      <c r="K85" s="4" t="str">
+        <f aca="false">IF(B85="","",IF(G85="","Пакет не выбран",IF(H85="","",IF(I85&gt;=H85,"Оплачено",IF(I85&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L85" s="4" t="str">
+        <f aca="false">IF(B85="","",IF(K85="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M85" s="5"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="str">
@@ -3137,20 +3581,25 @@
         <f aca="false">IF(E86="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E86,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G86" s="8"/>
-      <c r="H86" s="9" t="str">
-        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",Сводка!$C$4-G86)</f>
-        <v/>
-      </c>
-      <c r="I86" s="4" t="str">
-        <f aca="false">IF(OR(B86="",Сводка!$C$4=""),"",IF(G86&gt;=Сводка!$C$4,"Оплачено",IF(G86&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J86" s="4" t="str">
-        <f aca="false">IF(B86="","",IF(I86="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K86" s="5"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="8" t="str">
+        <f aca="false">IF(OR(B86="",G86=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G86,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G86,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="8" t="str">
+        <f aca="false">IF(H86="","",H86-I86)</f>
+        <v/>
+      </c>
+      <c r="K86" s="4" t="str">
+        <f aca="false">IF(B86="","",IF(G86="","Пакет не выбран",IF(H86="","",IF(I86&gt;=H86,"Оплачено",IF(I86&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L86" s="4" t="str">
+        <f aca="false">IF(B86="","",IF(K86="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M86" s="5"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="str">
@@ -3165,20 +3614,25 @@
         <f aca="false">IF(E87="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E87,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G87" s="8"/>
-      <c r="H87" s="9" t="str">
-        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",Сводка!$C$4-G87)</f>
-        <v/>
-      </c>
-      <c r="I87" s="4" t="str">
-        <f aca="false">IF(OR(B87="",Сводка!$C$4=""),"",IF(G87&gt;=Сводка!$C$4,"Оплачено",IF(G87&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J87" s="4" t="str">
-        <f aca="false">IF(B87="","",IF(I87="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K87" s="5"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="8" t="str">
+        <f aca="false">IF(OR(B87="",G87=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G87,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G87,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I87" s="9"/>
+      <c r="J87" s="8" t="str">
+        <f aca="false">IF(H87="","",H87-I87)</f>
+        <v/>
+      </c>
+      <c r="K87" s="4" t="str">
+        <f aca="false">IF(B87="","",IF(G87="","Пакет не выбран",IF(H87="","",IF(I87&gt;=H87,"Оплачено",IF(I87&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L87" s="4" t="str">
+        <f aca="false">IF(B87="","",IF(K87="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M87" s="5"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="str">
@@ -3193,20 +3647,25 @@
         <f aca="false">IF(E88="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E88,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G88" s="8"/>
-      <c r="H88" s="9" t="str">
-        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",Сводка!$C$4-G88)</f>
-        <v/>
-      </c>
-      <c r="I88" s="4" t="str">
-        <f aca="false">IF(OR(B88="",Сводка!$C$4=""),"",IF(G88&gt;=Сводка!$C$4,"Оплачено",IF(G88&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J88" s="4" t="str">
-        <f aca="false">IF(B88="","",IF(I88="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K88" s="5"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="8" t="str">
+        <f aca="false">IF(OR(B88="",G88=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G88,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G88,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I88" s="9"/>
+      <c r="J88" s="8" t="str">
+        <f aca="false">IF(H88="","",H88-I88)</f>
+        <v/>
+      </c>
+      <c r="K88" s="4" t="str">
+        <f aca="false">IF(B88="","",IF(G88="","Пакет не выбран",IF(H88="","",IF(I88&gt;=H88,"Оплачено",IF(I88&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L88" s="4" t="str">
+        <f aca="false">IF(B88="","",IF(K88="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M88" s="5"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="str">
@@ -3221,20 +3680,25 @@
         <f aca="false">IF(E89="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E89,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G89" s="8"/>
-      <c r="H89" s="9" t="str">
-        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",Сводка!$C$4-G89)</f>
-        <v/>
-      </c>
-      <c r="I89" s="4" t="str">
-        <f aca="false">IF(OR(B89="",Сводка!$C$4=""),"",IF(G89&gt;=Сводка!$C$4,"Оплачено",IF(G89&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J89" s="4" t="str">
-        <f aca="false">IF(B89="","",IF(I89="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K89" s="5"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="8" t="str">
+        <f aca="false">IF(OR(B89="",G89=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G89,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G89,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I89" s="9"/>
+      <c r="J89" s="8" t="str">
+        <f aca="false">IF(H89="","",H89-I89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="4" t="str">
+        <f aca="false">IF(B89="","",IF(G89="","Пакет не выбран",IF(H89="","",IF(I89&gt;=H89,"Оплачено",IF(I89&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L89" s="4" t="str">
+        <f aca="false">IF(B89="","",IF(K89="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M89" s="5"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="str">
@@ -3249,20 +3713,25 @@
         <f aca="false">IF(E90="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E90,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G90" s="8"/>
-      <c r="H90" s="9" t="str">
-        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",Сводка!$C$4-G90)</f>
-        <v/>
-      </c>
-      <c r="I90" s="4" t="str">
-        <f aca="false">IF(OR(B90="",Сводка!$C$4=""),"",IF(G90&gt;=Сводка!$C$4,"Оплачено",IF(G90&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J90" s="4" t="str">
-        <f aca="false">IF(B90="","",IF(I90="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K90" s="5"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="8" t="str">
+        <f aca="false">IF(OR(B90="",G90=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G90,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G90,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I90" s="9"/>
+      <c r="J90" s="8" t="str">
+        <f aca="false">IF(H90="","",H90-I90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="4" t="str">
+        <f aca="false">IF(B90="","",IF(G90="","Пакет не выбран",IF(H90="","",IF(I90&gt;=H90,"Оплачено",IF(I90&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L90" s="4" t="str">
+        <f aca="false">IF(B90="","",IF(K90="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M90" s="5"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="str">
@@ -3277,20 +3746,25 @@
         <f aca="false">IF(E91="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E91,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G91" s="8"/>
-      <c r="H91" s="9" t="str">
-        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",Сводка!$C$4-G91)</f>
-        <v/>
-      </c>
-      <c r="I91" s="4" t="str">
-        <f aca="false">IF(OR(B91="",Сводка!$C$4=""),"",IF(G91&gt;=Сводка!$C$4,"Оплачено",IF(G91&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J91" s="4" t="str">
-        <f aca="false">IF(B91="","",IF(I91="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K91" s="5"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="8" t="str">
+        <f aca="false">IF(OR(B91="",G91=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G91,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G91,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I91" s="9"/>
+      <c r="J91" s="8" t="str">
+        <f aca="false">IF(H91="","",H91-I91)</f>
+        <v/>
+      </c>
+      <c r="K91" s="4" t="str">
+        <f aca="false">IF(B91="","",IF(G91="","Пакет не выбран",IF(H91="","",IF(I91&gt;=H91,"Оплачено",IF(I91&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L91" s="4" t="str">
+        <f aca="false">IF(B91="","",IF(K91="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M91" s="5"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="str">
@@ -3305,20 +3779,25 @@
         <f aca="false">IF(E92="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E92,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G92" s="8"/>
-      <c r="H92" s="9" t="str">
-        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",Сводка!$C$4-G92)</f>
-        <v/>
-      </c>
-      <c r="I92" s="4" t="str">
-        <f aca="false">IF(OR(B92="",Сводка!$C$4=""),"",IF(G92&gt;=Сводка!$C$4,"Оплачено",IF(G92&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J92" s="4" t="str">
-        <f aca="false">IF(B92="","",IF(I92="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K92" s="5"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="8" t="str">
+        <f aca="false">IF(OR(B92="",G92=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G92,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G92,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I92" s="9"/>
+      <c r="J92" s="8" t="str">
+        <f aca="false">IF(H92="","",H92-I92)</f>
+        <v/>
+      </c>
+      <c r="K92" s="4" t="str">
+        <f aca="false">IF(B92="","",IF(G92="","Пакет не выбран",IF(H92="","",IF(I92&gt;=H92,"Оплачено",IF(I92&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L92" s="4" t="str">
+        <f aca="false">IF(B92="","",IF(K92="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M92" s="5"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="str">
@@ -3333,20 +3812,25 @@
         <f aca="false">IF(E93="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E93,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G93" s="8"/>
-      <c r="H93" s="9" t="str">
-        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",Сводка!$C$4-G93)</f>
-        <v/>
-      </c>
-      <c r="I93" s="4" t="str">
-        <f aca="false">IF(OR(B93="",Сводка!$C$4=""),"",IF(G93&gt;=Сводка!$C$4,"Оплачено",IF(G93&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J93" s="4" t="str">
-        <f aca="false">IF(B93="","",IF(I93="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K93" s="5"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="8" t="str">
+        <f aca="false">IF(OR(B93="",G93=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G93,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G93,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I93" s="9"/>
+      <c r="J93" s="8" t="str">
+        <f aca="false">IF(H93="","",H93-I93)</f>
+        <v/>
+      </c>
+      <c r="K93" s="4" t="str">
+        <f aca="false">IF(B93="","",IF(G93="","Пакет не выбран",IF(H93="","",IF(I93&gt;=H93,"Оплачено",IF(I93&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L93" s="4" t="str">
+        <f aca="false">IF(B93="","",IF(K93="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M93" s="5"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="str">
@@ -3361,20 +3845,25 @@
         <f aca="false">IF(E94="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E94,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G94" s="8"/>
-      <c r="H94" s="9" t="str">
-        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",Сводка!$C$4-G94)</f>
-        <v/>
-      </c>
-      <c r="I94" s="4" t="str">
-        <f aca="false">IF(OR(B94="",Сводка!$C$4=""),"",IF(G94&gt;=Сводка!$C$4,"Оплачено",IF(G94&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J94" s="4" t="str">
-        <f aca="false">IF(B94="","",IF(I94="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K94" s="5"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="8" t="str">
+        <f aca="false">IF(OR(B94="",G94=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G94,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G94,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I94" s="9"/>
+      <c r="J94" s="8" t="str">
+        <f aca="false">IF(H94="","",H94-I94)</f>
+        <v/>
+      </c>
+      <c r="K94" s="4" t="str">
+        <f aca="false">IF(B94="","",IF(G94="","Пакет не выбран",IF(H94="","",IF(I94&gt;=H94,"Оплачено",IF(I94&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L94" s="4" t="str">
+        <f aca="false">IF(B94="","",IF(K94="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M94" s="5"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="str">
@@ -3389,20 +3878,25 @@
         <f aca="false">IF(E95="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E95,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G95" s="8"/>
-      <c r="H95" s="9" t="str">
-        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",Сводка!$C$4-G95)</f>
-        <v/>
-      </c>
-      <c r="I95" s="4" t="str">
-        <f aca="false">IF(OR(B95="",Сводка!$C$4=""),"",IF(G95&gt;=Сводка!$C$4,"Оплачено",IF(G95&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J95" s="4" t="str">
-        <f aca="false">IF(B95="","",IF(I95="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K95" s="5"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="8" t="str">
+        <f aca="false">IF(OR(B95="",G95=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G95,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G95,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I95" s="9"/>
+      <c r="J95" s="8" t="str">
+        <f aca="false">IF(H95="","",H95-I95)</f>
+        <v/>
+      </c>
+      <c r="K95" s="4" t="str">
+        <f aca="false">IF(B95="","",IF(G95="","Пакет не выбран",IF(H95="","",IF(I95&gt;=H95,"Оплачено",IF(I95&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L95" s="4" t="str">
+        <f aca="false">IF(B95="","",IF(K95="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M95" s="5"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="str">
@@ -3417,20 +3911,25 @@
         <f aca="false">IF(E96="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E96,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G96" s="8"/>
-      <c r="H96" s="9" t="str">
-        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",Сводка!$C$4-G96)</f>
-        <v/>
-      </c>
-      <c r="I96" s="4" t="str">
-        <f aca="false">IF(OR(B96="",Сводка!$C$4=""),"",IF(G96&gt;=Сводка!$C$4,"Оплачено",IF(G96&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J96" s="4" t="str">
-        <f aca="false">IF(B96="","",IF(I96="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K96" s="5"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="8" t="str">
+        <f aca="false">IF(OR(B96="",G96=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G96,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G96,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I96" s="9"/>
+      <c r="J96" s="8" t="str">
+        <f aca="false">IF(H96="","",H96-I96)</f>
+        <v/>
+      </c>
+      <c r="K96" s="4" t="str">
+        <f aca="false">IF(B96="","",IF(G96="","Пакет не выбран",IF(H96="","",IF(I96&gt;=H96,"Оплачено",IF(I96&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L96" s="4" t="str">
+        <f aca="false">IF(B96="","",IF(K96="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M96" s="5"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="str">
@@ -3445,20 +3944,25 @@
         <f aca="false">IF(E97="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E97,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G97" s="8"/>
-      <c r="H97" s="9" t="str">
-        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",Сводка!$C$4-G97)</f>
-        <v/>
-      </c>
-      <c r="I97" s="4" t="str">
-        <f aca="false">IF(OR(B97="",Сводка!$C$4=""),"",IF(G97&gt;=Сводка!$C$4,"Оплачено",IF(G97&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J97" s="4" t="str">
-        <f aca="false">IF(B97="","",IF(I97="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K97" s="5"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="8" t="str">
+        <f aca="false">IF(OR(B97="",G97=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G97,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G97,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I97" s="9"/>
+      <c r="J97" s="8" t="str">
+        <f aca="false">IF(H97="","",H97-I97)</f>
+        <v/>
+      </c>
+      <c r="K97" s="4" t="str">
+        <f aca="false">IF(B97="","",IF(G97="","Пакет не выбран",IF(H97="","",IF(I97&gt;=H97,"Оплачено",IF(I97&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L97" s="4" t="str">
+        <f aca="false">IF(B97="","",IF(K97="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M97" s="5"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="str">
@@ -3473,20 +3977,25 @@
         <f aca="false">IF(E98="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E98,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G98" s="8"/>
-      <c r="H98" s="9" t="str">
-        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",Сводка!$C$4-G98)</f>
-        <v/>
-      </c>
-      <c r="I98" s="4" t="str">
-        <f aca="false">IF(OR(B98="",Сводка!$C$4=""),"",IF(G98&gt;=Сводка!$C$4,"Оплачено",IF(G98&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J98" s="4" t="str">
-        <f aca="false">IF(B98="","",IF(I98="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K98" s="5"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="8" t="str">
+        <f aca="false">IF(OR(B98="",G98=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G98,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G98,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I98" s="9"/>
+      <c r="J98" s="8" t="str">
+        <f aca="false">IF(H98="","",H98-I98)</f>
+        <v/>
+      </c>
+      <c r="K98" s="4" t="str">
+        <f aca="false">IF(B98="","",IF(G98="","Пакет не выбран",IF(H98="","",IF(I98&gt;=H98,"Оплачено",IF(I98&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L98" s="4" t="str">
+        <f aca="false">IF(B98="","",IF(K98="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M98" s="5"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="str">
@@ -3501,20 +4010,25 @@
         <f aca="false">IF(E99="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E99,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G99" s="8"/>
-      <c r="H99" s="9" t="str">
-        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",Сводка!$C$4-G99)</f>
-        <v/>
-      </c>
-      <c r="I99" s="4" t="str">
-        <f aca="false">IF(OR(B99="",Сводка!$C$4=""),"",IF(G99&gt;=Сводка!$C$4,"Оплачено",IF(G99&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J99" s="4" t="str">
-        <f aca="false">IF(B99="","",IF(I99="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K99" s="5"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="8" t="str">
+        <f aca="false">IF(OR(B99="",G99=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G99,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G99,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I99" s="9"/>
+      <c r="J99" s="8" t="str">
+        <f aca="false">IF(H99="","",H99-I99)</f>
+        <v/>
+      </c>
+      <c r="K99" s="4" t="str">
+        <f aca="false">IF(B99="","",IF(G99="","Пакет не выбран",IF(H99="","",IF(I99&gt;=H99,"Оплачено",IF(I99&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L99" s="4" t="str">
+        <f aca="false">IF(B99="","",IF(K99="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M99" s="5"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="str">
@@ -3529,20 +4043,25 @@
         <f aca="false">IF(E100="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E100,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G100" s="8"/>
-      <c r="H100" s="9" t="str">
-        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",Сводка!$C$4-G100)</f>
-        <v/>
-      </c>
-      <c r="I100" s="4" t="str">
-        <f aca="false">IF(OR(B100="",Сводка!$C$4=""),"",IF(G100&gt;=Сводка!$C$4,"Оплачено",IF(G100&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J100" s="4" t="str">
-        <f aca="false">IF(B100="","",IF(I100="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K100" s="5"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="8" t="str">
+        <f aca="false">IF(OR(B100="",G100=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G100,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G100,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I100" s="9"/>
+      <c r="J100" s="8" t="str">
+        <f aca="false">IF(H100="","",H100-I100)</f>
+        <v/>
+      </c>
+      <c r="K100" s="4" t="str">
+        <f aca="false">IF(B100="","",IF(G100="","Пакет не выбран",IF(H100="","",IF(I100&gt;=H100,"Оплачено",IF(I100&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L100" s="4" t="str">
+        <f aca="false">IF(B100="","",IF(K100="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M100" s="5"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="str">
@@ -3557,20 +4076,25 @@
         <f aca="false">IF(E101="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E101,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G101" s="8"/>
-      <c r="H101" s="9" t="str">
-        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",Сводка!$C$4-G101)</f>
-        <v/>
-      </c>
-      <c r="I101" s="4" t="str">
-        <f aca="false">IF(OR(B101="",Сводка!$C$4=""),"",IF(G101&gt;=Сводка!$C$4,"Оплачено",IF(G101&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J101" s="4" t="str">
-        <f aca="false">IF(B101="","",IF(I101="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K101" s="5"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="8" t="str">
+        <f aca="false">IF(OR(B101="",G101=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G101,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G101,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I101" s="9"/>
+      <c r="J101" s="8" t="str">
+        <f aca="false">IF(H101="","",H101-I101)</f>
+        <v/>
+      </c>
+      <c r="K101" s="4" t="str">
+        <f aca="false">IF(B101="","",IF(G101="","Пакет не выбран",IF(H101="","",IF(I101&gt;=H101,"Оплачено",IF(I101&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L101" s="4" t="str">
+        <f aca="false">IF(B101="","",IF(K101="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M101" s="5"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="str">
@@ -3585,20 +4109,25 @@
         <f aca="false">IF(E102="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E102,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G102" s="8"/>
-      <c r="H102" s="9" t="str">
-        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",Сводка!$C$4-G102)</f>
-        <v/>
-      </c>
-      <c r="I102" s="4" t="str">
-        <f aca="false">IF(OR(B102="",Сводка!$C$4=""),"",IF(G102&gt;=Сводка!$C$4,"Оплачено",IF(G102&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J102" s="4" t="str">
-        <f aca="false">IF(B102="","",IF(I102="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K102" s="5"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="8" t="str">
+        <f aca="false">IF(OR(B102="",G102=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G102,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G102,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I102" s="9"/>
+      <c r="J102" s="8" t="str">
+        <f aca="false">IF(H102="","",H102-I102)</f>
+        <v/>
+      </c>
+      <c r="K102" s="4" t="str">
+        <f aca="false">IF(B102="","",IF(G102="","Пакет не выбран",IF(H102="","",IF(I102&gt;=H102,"Оплачено",IF(I102&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L102" s="4" t="str">
+        <f aca="false">IF(B102="","",IF(K102="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M102" s="5"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="str">
@@ -3613,20 +4142,25 @@
         <f aca="false">IF(E103="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E103,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G103" s="8"/>
-      <c r="H103" s="9" t="str">
-        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",Сводка!$C$4-G103)</f>
-        <v/>
-      </c>
-      <c r="I103" s="4" t="str">
-        <f aca="false">IF(OR(B103="",Сводка!$C$4=""),"",IF(G103&gt;=Сводка!$C$4,"Оплачено",IF(G103&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J103" s="4" t="str">
-        <f aca="false">IF(B103="","",IF(I103="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K103" s="5"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="8" t="str">
+        <f aca="false">IF(OR(B103="",G103=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G103,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G103,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I103" s="9"/>
+      <c r="J103" s="8" t="str">
+        <f aca="false">IF(H103="","",H103-I103)</f>
+        <v/>
+      </c>
+      <c r="K103" s="4" t="str">
+        <f aca="false">IF(B103="","",IF(G103="","Пакет не выбран",IF(H103="","",IF(I103&gt;=H103,"Оплачено",IF(I103&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L103" s="4" t="str">
+        <f aca="false">IF(B103="","",IF(K103="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M103" s="5"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="str">
@@ -3641,24 +4175,29 @@
         <f aca="false">IF(E104="","",IFERROR(INDEX(Классы!$C$4:$C$33,MATCH(E104,Классы!$B$4:$B$33,0))&amp;"",""))</f>
         <v/>
       </c>
-      <c r="G104" s="8"/>
-      <c r="H104" s="9" t="str">
-        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",Сводка!$C$4-G104)</f>
-        <v/>
-      </c>
-      <c r="I104" s="4" t="str">
-        <f aca="false">IF(OR(B104="",Сводка!$C$4=""),"",IF(G104&gt;=Сводка!$C$4,"Оплачено",IF(G104&gt;0,"Частично","Не оплачено")))</f>
-        <v/>
-      </c>
-      <c r="J104" s="4" t="str">
-        <f aca="false">IF(B104="","",IF(I104="Оплачено","Да","Нет"))</f>
-        <v/>
-      </c>
-      <c r="K104" s="5"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="8" t="str">
+        <f aca="false">IF(OR(B104="",G104=""),"",IFERROR(IF(INDEX(Сводка!$C$7:$C$9,MATCH(G104,Сводка!$B$7:$B$9,0))="","",INDEX(Сводка!$C$7:$C$9,MATCH(G104,Сводка!$B$7:$B$9,0))),""))</f>
+        <v/>
+      </c>
+      <c r="I104" s="9"/>
+      <c r="J104" s="8" t="str">
+        <f aca="false">IF(H104="","",H104-I104)</f>
+        <v/>
+      </c>
+      <c r="K104" s="4" t="str">
+        <f aca="false">IF(B104="","",IF(G104="","Пакет не выбран",IF(H104="","",IF(I104&gt;=H104,"Оплачено",IF(I104&gt;0,"Частично","Не оплачено")))))</f>
+        <v/>
+      </c>
+      <c r="L104" s="4" t="str">
+        <f aca="false">IF(B104="","",IF(K104="Оплачено","Да","Нет"))</f>
+        <v/>
+      </c>
+      <c r="M104" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K104"/>
-  <conditionalFormatting sqref="J5:J104">
+  <autoFilter ref="A4:M104"/>
+  <conditionalFormatting sqref="L5:L104">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Да"</formula>
     </cfRule>
@@ -3666,7 +4205,7 @@
       <formula>"Нет"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I104">
+  <conditionalFormatting sqref="K5:K104">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"Оплачено"</formula>
     </cfRule>
@@ -3676,9 +4215,16 @@
     <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"Не оплачено"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>"Пакет не выбран"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G104" type="decimal">
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Выберите пакет из списка. Названия пакетов задаются на листе «Сводка»." errorStyle="stop" errorTitle="Пакет" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G104" type="list">
+      <formula1>Сводка!$B$7:$B$9</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I104" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3711,12 +4257,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3727,10 +4273,10 @@
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3741,7 +4287,7 @@
         <v/>
       </c>
       <c r="E4" s="4" t="str">
-        <f aca="false">IF(B4="","",COUNTIFS(Ученики!$E$5:$E$104,B4,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B4="","",COUNTIFS(Ученики!$E$5:$E$104,B4,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +4299,7 @@
         <v/>
       </c>
       <c r="E5" s="4" t="str">
-        <f aca="false">IF(B5="","",COUNTIFS(Ученики!$E$5:$E$104,B5,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B5="","",COUNTIFS(Ученики!$E$5:$E$104,B5,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3765,7 +4311,7 @@
         <v/>
       </c>
       <c r="E6" s="4" t="str">
-        <f aca="false">IF(B6="","",COUNTIFS(Ученики!$E$5:$E$104,B6,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B6="","",COUNTIFS(Ученики!$E$5:$E$104,B6,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3777,7 +4323,7 @@
         <v/>
       </c>
       <c r="E7" s="4" t="str">
-        <f aca="false">IF(B7="","",COUNTIFS(Ученики!$E$5:$E$104,B7,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B7="","",COUNTIFS(Ученики!$E$5:$E$104,B7,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3789,7 +4335,7 @@
         <v/>
       </c>
       <c r="E8" s="4" t="str">
-        <f aca="false">IF(B8="","",COUNTIFS(Ученики!$E$5:$E$104,B8,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B8="","",COUNTIFS(Ученики!$E$5:$E$104,B8,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3801,7 +4347,7 @@
         <v/>
       </c>
       <c r="E9" s="4" t="str">
-        <f aca="false">IF(B9="","",COUNTIFS(Ученики!$E$5:$E$104,B9,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B9="","",COUNTIFS(Ученики!$E$5:$E$104,B9,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3813,7 +4359,7 @@
         <v/>
       </c>
       <c r="E10" s="4" t="str">
-        <f aca="false">IF(B10="","",COUNTIFS(Ученики!$E$5:$E$104,B10,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B10="","",COUNTIFS(Ученики!$E$5:$E$104,B10,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3825,7 +4371,7 @@
         <v/>
       </c>
       <c r="E11" s="4" t="str">
-        <f aca="false">IF(B11="","",COUNTIFS(Ученики!$E$5:$E$104,B11,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B11="","",COUNTIFS(Ученики!$E$5:$E$104,B11,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3837,7 +4383,7 @@
         <v/>
       </c>
       <c r="E12" s="4" t="str">
-        <f aca="false">IF(B12="","",COUNTIFS(Ученики!$E$5:$E$104,B12,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B12="","",COUNTIFS(Ученики!$E$5:$E$104,B12,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3849,7 +4395,7 @@
         <v/>
       </c>
       <c r="E13" s="4" t="str">
-        <f aca="false">IF(B13="","",COUNTIFS(Ученики!$E$5:$E$104,B13,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B13="","",COUNTIFS(Ученики!$E$5:$E$104,B13,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3861,7 +4407,7 @@
         <v/>
       </c>
       <c r="E14" s="4" t="str">
-        <f aca="false">IF(B14="","",COUNTIFS(Ученики!$E$5:$E$104,B14,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B14="","",COUNTIFS(Ученики!$E$5:$E$104,B14,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3873,7 +4419,7 @@
         <v/>
       </c>
       <c r="E15" s="4" t="str">
-        <f aca="false">IF(B15="","",COUNTIFS(Ученики!$E$5:$E$104,B15,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B15="","",COUNTIFS(Ученики!$E$5:$E$104,B15,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3885,7 +4431,7 @@
         <v/>
       </c>
       <c r="E16" s="4" t="str">
-        <f aca="false">IF(B16="","",COUNTIFS(Ученики!$E$5:$E$104,B16,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B16="","",COUNTIFS(Ученики!$E$5:$E$104,B16,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +4443,7 @@
         <v/>
       </c>
       <c r="E17" s="4" t="str">
-        <f aca="false">IF(B17="","",COUNTIFS(Ученики!$E$5:$E$104,B17,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B17="","",COUNTIFS(Ученики!$E$5:$E$104,B17,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3909,7 +4455,7 @@
         <v/>
       </c>
       <c r="E18" s="4" t="str">
-        <f aca="false">IF(B18="","",COUNTIFS(Ученики!$E$5:$E$104,B18,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B18="","",COUNTIFS(Ученики!$E$5:$E$104,B18,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3921,7 +4467,7 @@
         <v/>
       </c>
       <c r="E19" s="4" t="str">
-        <f aca="false">IF(B19="","",COUNTIFS(Ученики!$E$5:$E$104,B19,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B19="","",COUNTIFS(Ученики!$E$5:$E$104,B19,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3933,7 +4479,7 @@
         <v/>
       </c>
       <c r="E20" s="4" t="str">
-        <f aca="false">IF(B20="","",COUNTIFS(Ученики!$E$5:$E$104,B20,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B20="","",COUNTIFS(Ученики!$E$5:$E$104,B20,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3945,7 +4491,7 @@
         <v/>
       </c>
       <c r="E21" s="4" t="str">
-        <f aca="false">IF(B21="","",COUNTIFS(Ученики!$E$5:$E$104,B21,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B21="","",COUNTIFS(Ученики!$E$5:$E$104,B21,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3957,7 +4503,7 @@
         <v/>
       </c>
       <c r="E22" s="4" t="str">
-        <f aca="false">IF(B22="","",COUNTIFS(Ученики!$E$5:$E$104,B22,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B22="","",COUNTIFS(Ученики!$E$5:$E$104,B22,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3969,7 +4515,7 @@
         <v/>
       </c>
       <c r="E23" s="4" t="str">
-        <f aca="false">IF(B23="","",COUNTIFS(Ученики!$E$5:$E$104,B23,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B23="","",COUNTIFS(Ученики!$E$5:$E$104,B23,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3981,7 +4527,7 @@
         <v/>
       </c>
       <c r="E24" s="4" t="str">
-        <f aca="false">IF(B24="","",COUNTIFS(Ученики!$E$5:$E$104,B24,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B24="","",COUNTIFS(Ученики!$E$5:$E$104,B24,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -3993,7 +4539,7 @@
         <v/>
       </c>
       <c r="E25" s="4" t="str">
-        <f aca="false">IF(B25="","",COUNTIFS(Ученики!$E$5:$E$104,B25,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B25="","",COUNTIFS(Ученики!$E$5:$E$104,B25,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4005,7 +4551,7 @@
         <v/>
       </c>
       <c r="E26" s="4" t="str">
-        <f aca="false">IF(B26="","",COUNTIFS(Ученики!$E$5:$E$104,B26,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B26="","",COUNTIFS(Ученики!$E$5:$E$104,B26,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4017,7 +4563,7 @@
         <v/>
       </c>
       <c r="E27" s="4" t="str">
-        <f aca="false">IF(B27="","",COUNTIFS(Ученики!$E$5:$E$104,B27,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B27="","",COUNTIFS(Ученики!$E$5:$E$104,B27,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4575,7 @@
         <v/>
       </c>
       <c r="E28" s="4" t="str">
-        <f aca="false">IF(B28="","",COUNTIFS(Ученики!$E$5:$E$104,B28,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B28="","",COUNTIFS(Ученики!$E$5:$E$104,B28,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4041,7 +4587,7 @@
         <v/>
       </c>
       <c r="E29" s="4" t="str">
-        <f aca="false">IF(B29="","",COUNTIFS(Ученики!$E$5:$E$104,B29,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B29="","",COUNTIFS(Ученики!$E$5:$E$104,B29,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4053,7 +4599,7 @@
         <v/>
       </c>
       <c r="E30" s="4" t="str">
-        <f aca="false">IF(B30="","",COUNTIFS(Ученики!$E$5:$E$104,B30,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B30="","",COUNTIFS(Ученики!$E$5:$E$104,B30,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4065,7 +4611,7 @@
         <v/>
       </c>
       <c r="E31" s="4" t="str">
-        <f aca="false">IF(B31="","",COUNTIFS(Ученики!$E$5:$E$104,B31,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B31="","",COUNTIFS(Ученики!$E$5:$E$104,B31,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4077,7 +4623,7 @@
         <v/>
       </c>
       <c r="E32" s="4" t="str">
-        <f aca="false">IF(B32="","",COUNTIFS(Ученики!$E$5:$E$104,B32,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B32="","",COUNTIFS(Ученики!$E$5:$E$104,B32,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
@@ -4089,20 +4635,20 @@
         <v/>
       </c>
       <c r="E33" s="4" t="str">
-        <f aca="false">IF(B33="","",COUNTIFS(Ученики!$E$5:$E$104,B33,Ученики!$J$5:$J$104,"Да"))</f>
+        <f aca="false">IF(B33="","",COUNTIFS(Ученики!$E$5:$E$104,B33,Ученики!$L$5:$L$104,"Да"))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="11" t="n">
         <f aca="false">SUM(D4:D33)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="11" t="n">
         <f aca="false">SUM(E4:E33)</f>
         <v>0</v>
       </c>
@@ -4123,118 +4669,172 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C17"/>
+  <dimension ref="B1:D23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="8"/>
+      <c r="B3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>46322</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>46322</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>22</v>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="4" t="n">
+        <f aca="false">IF(B7="","",COUNTIF(Ученики!$G$5:$G$104,B7))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="17" t="n">
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="4" t="n">
+        <f aca="false">IF(B8="","",COUNTIF(Ученики!$G$5:$G$104,B8))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="4" t="n">
+        <f aca="false">IF(B9="","",COUNTIF(Ученики!$G$5:$G$104,B9))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <f aca="false">COUNTA(Ученики!$B$5:$B$104)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Оплачено")</f>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <f aca="false">COUNTA(Ученики!$G$5:$G$104)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Частично")</f>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <f aca="false">C12-C13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <f aca="false">COUNTIF(Ученики!$I$5:$I$104,"Не оплачено")</f>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <f aca="false">COUNTIF(Ученики!$K$5:$K$104,"Оплачено")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <f aca="false">SUM(Ученики!$G$5:$G$104)</f>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">COUNTIF(Ученики!$K$5:$K$104,"Частично")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="18" t="n">
-        <f aca="false">C8*$C$4</f>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <f aca="false">COUNTIF(Ученики!$K$5:$K$104,"Не оплачено")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <f aca="false">C13-C12</f>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">SUM(Ученики!$I$5:$I$104)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="17" t="n">
-        <f aca="false">COUNTIF(Ученики!$J$5:$J$104,"Да")</f>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">SUM(Ученики!$H$5:$H$104)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
-        <v>31</v>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">C19-C18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <f aca="false">COUNTIF(Ученики!$L$5:$L$104,"Да")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4254,98 +4854,110 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>32</v>
+      <c r="A1" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
-        <v>33</v>
+      <c r="A2" s="17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
-        <v>34</v>
+      <c r="A3" s="17" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
-        <v>35</v>
+      <c r="A4" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>36</v>
+      <c r="A5" s="17" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>37</v>
+      <c r="A6" s="17" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19"/>
+      <c r="A7" s="17" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="21" t="n">
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <v>45000</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>44</v>
+      <c r="G12" s="18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
